--- a/samples/09_종신보험(암진단포함)_검산.xlsx
+++ b/samples/09_종신보험(암진단포함)_검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00 App Project\Life_ins_Doc_Convert_Studio\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3524D9DF-3D34-4AF1-9C16-45DD3FC44EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308559C8-8479-409D-9BA5-388E4D5B8B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/samples/09_종신보험(암진단포함)_검산.xlsx
+++ b/samples/09_종신보험(암진단포함)_검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00 App Project\Life_ins_Doc_Convert_Studio\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308559C8-8479-409D-9BA5-388E4D5B8B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3D6974-1183-4E70-AE7C-7D7F2AFCFD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7884,7 +7884,7 @@
         <v>64</v>
       </c>
       <c r="B80">
-        <f t="shared" ref="B80:B111" si="20">가입나이+A80</f>
+        <f t="shared" ref="B80:B87" si="20">가입나이+A80</f>
         <v>104</v>
       </c>
       <c r="C80" s="19">
@@ -7940,14 +7940,14 @@
         <v>0.9690964262657521</v>
       </c>
       <c r="P80" s="6">
-        <f t="shared" ref="P80:P111" si="26">ROUND(O80*100000,0)</f>
+        <f t="shared" ref="P80:P87" si="26">ROUND(O80*100000,0)</f>
         <v>96910</v>
       </c>
       <c r="Q80" s="7">
         <v>96910</v>
       </c>
       <c r="R80" s="6">
-        <f t="shared" ref="R80:R111" si="27">P80-Q80</f>
+        <f t="shared" ref="R80:R87" si="27">P80-Q80</f>
         <v>0</v>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
         <v>32</v>
       </c>
       <c r="B48">
-        <f t="shared" ref="B48:B79" si="10">가입나이+A48</f>
+        <f t="shared" ref="B48:B77" si="10">가입나이+A48</f>
         <v>72</v>
       </c>
       <c r="C48" s="19">
@@ -11147,14 +11147,14 @@
         <v>0.3162380436765313</v>
       </c>
       <c r="P48" s="6">
-        <f t="shared" ref="P48:P79" si="16">ROUND(O48*100000,0)</f>
+        <f t="shared" ref="P48:P77" si="16">ROUND(O48*100000,0)</f>
         <v>31624</v>
       </c>
       <c r="Q48" s="7">
         <v>31624</v>
       </c>
       <c r="R48" s="6">
-        <f t="shared" ref="R48:R79" si="17">P48-Q48</f>
+        <f t="shared" ref="R48:R77" si="17">P48-Q48</f>
         <v>0</v>
       </c>
     </row>

--- a/samples/09_종신보험(암진단포함)_검산.xlsx
+++ b/samples/09_종신보험(암진단포함)_검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00 App Project\Life_ins_Doc_Convert_Studio\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3D6974-1183-4E70-AE7C-7D7F2AFCFD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559B55F0-4C29-4B72-8DF2-3099D1D8D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">  입력      기초율·사업비·계약 (노란 칸을 바꾸면 모든 시트가 다시 계산된다)</t>
   </si>
   <si>
-    <t xml:space="preserve">  위험률    연령 × 위험률 (계약 성별 — 공개 기본 위험률: 제7회 경험생명표 사망률 · 80% 이상 장해율 · 생명장기제2024-112호 암발생률)</t>
+    <t xml:space="preserve">  위험률    연령 × 위험률 (계약 성별 — 공개 기본 위험률: 사망률 · 80% 이상 장해율 · 암발생률)</t>
   </si>
   <si>
     <t xml:space="preserve">  기수_*    담보마다 계산기수와 연말 책임준비금 V — 모두 수식. 초록 열 = 앱(자유설계보험) 값, 그 옆 = 차이</t>
@@ -270,7 +270,7 @@
     <t>연령</t>
   </si>
   <si>
-    <t>제7회 경험생명표 사망률 (남)</t>
+    <t>사망률 (남)</t>
   </si>
   <si>
     <t>80% 이상 장해율 (남)</t>
@@ -7884,7 +7884,7 @@
         <v>64</v>
       </c>
       <c r="B80">
-        <f t="shared" ref="B80:B87" si="20">가입나이+A80</f>
+        <f t="shared" ref="B80:B111" si="20">가입나이+A80</f>
         <v>104</v>
       </c>
       <c r="C80" s="19">
@@ -7940,14 +7940,14 @@
         <v>0.9690964262657521</v>
       </c>
       <c r="P80" s="6">
-        <f t="shared" ref="P80:P87" si="26">ROUND(O80*100000,0)</f>
+        <f t="shared" ref="P80:P111" si="26">ROUND(O80*100000,0)</f>
         <v>96910</v>
       </c>
       <c r="Q80" s="7">
         <v>96910</v>
       </c>
       <c r="R80" s="6">
-        <f t="shared" ref="R80:R87" si="27">P80-Q80</f>
+        <f t="shared" ref="R80:R111" si="27">P80-Q80</f>
         <v>0</v>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
         <v>32</v>
       </c>
       <c r="B48">
-        <f t="shared" ref="B48:B77" si="10">가입나이+A48</f>
+        <f t="shared" ref="B48:B79" si="10">가입나이+A48</f>
         <v>72</v>
       </c>
       <c r="C48" s="19">
@@ -11147,14 +11147,14 @@
         <v>0.3162380436765313</v>
       </c>
       <c r="P48" s="6">
-        <f t="shared" ref="P48:P77" si="16">ROUND(O48*100000,0)</f>
+        <f t="shared" ref="P48:P79" si="16">ROUND(O48*100000,0)</f>
         <v>31624</v>
       </c>
       <c r="Q48" s="7">
         <v>31624</v>
       </c>
       <c r="R48" s="6">
-        <f t="shared" ref="R48:R77" si="17">P48-Q48</f>
+        <f t="shared" ref="R48:R79" si="17">P48-Q48</f>
         <v>0</v>
       </c>
     </row>

--- a/samples/09_종신보험(암진단포함)_검산.xlsx
+++ b/samples/09_종신보험(암진단포함)_검산.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00 App Project\Life_ins_Doc_Convert_Studio\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tklee\OneDrive\Documents\00 App Project\Life_ins_Doc_Convert_Studio\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559B55F0-4C29-4B72-8DF2-3099D1D8D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A7D182-C9B1-42E3-9A7A-1C563D4A2E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
   <si>
     <t>종신보험(암진단 포함) — 산출방법서 식 엑셀 검산</t>
   </si>
@@ -87,7 +87,10 @@
     <t>식 (산출방법서 3~5절과 같다)</t>
   </si>
   <si>
-    <t xml:space="preserve">  탈퇴율 Q = q + r − q·r/2 ,  l_{t+1} = l_t·(1 − Q) ,  l′_{t+1} = l′_t·(1 − Q − f + Q·f/2)</t>
+    <t xml:space="preserve">  탈퇴율 Q = q + r − q·r/2 ,  l_{t+1} = l_t·(1 − Q) ,  질병 F = 1 − (1 − r)(1 − f) ,  Q′ = q + F − q·F/2 ,  l′_{t+1} = l′_t·(1 − Q′)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (질병끼리는 곱으로, 사망과는 겹치는 부분을 절반으로 결합한다 · 보장기간 n = 만기 나이 − 가입나이, 종신(110세)은 + 1)</t>
   </si>
   <si>
     <t xml:space="preserve">  D = l·v^t ,  D′ = l′·v^t ,  C = l·g·v^{t+½} (사망형 g = Q, 진단형 g = 그 발생률) ,  N = Σ_{u≥t} D ,  N′ = Σ_{u≥t} D′</t>
@@ -96,7 +99,7 @@
     <t xml:space="preserve">  PVB = Σ S·C ,  N* = k·[(N′_x − N′_{x+m}) − (k−1)/(2k)·(D′_x − D′_{x+m})] ,  P = PVB/N* ,  P_base = PVB/(N′_x − N′_{x+min(n,20)})</t>
   </si>
   <si>
-    <t xml:space="preserve">  G = [P + (α_S + α_P·P_base)·D′_x/N* + β_S/k + β′·(N_{x+m} − N_{x+n})/N*] / (1 − β_G − γ) ,  10만원당 G = ROUND(G×100,000, 0)</t>
+    <t xml:space="preserve">  G = [P + (α_S + α_P·P_base)·D′_x/N* + β_S/k + β′·(N_{x+m} − N_{x+n})/N*] / (1 − β_G − γ) ,  10만원당 G = ROUND(ROUND(G, 6)×100,000, 0)</t>
   </si>
   <si>
     <t xml:space="preserve">  V_t = [Σ_{u≥t} S·C + β′·(N_{x+max(t,m)} − N_{x+n}) − P_β·(N′_{x+t} − N′_{x+m})·[t≤m]] / D_{x+t} ,  P_β = [PVB + β′·(N_{x+m} − N_{x+n})] / (N′_x − N′_{x+m})</t>
@@ -294,7 +297,7 @@
     <t>PVB = Σ S·C</t>
   </si>
   <si>
-    <t>보장 종료 나이</t>
+    <t>만기 나이</t>
   </si>
   <si>
     <t>N* (연납 환산 납입기수)</t>
@@ -351,7 +354,7 @@
     <t>G (영업보험료, 1원당)</t>
   </si>
   <si>
-    <t>10만원당 G (반올림)</t>
+    <t>10만원당 G (1원당 6자리 → 10만원당 반올림)</t>
   </si>
   <si>
     <t>월보험료 = 10만원당 G × 보장금액/10만</t>
@@ -846,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="150" customWidth="1"/>
@@ -932,9 +935,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -954,49 +962,49 @@
   <sheetData>
     <row r="1" spans="1:15" ht="34" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="O1" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
@@ -1018,19 +1026,19 @@
       </c>
       <c r="E2" s="4">
         <f>기수_사망장해!E3</f>
-        <v>18044821.63646188</v>
+        <v>18044892.918851402</v>
       </c>
       <c r="F2" s="5">
         <f>기수_사망장해!E4</f>
-        <v>2.0520117530826677E-3</v>
+        <v>2.0520036470605516E-3</v>
       </c>
       <c r="G2" s="5">
         <f>기수_사망장해!E5</f>
-        <v>2.4273736809634384E-2</v>
+        <v>2.4273647717323835E-2</v>
       </c>
       <c r="H2" s="5">
         <f>기수_사망장해!E10</f>
-        <v>2.6064733255100675E-3</v>
+        <v>2.6064630292728054E-3</v>
       </c>
       <c r="I2" s="6">
         <f>기수_사망장해!E11</f>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="B3">
         <f>기수_암진단!B4</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <f>기수_암진단!B5</f>
@@ -1074,23 +1082,23 @@
       </c>
       <c r="D3" s="3">
         <f>기수_암진단!E2</f>
-        <v>21792.989151600847</v>
+        <v>21787.536743751647</v>
       </c>
       <c r="E3" s="4">
         <f>기수_암진단!E3</f>
-        <v>18044821.636461876</v>
+        <v>18044892.918851402</v>
       </c>
       <c r="F3" s="5">
         <f>기수_암진단!E4</f>
-        <v>1.2077143011247791E-3</v>
+        <v>1.2074073723646387E-3</v>
       </c>
       <c r="G3" s="5">
         <f>기수_암진단!E5</f>
-        <v>1.428634073011247E-2</v>
+        <v>1.4282713995202779E-2</v>
       </c>
       <c r="H3" s="5">
         <f>기수_암진단!E10</f>
-        <v>1.6246051414275189E-3</v>
+        <v>1.6242446156049699E-3</v>
       </c>
       <c r="I3" s="6">
         <f>기수_암진단!E11</f>
@@ -1115,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="6">
-        <f>MAX(MAX(기수_암진단!R16:R77),-MIN(기수_암진단!R16:R77))</f>
+        <f>MAX(MAX(기수_암진단!R16:R76),-MIN(기수_암진단!R16:R76))</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1160,7 +1168,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1181,42 +1189,42 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <f>1/(1+이율)</f>
         <v>0.97560975609756106</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="e">
         <f>1/(1+i)</f>
@@ -1225,140 +1233,140 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="12">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="12">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="12">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7">
-        <f>MAX(기수_사망장해!B3,기수_암진단!B3)+1-가입나이</f>
+        <f>MAX(IF(기수_사망장해!B3&gt;=110,기수_사망장해!B3+1,기수_사망장해!B3),IF(기수_암진단!B3&gt;=110,기수_암진단!B3+1,기수_암진단!B3))-가입나이</f>
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" s="12">
         <v>0.01</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="12">
         <v>1.5E-3</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="12">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="12">
         <v>1E-3</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1378,16 +1386,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -2970,33 +2978,33 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="12">
         <v>100000000</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="15">
         <f>SUMPRODUCT($L$16:$L$86,$K$16:$K$86)</f>
@@ -3012,20 +3020,20 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="12">
         <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="15">
         <f>납입주기*(($N$16-INDEX($N$16:$N$87,B5+1))-(납입주기-1)/(2*납입주기)*($J$16-INDEX($J$16:$J$87,B5+1)))</f>
-        <v>18044821.63646188</v>
+        <v>18044892.918851402</v>
       </c>
       <c r="F3" s="16">
-        <v>18044821.63646188</v>
+        <v>18044892.91885139</v>
       </c>
       <c r="G3" s="17">
         <f>E3-F3</f>
@@ -3034,21 +3042,21 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <f>MIN(보험기간,B3+1-가입나이)</f>
+        <f>MIN(보험기간,IF(B3&gt;=110,B3+1,B3)-가입나이)</f>
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="15">
         <f>E2/E3</f>
-        <v>2.0520117530826677E-3</v>
+        <v>2.0520036470605516E-3</v>
       </c>
       <c r="F4" s="16">
-        <v>2.0520117530826681E-3</v>
+        <v>2.0520036470605529E-3</v>
       </c>
       <c r="G4" s="17">
         <f>E4-F4</f>
@@ -3057,21 +3065,21 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5">
         <f>MIN(납입기간,B4)</f>
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="15">
         <f>E2/($N$16-INDEX($N$16:$N$87,MIN(B4,20)+1))</f>
-        <v>2.4273736809634384E-2</v>
+        <v>2.4273647717323835E-2</v>
       </c>
       <c r="F5" s="16">
-        <v>2.4273736809634391E-2</v>
+        <v>2.4273647717323859E-2</v>
       </c>
       <c r="G5" s="17">
         <f>E5-F5</f>
@@ -3080,13 +3088,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="15">
         <f>알파P*MIN(B4,20)/20</f>
@@ -3097,31 +3105,31 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <f>MAX(0,1-B6/12)</f>
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="15">
         <f>(알파S+E6*E5)*$J$16/E3</f>
-        <v>1.8993668931800302E-4</v>
+        <v>1.8993544528889028E-4</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="15">
         <f>베타S/납입주기</f>
@@ -3132,37 +3140,37 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" s="15">
         <f>베타후*(INDEX($M$16:$M$87,B5+1)-$M$87)/E3</f>
-        <v>5.7071750323691623E-5</v>
+        <v>5.7071524874266374E-5</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="15">
         <f>(E4+E7+E8+E9)/(1-베타G-감마)</f>
-        <v>2.6064733255100675E-3</v>
+        <v>2.6064630292728054E-3</v>
       </c>
       <c r="F10" s="16">
-        <v>2.6064733255100679E-3</v>
+        <v>2.6064630292728071E-3</v>
       </c>
       <c r="G10" s="17">
         <f>E10-F10</f>
@@ -3171,10 +3179,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" s="6">
-        <f>ROUND(E10*100000,0)</f>
+        <f>ROUND(ROUND(E10,6)*100000,0)</f>
         <v>261</v>
       </c>
       <c r="F11" s="7">
@@ -3187,7 +3195,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="6">
         <f>E11*B2/100000</f>
@@ -3203,14 +3211,14 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="15">
         <f>(E2+베타후*(INDEX($M$16:$M$87,B5+1)-$M$87))/($N$16-INDEX($N$16:$N$87,B5+1))</f>
-        <v>2.4948852166328271E-2</v>
+        <v>2.4948760596130305E-2</v>
       </c>
       <c r="F13" s="16">
-        <v>2.4948852166328282E-2</v>
+        <v>2.494876059613033E-2</v>
       </c>
       <c r="G13" s="17">
         <f>E13-F13</f>
@@ -3219,58 +3227,58 @@
     </row>
     <row r="15" spans="1:18" ht="34" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.45">
@@ -3325,7 +3333,7 @@
       </c>
       <c r="N16" s="20">
         <f>SUM(J16:$J$87)</f>
-        <v>2300538.312403921</v>
+        <v>2300628.8044605237</v>
       </c>
       <c r="O16" s="22">
         <f>IF(I16&lt;=0,0,(IF(A16&lt;$B$4,SUMPRODUCT(L16:$L$86,K16:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A16,$B$5)+1)-$M$87)-IF(A16&lt;=$B$5,$E$13*(N16-INDEX($N$16:$N$87,$B$5+1)),0))/I16)</f>
@@ -3372,8 +3380,8 @@
         <v>99899.306320999996</v>
       </c>
       <c r="H17" s="20">
-        <f t="shared" ref="H17:H48" si="9">H16*MAX(0,1-F16-E16+F16*E16/2)</f>
-        <v>99642.435712377526</v>
+        <f t="shared" ref="H17:H48" si="9">H16*MAX(0,1-MIN(1,C16+(1-(1-D16)*(1-E16))-C16*(1-(1-D16)*(1-E16))/2))</f>
+        <v>99642.454593755028</v>
       </c>
       <c r="I17" s="20">
         <f t="shared" si="2"/>
@@ -3381,7 +3389,7 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="3"/>
-        <v>97212.132402319548</v>
+        <v>97212.150823175645</v>
       </c>
       <c r="K17" s="20">
         <f t="shared" si="4"/>
@@ -3397,11 +3405,11 @@
       </c>
       <c r="N17" s="20">
         <f>SUM(J17:$J$87)</f>
-        <v>2200538.3124039206</v>
+        <v>2200628.8044605237</v>
       </c>
       <c r="O17" s="22">
         <f>IF(I17&lt;=0,0,(IF(A17&lt;$B$4,SUMPRODUCT(L17:$L$86,K17:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A17,$B$5)+1)-$M$87)-IF(A17&lt;=$B$5,$E$13*(N17-INDEX($N$16:$N$87,$B$5+1)),0))/I17)</f>
-        <v>2.4577876036913887E-2</v>
+        <v>2.4577782082855083E-2</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="6"/>
@@ -3445,7 +3453,7 @@
       </c>
       <c r="H18" s="20">
         <f t="shared" si="9"/>
-        <v>99263.850194460858</v>
+        <v>99263.890398135787</v>
       </c>
       <c r="I18" s="20">
         <f t="shared" si="2"/>
@@ -3453,7 +3461,7 @@
       </c>
       <c r="J18" s="20">
         <f t="shared" si="3"/>
-        <v>94480.761636607611</v>
+        <v>94480.799903044186</v>
       </c>
       <c r="K18" s="20">
         <f t="shared" si="4"/>
@@ -3469,11 +3477,11 @@
       </c>
       <c r="N18" s="20">
         <f>SUM(J18:$J$87)</f>
-        <v>2103326.1800016006</v>
+        <v>2103416.6536373473</v>
       </c>
       <c r="O18" s="22">
         <f>IF(I18&lt;=0,0,(IF(A18&lt;$B$4,SUMPRODUCT(L18:$L$86,K18:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A18,$B$5)+1)-$M$87)-IF(A18&lt;=$B$5,$E$13*(N18-INDEX($N$16:$N$87,$B$5+1)),0))/I18)</f>
-        <v>4.964111661089475E-2</v>
+        <v>4.9640931319553917E-2</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="6"/>
@@ -3517,7 +3525,7 @@
       </c>
       <c r="H19" s="20">
         <f t="shared" si="9"/>
-        <v>98862.706361801102</v>
+        <v>98862.770340922172</v>
       </c>
       <c r="I19" s="20">
         <f t="shared" si="2"/>
@@ -3525,7 +3533,7 @@
       </c>
       <c r="J19" s="20">
         <f t="shared" si="3"/>
-        <v>91803.850889500623</v>
+        <v>91803.910300474759</v>
       </c>
       <c r="K19" s="20">
         <f t="shared" si="4"/>
@@ -3541,11 +3549,11 @@
       </c>
       <c r="N19" s="20">
         <f>SUM(J19:$J$87)</f>
-        <v>2008845.4183649935</v>
+        <v>2008935.8537343035</v>
       </c>
       <c r="O19" s="22">
         <f>IF(I19&lt;=0,0,(IF(A19&lt;$B$4,SUMPRODUCT(L19:$L$86,K19:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A19,$B$5)+1)-$M$87)-IF(A19&lt;=$B$5,$E$13*(N19-INDEX($N$16:$N$87,$B$5+1)),0))/I19)</f>
-        <v>7.5175711427543881E-2</v>
+        <v>7.517543810796487E-2</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="6"/>
@@ -3589,7 +3597,7 @@
       </c>
       <c r="H20" s="20">
         <f t="shared" si="9"/>
-        <v>98438.892417949377</v>
+        <v>98438.982981699257</v>
       </c>
       <c r="I20" s="20">
         <f t="shared" si="2"/>
@@ -3597,7 +3605,7 @@
       </c>
       <c r="J20" s="20">
         <f t="shared" si="3"/>
-        <v>89180.778059414952</v>
+        <v>89180.860105702552</v>
       </c>
       <c r="K20" s="20">
         <f t="shared" si="4"/>
@@ -3613,11 +3621,11 @@
       </c>
       <c r="N20" s="20">
         <f>SUM(J20:$J$87)</f>
-        <v>1917041.5674754926</v>
+        <v>1917131.9434338284</v>
       </c>
       <c r="O20" s="22">
         <f>IF(I20&lt;=0,0,(IF(A20&lt;$B$4,SUMPRODUCT(L20:$L$86,K20:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A20,$B$5)+1)-$M$87)-IF(A20&lt;=$B$5,$E$13*(N20-INDEX($N$16:$N$87,$B$5+1)),0))/I20)</f>
-        <v>0.10117647366085578</v>
+        <v>0.10117611633443681</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="6"/>
@@ -3661,7 +3669,7 @@
       </c>
       <c r="H21" s="20">
         <f t="shared" si="9"/>
-        <v>97991.040606488357</v>
+        <v>97991.160940633941</v>
       </c>
       <c r="I21" s="20">
         <f t="shared" si="2"/>
@@ -3669,7 +3677,7 @@
       </c>
       <c r="J21" s="20">
         <f t="shared" si="3"/>
-        <v>86609.801387363041</v>
+        <v>86609.907745213568</v>
       </c>
       <c r="K21" s="20">
         <f t="shared" si="4"/>
@@ -3685,11 +3693,11 @@
       </c>
       <c r="N21" s="20">
         <f>SUM(J21:$J$87)</f>
-        <v>1827860.7894160778</v>
+        <v>1827951.083328126</v>
       </c>
       <c r="O21" s="22">
         <f>IF(I21&lt;=0,0,(IF(A21&lt;$B$4,SUMPRODUCT(L21:$L$86,K21:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A21,$B$5)+1)-$M$87)-IF(A21&lt;=$B$5,$E$13*(N21-INDEX($N$16:$N$87,$B$5+1)),0))/I21)</f>
-        <v>0.12763172532139996</v>
+        <v>0.12763128882727065</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="6"/>
@@ -3733,7 +3741,7 @@
       </c>
       <c r="H22" s="20">
         <f t="shared" si="9"/>
-        <v>97517.045875529191</v>
+        <v>97517.200282228834</v>
       </c>
       <c r="I22" s="20">
         <f t="shared" si="2"/>
@@ -3741,7 +3749,7 @@
       </c>
       <c r="J22" s="20">
         <f t="shared" si="3"/>
-        <v>84088.643036195586</v>
+        <v>84088.776180608766</v>
       </c>
       <c r="K22" s="20">
         <f t="shared" si="4"/>
@@ -3757,11 +3765,11 @@
       </c>
       <c r="N22" s="20">
         <f>SUM(J22:$J$87)</f>
-        <v>1741250.9880287147</v>
+        <v>1741341.1755829123</v>
       </c>
       <c r="O22" s="22">
         <f>IF(I22&lt;=0,0,(IF(A22&lt;$B$4,SUMPRODUCT(L22:$L$86,K22:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A22,$B$5)+1)-$M$87)-IF(A22&lt;=$B$5,$E$13*(N22-INDEX($N$16:$N$87,$B$5+1)),0))/I22)</f>
-        <v>0.15453792675351996</v>
+        <v>0.15453741687078906</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="6"/>
@@ -3805,7 +3813,7 @@
       </c>
       <c r="H23" s="20">
         <f t="shared" si="9"/>
-        <v>97014.672213468817</v>
+        <v>97014.86615102661</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="2"/>
@@ -3813,7 +3821,7 @@
       </c>
       <c r="J23" s="20">
         <f t="shared" si="3"/>
-        <v>81615.071026204707</v>
+        <v>81615.234179129868</v>
       </c>
       <c r="K23" s="20">
         <f t="shared" si="4"/>
@@ -3829,11 +3837,11 @@
       </c>
       <c r="N23" s="20">
         <f>SUM(J23:$J$87)</f>
-        <v>1657162.3449925194</v>
+        <v>1657252.3994023034</v>
       </c>
       <c r="O23" s="22">
         <f>IF(I23&lt;=0,0,(IF(A23&lt;$B$4,SUMPRODUCT(L23:$L$86,K23:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A23,$B$5)+1)-$M$87)-IF(A23&lt;=$B$5,$E$13*(N23-INDEX($N$16:$N$87,$B$5+1)),0))/I23)</f>
-        <v>0.18191227727323189</v>
+        <v>0.18191170105386456</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="6"/>
@@ -3877,7 +3885,7 @@
       </c>
       <c r="H24" s="20">
         <f t="shared" si="9"/>
-        <v>96480.112296612875</v>
+        <v>96480.352753141153</v>
       </c>
       <c r="I24" s="20">
         <f t="shared" si="2"/>
@@ -3885,7 +3893,7 @@
       </c>
       <c r="J24" s="20">
         <f t="shared" si="3"/>
-        <v>79185.721319107048</v>
+        <v>79185.918672978063</v>
       </c>
       <c r="K24" s="20">
         <f t="shared" si="4"/>
@@ -3901,11 +3909,11 @@
       </c>
       <c r="N24" s="20">
         <f>SUM(J24:$J$87)</f>
-        <v>1575547.2739663145</v>
+        <v>1575637.1652231738</v>
       </c>
       <c r="O24" s="22">
         <f>IF(I24&lt;=0,0,(IF(A24&lt;$B$4,SUMPRODUCT(L24:$L$86,K24:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A24,$B$5)+1)-$M$87)-IF(A24&lt;=$B$5,$E$13*(N24-INDEX($N$16:$N$87,$B$5+1)),0))/I24)</f>
-        <v>0.20977261524901444</v>
+        <v>0.20977198136880448</v>
       </c>
       <c r="P24" s="6">
         <f t="shared" si="6"/>
@@ -3949,7 +3957,7 @@
       </c>
       <c r="H25" s="20">
         <f t="shared" si="9"/>
-        <v>95910.064154332795</v>
+        <v>95910.359061995317</v>
       </c>
       <c r="I25" s="20">
         <f t="shared" si="2"/>
@@ -3957,7 +3965,7 @@
       </c>
       <c r="J25" s="20">
         <f t="shared" si="3"/>
-        <v>76797.908547446146</v>
+        <v>76798.144688375629</v>
       </c>
       <c r="K25" s="20">
         <f t="shared" si="4"/>
@@ -3973,11 +3981,11 @@
       </c>
       <c r="N25" s="20">
         <f>SUM(J25:$J$87)</f>
-        <v>1496361.5526472074</v>
+        <v>1496451.2465501954</v>
       </c>
       <c r="O25" s="22">
         <f>IF(I25&lt;=0,0,(IF(A25&lt;$B$4,SUMPRODUCT(L25:$L$86,K25:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A25,$B$5)+1)-$M$87)-IF(A25&lt;=$B$5,$E$13*(N25-INDEX($N$16:$N$87,$B$5+1)),0))/I25)</f>
-        <v>0.23814092187813884</v>
+        <v>0.23814024110514223</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="6"/>
@@ -4021,7 +4029,7 @@
       </c>
       <c r="H26" s="20">
         <f t="shared" si="9"/>
-        <v>95300.776980448776</v>
+        <v>95301.135780503479</v>
       </c>
       <c r="I26" s="20">
         <f t="shared" si="2"/>
@@ -4029,7 +4037,7 @@
       </c>
       <c r="J26" s="20">
         <f t="shared" si="3"/>
-        <v>74448.814660346558</v>
+        <v>74449.094954375832</v>
       </c>
       <c r="K26" s="20">
         <f t="shared" si="4"/>
@@ -4045,11 +4053,11 @@
       </c>
       <c r="N26" s="20">
         <f>SUM(J26:$J$87)</f>
-        <v>1419563.6440997613</v>
+        <v>1419653.1018618196</v>
       </c>
       <c r="O26" s="22">
         <f>IF(I26&lt;=0,0,(IF(A26&lt;$B$4,SUMPRODUCT(L26:$L$86,K26:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A26,$B$5)+1)-$M$87)-IF(A26&lt;=$B$5,$E$13*(N26-INDEX($N$16:$N$87,$B$5+1)),0))/I26)</f>
-        <v>0.26702943457396017</v>
+        <v>0.26702872009307138</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="6"/>
@@ -4093,7 +4101,7 @@
       </c>
       <c r="H27" s="20">
         <f t="shared" si="9"/>
-        <v>94663.948633455671</v>
+        <v>94664.354383544051</v>
       </c>
       <c r="I27" s="20">
         <f t="shared" si="2"/>
@@ -4101,7 +4109,7 @@
       </c>
       <c r="J27" s="20">
         <f t="shared" si="3"/>
-        <v>72147.63451073358</v>
+        <v>72147.943751046303</v>
       </c>
       <c r="K27" s="20">
         <f t="shared" si="4"/>
@@ -4117,11 +4125,11 @@
       </c>
       <c r="N27" s="20">
         <f>SUM(J27:$J$87)</f>
-        <v>1345114.8294394149</v>
+        <v>1345204.006907444</v>
       </c>
       <c r="O27" s="22">
         <f>IF(I27&lt;=0,0,(IF(A27&lt;$B$4,SUMPRODUCT(L27:$L$86,K27:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A27,$B$5)+1)-$M$87)-IF(A27&lt;=$B$5,$E$13*(N27-INDEX($N$16:$N$87,$B$5+1)),0))/I27)</f>
-        <v>0.29656473876211281</v>
+        <v>0.29656400678823863</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="6"/>
@@ -4165,7 +4173,7 @@
       </c>
       <c r="H28" s="20">
         <f t="shared" si="9"/>
-        <v>93983.090137495019</v>
+        <v>93983.549659921133</v>
       </c>
       <c r="I28" s="20">
         <f t="shared" si="2"/>
@@ -4173,7 +4181,7 @@
       </c>
       <c r="J28" s="20">
         <f t="shared" si="3"/>
-        <v>69881.679766478119</v>
+        <v>69882.02144708237</v>
       </c>
       <c r="K28" s="20">
         <f t="shared" si="4"/>
@@ -4189,11 +4197,11 @@
       </c>
       <c r="N28" s="20">
         <f>SUM(J28:$J$87)</f>
-        <v>1272967.1949286817</v>
+        <v>1273056.0631563975</v>
       </c>
       <c r="O28" s="22">
         <f>IF(I28&lt;=0,0,(IF(A28&lt;$B$4,SUMPRODUCT(L28:$L$86,K28:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A28,$B$5)+1)-$M$87)-IF(A28&lt;=$B$5,$E$13*(N28-INDEX($N$16:$N$87,$B$5+1)),0))/I28)</f>
-        <v>0.32666230159846305</v>
+        <v>0.32666156437279525</v>
       </c>
       <c r="P28" s="6">
         <f t="shared" si="6"/>
@@ -4237,7 +4245,7 @@
       </c>
       <c r="H29" s="20">
         <f t="shared" si="9"/>
-        <v>93251.411770440231</v>
+        <v>93251.932774164146</v>
       </c>
       <c r="I29" s="20">
         <f t="shared" si="2"/>
@@ -4245,7 +4253,7 @@
       </c>
       <c r="J29" s="20">
         <f t="shared" si="3"/>
-        <v>67646.474156774813</v>
+        <v>67646.852103491939</v>
       </c>
       <c r="K29" s="20">
         <f t="shared" si="4"/>
@@ -4261,11 +4269,11 @@
       </c>
       <c r="N29" s="20">
         <f>SUM(J29:$J$87)</f>
-        <v>1203085.5151622039</v>
+        <v>1203174.041709315</v>
       </c>
       <c r="O29" s="22">
         <f>IF(I29&lt;=0,0,(IF(A29&lt;$B$4,SUMPRODUCT(L29:$L$86,K29:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A29,$B$5)+1)-$M$87)-IF(A29&lt;=$B$5,$E$13*(N29-INDEX($N$16:$N$87,$B$5+1)),0))/I29)</f>
-        <v>0.35731911178949438</v>
+        <v>0.35731838377669251</v>
       </c>
       <c r="P29" s="6">
         <f t="shared" si="6"/>
@@ -4309,7 +4317,7 @@
       </c>
       <c r="H30" s="20">
         <f t="shared" si="9"/>
-        <v>92464.478455144606</v>
+        <v>92465.069567153332</v>
       </c>
       <c r="I30" s="20">
         <f t="shared" si="2"/>
@@ -4317,7 +4325,7 @@
       </c>
       <c r="J30" s="20">
         <f t="shared" si="3"/>
-        <v>65439.626044466793</v>
+        <v>65440.04439051111</v>
       </c>
       <c r="K30" s="20">
         <f t="shared" si="4"/>
@@ -4333,11 +4341,11 @@
       </c>
       <c r="N30" s="20">
         <f>SUM(J30:$J$87)</f>
-        <v>1135439.0410054291</v>
+        <v>1135527.1896058233</v>
       </c>
       <c r="O30" s="22">
         <f>IF(I30&lt;=0,0,(IF(A30&lt;$B$4,SUMPRODUCT(L30:$L$86,K30:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A30,$B$5)+1)-$M$87)-IF(A30&lt;=$B$5,$E$13*(N30-INDEX($N$16:$N$87,$B$5+1)),0))/I30)</f>
-        <v>0.38854775825235022</v>
+        <v>0.38854705649992927</v>
       </c>
       <c r="P30" s="6">
         <f t="shared" si="6"/>
@@ -4381,7 +4389,7 @@
       </c>
       <c r="H31" s="20">
         <f t="shared" si="9"/>
-        <v>91616.563888028206</v>
+        <v>91617.234165977541</v>
       </c>
       <c r="I31" s="20">
         <f t="shared" si="2"/>
@@ -4389,7 +4397,7 @@
       </c>
       <c r="J31" s="20">
         <f t="shared" si="3"/>
-        <v>63258.081800621942</v>
+        <v>63258.544604459472</v>
       </c>
       <c r="K31" s="20">
         <f t="shared" si="4"/>
@@ -4405,11 +4413,11 @@
       </c>
       <c r="N31" s="20">
         <f>SUM(J31:$J$87)</f>
-        <v>1069999.414960962</v>
+        <v>1070087.1452153123</v>
       </c>
       <c r="O31" s="22">
         <f>IF(I31&lt;=0,0,(IF(A31&lt;$B$4,SUMPRODUCT(L31:$L$86,K31:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A31,$B$5)+1)-$M$87)-IF(A31&lt;=$B$5,$E$13*(N31-INDEX($N$16:$N$87,$B$5+1)),0))/I31)</f>
-        <v>0.42035197072797792</v>
+        <v>0.42035131522837932</v>
       </c>
       <c r="P31" s="6">
         <f t="shared" si="6"/>
@@ -4453,7 +4461,7 @@
       </c>
       <c r="H32" s="20">
         <f t="shared" si="9"/>
-        <v>90704.317064834278</v>
+        <v>90705.075886087056</v>
       </c>
       <c r="I32" s="20">
         <f t="shared" si="2"/>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="J32" s="20">
         <f t="shared" si="3"/>
-        <v>61100.689551093412</v>
+        <v>61101.200712009348</v>
       </c>
       <c r="K32" s="20">
         <f t="shared" si="4"/>
@@ -4477,11 +4485,11 @@
       </c>
       <c r="N32" s="20">
         <f>SUM(J32:$J$87)</f>
-        <v>1006741.3331603402</v>
+        <v>1006828.6006108528</v>
       </c>
       <c r="O32" s="22">
         <f>IF(I32&lt;=0,0,(IF(A32&lt;$B$4,SUMPRODUCT(L32:$L$86,K32:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A32,$B$5)+1)-$M$87)-IF(A32&lt;=$B$5,$E$13*(N32-INDEX($N$16:$N$87,$B$5+1)),0))/I32)</f>
-        <v>0.45275018011504869</v>
+        <v>0.45274959409437837</v>
       </c>
       <c r="P32" s="6">
         <f t="shared" si="6"/>
@@ -4525,7 +4533,7 @@
       </c>
       <c r="H33" s="20">
         <f t="shared" si="9"/>
-        <v>89720.823481680229</v>
+        <v>89721.680877245992</v>
       </c>
       <c r="I33" s="20">
         <f t="shared" si="2"/>
@@ -4533,7 +4541,7 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="3"/>
-        <v>58964.081708821628</v>
+        <v>58964.645184949404</v>
       </c>
       <c r="K33" s="20">
         <f t="shared" si="4"/>
@@ -4549,11 +4557,11 @@
       </c>
       <c r="N33" s="20">
         <f>SUM(J33:$J$87)</f>
-        <v>945640.64360924682</v>
+        <v>945727.39989884337</v>
       </c>
       <c r="O33" s="22">
         <f>IF(I33&lt;=0,0,(IF(A33&lt;$B$4,SUMPRODUCT(L33:$L$86,K33:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A33,$B$5)+1)-$M$87)-IF(A33&lt;=$B$5,$E$13*(N33-INDEX($N$16:$N$87,$B$5+1)),0))/I33)</f>
-        <v>0.48574656622405982</v>
+        <v>0.48574607639256512</v>
       </c>
       <c r="P33" s="6">
         <f t="shared" si="6"/>
@@ -4597,7 +4605,7 @@
       </c>
       <c r="H34" s="20">
         <f t="shared" si="9"/>
-        <v>88657.370864054858</v>
+        <v>88658.337393518261</v>
       </c>
       <c r="I34" s="20">
         <f t="shared" si="2"/>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="J34" s="20">
         <f t="shared" si="3"/>
-        <v>56844.08380983922</v>
+        <v>56844.703515581532</v>
       </c>
       <c r="K34" s="20">
         <f t="shared" si="4"/>
@@ -4621,11 +4629,11 @@
       </c>
       <c r="N34" s="20">
         <f>SUM(J34:$J$87)</f>
-        <v>886676.56190042512</v>
+        <v>886762.75471389398</v>
       </c>
       <c r="O34" s="22">
         <f>IF(I34&lt;=0,0,(IF(A34&lt;$B$4,SUMPRODUCT(L34:$L$86,K34:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A34,$B$5)+1)-$M$87)-IF(A34&lt;=$B$5,$E$13*(N34-INDEX($N$16:$N$87,$B$5+1)),0))/I34)</f>
-        <v>0.51934552210655083</v>
+        <v>0.5193451590548892</v>
       </c>
       <c r="P34" s="6">
         <f t="shared" si="6"/>
@@ -4669,7 +4677,7 @@
       </c>
       <c r="H35" s="20">
         <f t="shared" si="9"/>
-        <v>87504.538206749407</v>
+        <v>87505.625174992616</v>
       </c>
       <c r="I35" s="20">
         <f t="shared" si="2"/>
@@ -4677,7 +4685,7 @@
       </c>
       <c r="J35" s="20">
         <f t="shared" si="3"/>
-        <v>54736.513961756013</v>
+        <v>54737.193890519018</v>
       </c>
       <c r="K35" s="20">
         <f t="shared" si="4"/>
@@ -4693,11 +4701,11 @@
       </c>
       <c r="N35" s="20">
         <f>SUM(J35:$J$87)</f>
-        <v>829832.47809058579</v>
+        <v>829918.05119831243</v>
       </c>
       <c r="O35" s="22">
         <f>IF(I35&lt;=0,0,(IF(A35&lt;$B$4,SUMPRODUCT(L35:$L$86,K35:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A35,$B$5)+1)-$M$87)-IF(A35&lt;=$B$5,$E$13*(N35-INDEX($N$16:$N$87,$B$5+1)),0))/I35)</f>
-        <v>0.55355179454642656</v>
+        <v>0.55355159316067604</v>
       </c>
       <c r="P35" s="6">
         <f t="shared" si="6"/>
@@ -4741,7 +4749,7 @@
       </c>
       <c r="H36" s="20">
         <f t="shared" si="9"/>
-        <v>86254.820107085761</v>
+        <v>86256.040387089888</v>
       </c>
       <c r="I36" s="20">
         <f t="shared" si="2"/>
@@ -4749,7 +4757,7 @@
       </c>
       <c r="J36" s="20">
         <f t="shared" si="3"/>
-        <v>52638.810392870044</v>
+        <v>52639.55509429871</v>
       </c>
       <c r="K36" s="20">
         <f t="shared" si="4"/>
@@ -4765,7 +4773,7 @@
       </c>
       <c r="N36" s="20">
         <f>SUM(J36:$J$87)</f>
-        <v>775095.96412882977</v>
+        <v>775180.85730779346</v>
       </c>
       <c r="O36" s="22">
         <f>IF(I36&lt;=0,0,(IF(A36&lt;$B$4,SUMPRODUCT(L36:$L$86,K36:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A36,$B$5)+1)-$M$87)-IF(A36&lt;=$B$5,$E$13*(N36-INDEX($N$16:$N$87,$B$5+1)),0))/I36)</f>
@@ -4813,7 +4821,7 @@
       </c>
       <c r="H37" s="20">
         <f t="shared" si="9"/>
-        <v>84896.755289116554</v>
+        <v>84898.154839736613</v>
       </c>
       <c r="I37" s="20">
         <f t="shared" si="2"/>
@@ -4821,7 +4829,7 @@
       </c>
       <c r="J37" s="20">
         <f t="shared" si="3"/>
-        <v>50546.363800921536</v>
+        <v>50547.197074166885</v>
       </c>
       <c r="K37" s="20">
         <f t="shared" si="4"/>
@@ -4837,7 +4845,7 @@
       </c>
       <c r="N37" s="20">
         <f>SUM(J37:$J$87)</f>
-        <v>722457.15373595979</v>
+        <v>722541.30221349478</v>
       </c>
       <c r="O37" s="22">
         <f>IF(I37&lt;=0,0,(IF(A37&lt;$B$4,SUMPRODUCT(L37:$L$86,K37:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A37,$B$5)+1)-$M$87)-IF(A37&lt;=$B$5,$E$13*(N37-INDEX($N$16:$N$87,$B$5+1)),0))/I37)</f>
@@ -4885,7 +4893,7 @@
       </c>
       <c r="H38" s="20">
         <f t="shared" si="9"/>
-        <v>83435.127346083565</v>
+        <v>83436.721217583734</v>
       </c>
       <c r="I38" s="20">
         <f t="shared" si="2"/>
@@ -4893,7 +4901,7 @@
       </c>
       <c r="J38" s="20">
         <f t="shared" si="3"/>
-        <v>48464.517628117574</v>
+        <v>48465.443451758932</v>
       </c>
       <c r="K38" s="20">
         <f t="shared" si="4"/>
@@ -4909,7 +4917,7 @@
       </c>
       <c r="N38" s="20">
         <f>SUM(J38:$J$87)</f>
-        <v>671910.78993503819</v>
+        <v>671994.10513932793</v>
       </c>
       <c r="O38" s="22">
         <f>IF(I38&lt;=0,0,(IF(A38&lt;$B$4,SUMPRODUCT(L38:$L$86,K38:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A38,$B$5)+1)-$M$87)-IF(A38&lt;=$B$5,$E$13*(N38-INDEX($N$16:$N$87,$B$5+1)),0))/I38)</f>
@@ -4957,7 +4965,7 @@
       </c>
       <c r="H39" s="20">
         <f t="shared" si="9"/>
-        <v>81867.528481342306</v>
+        <v>81869.331364767611</v>
       </c>
       <c r="I39" s="20">
         <f t="shared" si="2"/>
@@ -4965,7 +4973,7 @@
       </c>
       <c r="J39" s="20">
         <f t="shared" si="3"/>
-        <v>46394.102275549994</v>
+        <v>46395.123964607621</v>
       </c>
       <c r="K39" s="20">
         <f t="shared" si="4"/>
@@ -4981,7 +4989,7 @@
       </c>
       <c r="N39" s="20">
         <f>SUM(J39:$J$87)</f>
-        <v>623446.27230692049</v>
+        <v>623528.66168756888</v>
       </c>
       <c r="O39" s="22">
         <f>IF(I39&lt;=0,0,(IF(A39&lt;$B$4,SUMPRODUCT(L39:$L$86,K39:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A39,$B$5)+1)-$M$87)-IF(A39&lt;=$B$5,$E$13*(N39-INDEX($N$16:$N$87,$B$5+1)),0))/I39)</f>
@@ -5029,7 +5037,7 @@
       </c>
       <c r="H40" s="20">
         <f t="shared" si="9"/>
-        <v>80193.108498271424</v>
+        <v>80195.137144922948</v>
       </c>
       <c r="I40" s="20">
         <f t="shared" si="2"/>
@@ -5037,7 +5045,7 @@
       </c>
       <c r="J40" s="20">
         <f t="shared" si="3"/>
-        <v>44336.793264219006</v>
+        <v>44337.914852954986</v>
       </c>
       <c r="K40" s="20">
         <f t="shared" si="4"/>
@@ -5053,7 +5061,7 @@
       </c>
       <c r="N40" s="20">
         <f>SUM(J40:$J$87)</f>
-        <v>577052.17003137071</v>
+        <v>577133.53772296128</v>
       </c>
       <c r="O40" s="22">
         <f>IF(I40&lt;=0,0,(IF(A40&lt;$B$4,SUMPRODUCT(L40:$L$86,K40:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A40,$B$5)+1)-$M$87)-IF(A40&lt;=$B$5,$E$13*(N40-INDEX($N$16:$N$87,$B$5+1)),0))/I40)</f>
@@ -5101,7 +5109,7 @@
       </c>
       <c r="H41" s="20">
         <f t="shared" si="9"/>
-        <v>78411.615307435437</v>
+        <v>78413.891092198639</v>
       </c>
       <c r="I41" s="20">
         <f t="shared" si="2"/>
@@ -5109,7 +5117,7 @@
       </c>
       <c r="J41" s="20">
         <f t="shared" si="3"/>
-        <v>42294.487400347796</v>
+        <v>42295.714937232675</v>
       </c>
       <c r="K41" s="20">
         <f t="shared" si="4"/>
@@ -5125,7 +5133,7 @@
       </c>
       <c r="N41" s="20">
         <f>SUM(J41:$J$87)</f>
-        <v>532715.37676715176</v>
+        <v>532795.62287000613</v>
       </c>
       <c r="O41" s="22">
         <f>IF(I41&lt;=0,0,(IF(A41&lt;$B$4,SUMPRODUCT(L41:$L$86,K41:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A41,$B$5)+1)-$M$87)-IF(A41&lt;=$B$5,$E$13*(N41-INDEX($N$16:$N$87,$B$5+1)),0))/I41)</f>
@@ -5173,7 +5181,7 @@
       </c>
       <c r="H42" s="20">
         <f t="shared" si="9"/>
-        <v>76521.534330309252</v>
+        <v>76524.084065295217</v>
       </c>
       <c r="I42" s="20">
         <f t="shared" si="2"/>
@@ -5181,7 +5189,7 @@
       </c>
       <c r="J42" s="20">
         <f t="shared" si="3"/>
-        <v>40268.28830047691</v>
+        <v>40269.630059556926</v>
       </c>
       <c r="K42" s="20">
         <f t="shared" si="4"/>
@@ -5197,7 +5205,7 @@
       </c>
       <c r="N42" s="20">
         <f>SUM(J42:$J$87)</f>
-        <v>490420.88936680381</v>
+        <v>490499.90793277329</v>
       </c>
       <c r="O42" s="22">
         <f>IF(I42&lt;=0,0,(IF(A42&lt;$B$4,SUMPRODUCT(L42:$L$86,K42:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A42,$B$5)+1)-$M$87)-IF(A42&lt;=$B$5,$E$13*(N42-INDEX($N$16:$N$87,$B$5+1)),0))/I42)</f>
@@ -5245,7 +5253,7 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="9"/>
-        <v>74516.313655742357</v>
+        <v>74519.171068280775</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="2"/>
@@ -5253,7 +5261,7 @@
       </c>
       <c r="J43" s="20">
         <f t="shared" si="3"/>
-        <v>38256.655177973415</v>
+        <v>38258.122172794014</v>
       </c>
       <c r="K43" s="20">
         <f t="shared" si="4"/>
@@ -5269,7 +5277,7 @@
       </c>
       <c r="N43" s="20">
         <f>SUM(J43:$J$87)</f>
-        <v>450152.6010663269</v>
+        <v>450230.27787321631</v>
       </c>
       <c r="O43" s="22">
         <f>IF(I43&lt;=0,0,(IF(A43&lt;$B$4,SUMPRODUCT(L43:$L$86,K43:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A43,$B$5)+1)-$M$87)-IF(A43&lt;=$B$5,$E$13*(N43-INDEX($N$16:$N$87,$B$5+1)),0))/I43)</f>
@@ -5317,7 +5325,7 @@
       </c>
       <c r="H44" s="20">
         <f t="shared" si="9"/>
-        <v>72383.801745158213</v>
+        <v>72387.00443097479</v>
       </c>
       <c r="I44" s="20">
         <f t="shared" si="2"/>
@@ -5325,7 +5333,7 @@
       </c>
       <c r="J44" s="20">
         <f t="shared" si="3"/>
-        <v>36255.438187978216</v>
+        <v>36257.042342151646</v>
       </c>
       <c r="K44" s="20">
         <f t="shared" si="4"/>
@@ -5341,7 +5349,7 @@
       </c>
       <c r="N44" s="20">
         <f>SUM(J44:$J$87)</f>
-        <v>411895.94588835351</v>
+        <v>411972.1557004223</v>
       </c>
       <c r="O44" s="22">
         <f>IF(I44&lt;=0,0,(IF(A44&lt;$B$4,SUMPRODUCT(L44:$L$86,K44:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A44,$B$5)+1)-$M$87)-IF(A44&lt;=$B$5,$E$13*(N44-INDEX($N$16:$N$87,$B$5+1)),0))/I44)</f>
@@ -5389,7 +5397,7 @@
       </c>
       <c r="H45" s="20">
         <f t="shared" si="9"/>
-        <v>70111.400350264041</v>
+        <v>70114.988799704923</v>
       </c>
       <c r="I45" s="20">
         <f t="shared" si="2"/>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="J45" s="20">
         <f t="shared" si="3"/>
-        <v>34260.724696402518</v>
+        <v>34262.478232600151</v>
       </c>
       <c r="K45" s="20">
         <f t="shared" si="4"/>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="N45" s="20">
         <f>SUM(J45:$J$87)</f>
-        <v>375640.50770037534</v>
+        <v>375715.11335827078</v>
       </c>
       <c r="O45" s="22">
         <f>IF(I45&lt;=0,0,(IF(A45&lt;$B$4,SUMPRODUCT(L45:$L$86,K45:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A45,$B$5)+1)-$M$87)-IF(A45&lt;=$B$5,$E$13*(N45-INDEX($N$16:$N$87,$B$5+1)),0))/I45)</f>
@@ -5461,7 +5469,7 @@
       </c>
       <c r="H46" s="20">
         <f t="shared" si="9"/>
-        <v>67694.055738688883</v>
+        <v>67698.068647821274</v>
       </c>
       <c r="I46" s="20">
         <f t="shared" si="2"/>
@@ -5469,7 +5477,7 @@
       </c>
       <c r="J46" s="20">
         <f t="shared" si="3"/>
-        <v>32272.645903652861</v>
+        <v>32274.559028728025</v>
       </c>
       <c r="K46" s="20">
         <f t="shared" si="4"/>
@@ -5485,7 +5493,7 @@
       </c>
       <c r="N46" s="20">
         <f>SUM(J46:$J$87)</f>
-        <v>341379.78300397284</v>
+        <v>341452.63512567064</v>
       </c>
       <c r="O46" s="22">
         <f>IF(I46&lt;=0,0,(IF(A46&lt;$B$4,SUMPRODUCT(L46:$L$86,K46:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A46,$B$5)+1)-$M$87)-IF(A46&lt;=$B$5,$E$13*(N46-INDEX($N$16:$N$87,$B$5+1)),0))/I46)</f>
@@ -5533,7 +5541,7 @@
       </c>
       <c r="H47" s="20">
         <f t="shared" si="9"/>
-        <v>65132.228604667049</v>
+        <v>65136.774487252987</v>
       </c>
       <c r="I47" s="20">
         <f t="shared" si="2"/>
@@ -5541,7 +5549,7 @@
       </c>
       <c r="J47" s="20">
         <f t="shared" si="3"/>
-        <v>30293.964445668124</v>
+        <v>30296.078803005232</v>
       </c>
       <c r="K47" s="20">
         <f t="shared" si="4"/>
@@ -5557,7 +5565,7 @@
       </c>
       <c r="N47" s="20">
         <f>SUM(J47:$J$87)</f>
-        <v>309107.13710032002</v>
+        <v>309178.07609694265</v>
       </c>
       <c r="O47" s="22">
         <f>IF(I47&lt;=0,0,(IF(A47&lt;$B$4,SUMPRODUCT(L47:$L$86,K47:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A47,$B$5)+1)-$M$87)-IF(A47&lt;=$B$5,$E$13*(N47-INDEX($N$16:$N$87,$B$5+1)),0))/I47)</f>
@@ -5605,7 +5613,7 @@
       </c>
       <c r="H48" s="20">
         <f t="shared" si="9"/>
-        <v>62454.268463173357</v>
+        <v>62459.374879814619</v>
       </c>
       <c r="I48" s="20">
         <f t="shared" ref="I48:I79" si="12">G48*현가율^A48</f>
@@ -5613,7 +5621,7 @@
       </c>
       <c r="J48" s="20">
         <f t="shared" ref="J48:J79" si="13">H48*현가율^A48</f>
-        <v>28339.907815011546</v>
+        <v>28342.224956504666</v>
       </c>
       <c r="K48" s="20">
         <f t="shared" ref="K48:K79" si="14">G48*F48*현가율^(A48+0.5)</f>
@@ -5629,7 +5637,7 @@
       </c>
       <c r="N48" s="20">
         <f>SUM(J48:$J$87)</f>
-        <v>278813.17265465175</v>
+        <v>278881.99729393743</v>
       </c>
       <c r="O48" s="22">
         <f>IF(I48&lt;=0,0,(IF(A48&lt;$B$4,SUMPRODUCT(L48:$L$86,K48:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A48,$B$5)+1)-$M$87)-IF(A48&lt;=$B$5,$E$13*(N48-INDEX($N$16:$N$87,$B$5+1)),0))/I48)</f>
@@ -5676,8 +5684,8 @@
         <v>79462.976791145498</v>
       </c>
       <c r="H49" s="20">
-        <f t="shared" ref="H49:H80" si="19">H48*MAX(0,1-F48-E48+F48*E48/2)</f>
-        <v>59689.240784556823</v>
+        <f t="shared" ref="H49:H80" si="19">H48*MAX(0,1-MIN(1,C48+(1-(1-D48)*(1-E48))-C48*(1-(1-D48)*(1-E48))/2))</f>
+        <v>59694.928896422469</v>
       </c>
       <c r="I49" s="20">
         <f t="shared" si="12"/>
@@ -5685,7 +5693,7 @@
       </c>
       <c r="J49" s="20">
         <f t="shared" si="13"/>
-        <v>26424.60456747235</v>
+        <v>26427.122711526616</v>
       </c>
       <c r="K49" s="20">
         <f t="shared" si="14"/>
@@ -5701,7 +5709,7 @@
       </c>
       <c r="N49" s="20">
         <f>SUM(J49:$J$87)</f>
-        <v>250473.26483964027</v>
+        <v>250539.77233743292</v>
       </c>
       <c r="O49" s="22">
         <f>IF(I49&lt;=0,0,(IF(A49&lt;$B$4,SUMPRODUCT(L49:$L$86,K49:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A49,$B$5)+1)-$M$87)-IF(A49&lt;=$B$5,$E$13*(N49-INDEX($N$16:$N$87,$B$5+1)),0))/I49)</f>
@@ -5749,7 +5757,7 @@
       </c>
       <c r="H50" s="20">
         <f t="shared" si="19"/>
-        <v>56870.482298730065</v>
+        <v>56876.764475438387</v>
       </c>
       <c r="I50" s="20">
         <f t="shared" si="12"/>
@@ -5757,7 +5765,7 @@
       </c>
       <c r="J50" s="20">
         <f t="shared" si="13"/>
-        <v>24562.665166269071</v>
+        <v>24565.378471955337</v>
       </c>
       <c r="K50" s="20">
         <f t="shared" si="14"/>
@@ -5773,7 +5781,7 @@
       </c>
       <c r="N50" s="20">
         <f>SUM(J50:$J$87)</f>
-        <v>224048.66027216785</v>
+        <v>224112.64962590628</v>
       </c>
       <c r="O50" s="22">
         <f>IF(I50&lt;=0,0,(IF(A50&lt;$B$4,SUMPRODUCT(L50:$L$86,K50:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A50,$B$5)+1)-$M$87)-IF(A50&lt;=$B$5,$E$13*(N50-INDEX($N$16:$N$87,$B$5+1)),0))/I50)</f>
@@ -5821,7 +5829,7 @@
       </c>
       <c r="H51" s="20">
         <f t="shared" si="19"/>
-        <v>54026.845845416603</v>
+        <v>54033.723560711835</v>
       </c>
       <c r="I51" s="20">
         <f t="shared" si="12"/>
@@ -5829,7 +5837,7 @@
       </c>
       <c r="J51" s="20">
         <f t="shared" si="13"/>
-        <v>22765.349647229643</v>
+        <v>22768.247717457878</v>
       </c>
       <c r="K51" s="20">
         <f t="shared" si="14"/>
@@ -5845,7 +5853,7 @@
       </c>
       <c r="N51" s="20">
         <f>SUM(J51:$J$87)</f>
-        <v>199485.99510589879</v>
+        <v>199547.27115395095</v>
       </c>
       <c r="O51" s="22">
         <f>IF(I51&lt;=0,0,(IF(A51&lt;$B$4,SUMPRODUCT(L51:$L$86,K51:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A51,$B$5)+1)-$M$87)-IF(A51&lt;=$B$5,$E$13*(N51-INDEX($N$16:$N$87,$B$5+1)),0))/I51)</f>
@@ -5893,7 +5901,7 @@
       </c>
       <c r="H52" s="20">
         <f t="shared" si="19"/>
-        <v>51170.458866533772</v>
+        <v>51177.922691144784</v>
       </c>
       <c r="I52" s="20">
         <f t="shared" si="12"/>
@@ -5901,7 +5909,7 @@
       </c>
       <c r="J52" s="20">
         <f t="shared" si="13"/>
-        <v>21035.854458471549</v>
+        <v>21038.922789920955</v>
       </c>
       <c r="K52" s="20">
         <f t="shared" si="14"/>
@@ -5917,7 +5925,7 @@
       </c>
       <c r="N52" s="20">
         <f>SUM(J52:$J$87)</f>
-        <v>176720.64545866914</v>
+        <v>176779.02343649304</v>
       </c>
       <c r="O52" s="22">
         <f>IF(I52&lt;=0,0,(IF(A52&lt;$B$4,SUMPRODUCT(L52:$L$86,K52:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A52,$B$5)+1)-$M$87)-IF(A52&lt;=$B$5,$E$13*(N52-INDEX($N$16:$N$87,$B$5+1)),0))/I52)</f>
@@ -5965,7 +5973,7 @@
       </c>
       <c r="H53" s="20">
         <f t="shared" si="19"/>
-        <v>48292.480571559441</v>
+        <v>48300.506219126815</v>
       </c>
       <c r="I53" s="20">
         <f t="shared" si="12"/>
@@ -5973,7 +5981,7 @@
       </c>
       <c r="J53" s="20">
         <f t="shared" si="13"/>
-        <v>19368.52258108358</v>
+        <v>19371.741403854674</v>
       </c>
       <c r="K53" s="20">
         <f t="shared" si="14"/>
@@ -5989,7 +5997,7 @@
       </c>
       <c r="N53" s="20">
         <f>SUM(J53:$J$87)</f>
-        <v>155684.79100019761</v>
+        <v>155740.10064657207</v>
       </c>
       <c r="O53" s="22">
         <f>IF(I53&lt;=0,0,(IF(A53&lt;$B$4,SUMPRODUCT(L53:$L$86,K53:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A53,$B$5)+1)-$M$87)-IF(A53&lt;=$B$5,$E$13*(N53-INDEX($N$16:$N$87,$B$5+1)),0))/I53)</f>
@@ -6037,7 +6045,7 @@
       </c>
       <c r="H54" s="20">
         <f t="shared" si="19"/>
-        <v>45371.721691841951</v>
+        <v>45380.270996650659</v>
       </c>
       <c r="I54" s="20">
         <f t="shared" si="12"/>
@@ -6045,7 +6053,7 @@
       </c>
       <c r="J54" s="20">
         <f t="shared" si="13"/>
-        <v>17753.270674962732</v>
+        <v>17756.615889045253</v>
       </c>
       <c r="K54" s="20">
         <f t="shared" si="14"/>
@@ -6061,7 +6069,7 @@
       </c>
       <c r="N54" s="20">
         <f>SUM(J54:$J$87)</f>
-        <v>136316.26841911406</v>
+        <v>136368.35924271739</v>
       </c>
       <c r="O54" s="22">
         <f>IF(I54&lt;=0,0,(IF(A54&lt;$B$4,SUMPRODUCT(L54:$L$86,K54:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A54,$B$5)+1)-$M$87)-IF(A54&lt;=$B$5,$E$13*(N54-INDEX($N$16:$N$87,$B$5+1)),0))/I54)</f>
@@ -6109,7 +6117,7 @@
       </c>
       <c r="H55" s="20">
         <f t="shared" si="19"/>
-        <v>42391.945145259589</v>
+        <v>42400.965021732503</v>
       </c>
       <c r="I55" s="20">
         <f t="shared" si="12"/>
@@ -6117,7 +6125,7 @@
       </c>
       <c r="J55" s="20">
         <f t="shared" si="13"/>
-        <v>16182.760034467516</v>
+        <v>16186.203294643512</v>
       </c>
       <c r="K55" s="20">
         <f t="shared" si="14"/>
@@ -6133,7 +6141,7 @@
       </c>
       <c r="N55" s="20">
         <f>SUM(J55:$J$87)</f>
-        <v>118562.99774415129</v>
+        <v>118611.74335367217</v>
       </c>
       <c r="O55" s="22">
         <f>IF(I55&lt;=0,0,(IF(A55&lt;$B$4,SUMPRODUCT(L55:$L$86,K55:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A55,$B$5)+1)-$M$87)-IF(A55&lt;=$B$5,$E$13*(N55-INDEX($N$16:$N$87,$B$5+1)),0))/I55)</f>
@@ -6181,7 +6189,7 @@
       </c>
       <c r="H56" s="20">
         <f t="shared" si="19"/>
-        <v>39353.841126284417</v>
+        <v>39363.264775186391</v>
       </c>
       <c r="I56" s="20">
         <f t="shared" si="12"/>
@@ -6189,7 +6197,7 @@
       </c>
       <c r="J56" s="20">
         <f t="shared" si="13"/>
-        <v>14656.575595566475</v>
+        <v>14660.085251004548</v>
       </c>
       <c r="K56" s="20">
         <f t="shared" si="14"/>
@@ -6205,7 +6213,7 @@
       </c>
       <c r="N56" s="20">
         <f>SUM(J56:$J$87)</f>
-        <v>102380.23770968377</v>
+        <v>102425.54005902864</v>
       </c>
       <c r="O56" s="22">
         <f>IF(I56&lt;=0,0,(IF(A56&lt;$B$4,SUMPRODUCT(L56:$L$86,K56:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A56,$B$5)+1)-$M$87)-IF(A56&lt;=$B$5,$E$13*(N56-INDEX($N$16:$N$87,$B$5+1)),0))/I56)</f>
@@ -6253,7 +6261,7 @@
       </c>
       <c r="H57" s="20">
         <f t="shared" si="19"/>
-        <v>36273.993303760551</v>
+        <v>36283.743676059945</v>
       </c>
       <c r="I57" s="20">
         <f t="shared" si="12"/>
@@ -6261,7 +6269,7 @@
       </c>
       <c r="J57" s="20">
         <f t="shared" si="13"/>
-        <v>13180.044829394716</v>
+        <v>13183.587597430569</v>
       </c>
       <c r="K57" s="20">
         <f t="shared" si="14"/>
@@ -6277,7 +6285,7 @@
       </c>
       <c r="N57" s="20">
         <f>SUM(J57:$J$87)</f>
-        <v>87723.662114117295</v>
+        <v>87765.454808024122</v>
       </c>
       <c r="O57" s="22">
         <f>IF(I57&lt;=0,0,(IF(A57&lt;$B$4,SUMPRODUCT(L57:$L$86,K57:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A57,$B$5)+1)-$M$87)-IF(A57&lt;=$B$5,$E$13*(N57-INDEX($N$16:$N$87,$B$5+1)),0))/I57)</f>
@@ -6325,7 +6333,7 @@
       </c>
       <c r="H58" s="20">
         <f t="shared" si="19"/>
-        <v>33180.32377240347</v>
+        <v>33190.289423591792</v>
       </c>
       <c r="I58" s="20">
         <f t="shared" si="12"/>
@@ -6333,7 +6341,7 @@
       </c>
       <c r="J58" s="20">
         <f t="shared" si="13"/>
-        <v>11761.921405878755</v>
+        <v>11765.454078038299</v>
       </c>
       <c r="K58" s="20">
         <f t="shared" si="14"/>
@@ -6349,7 +6357,7 @@
       </c>
       <c r="N58" s="20">
         <f>SUM(J58:$J$87)</f>
-        <v>74543.617284722568</v>
+        <v>74581.867210593555</v>
       </c>
       <c r="O58" s="22">
         <f>IF(I58&lt;=0,0,(IF(A58&lt;$B$4,SUMPRODUCT(L58:$L$86,K58:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A58,$B$5)+1)-$M$87)-IF(A58&lt;=$B$5,$E$13*(N58-INDEX($N$16:$N$87,$B$5+1)),0))/I58)</f>
@@ -6397,7 +6405,7 @@
       </c>
       <c r="H59" s="20">
         <f t="shared" si="19"/>
-        <v>30102.780640637764</v>
+        <v>30112.833348394222</v>
       </c>
       <c r="I59" s="20">
         <f t="shared" si="12"/>
@@ -6405,7 +6413,7 @@
       </c>
       <c r="J59" s="20">
         <f t="shared" si="13"/>
-        <v>10410.711272587192</v>
+        <v>10414.187889555224</v>
       </c>
       <c r="K59" s="20">
         <f t="shared" si="14"/>
@@ -6421,7 +6429,7 @@
       </c>
       <c r="N59" s="20">
         <f>SUM(J59:$J$87)</f>
-        <v>62781.695878843835</v>
+        <v>62816.413132555201</v>
       </c>
       <c r="O59" s="22">
         <f>IF(I59&lt;=0,0,(IF(A59&lt;$B$4,SUMPRODUCT(L59:$L$86,K59:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A59,$B$5)+1)-$M$87)-IF(A59&lt;=$B$5,$E$13*(N59-INDEX($N$16:$N$87,$B$5+1)),0))/I59)</f>
@@ -6469,7 +6477,7 @@
       </c>
       <c r="H60" s="20">
         <f t="shared" si="19"/>
-        <v>27072.543057345596</v>
+        <v>27082.55348176237</v>
       </c>
       <c r="I60" s="20">
         <f t="shared" si="12"/>
@@ -6477,7 +6485,7 @@
       </c>
       <c r="J60" s="20">
         <f t="shared" si="13"/>
-        <v>9134.3779199968812</v>
+        <v>9137.7554748711573</v>
       </c>
       <c r="K60" s="20">
         <f t="shared" si="14"/>
@@ -6493,7 +6501,7 @@
       </c>
       <c r="N60" s="20">
         <f>SUM(J60:$J$87)</f>
-        <v>52370.984606256636</v>
+        <v>52402.225242999972</v>
       </c>
       <c r="O60" s="22">
         <f>IF(I60&lt;=0,0,(IF(A60&lt;$B$4,SUMPRODUCT(L60:$L$86,K60:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A60,$B$5)+1)-$M$87)-IF(A60&lt;=$B$5,$E$13*(N60-INDEX($N$16:$N$87,$B$5+1)),0))/I60)</f>
@@ -6541,7 +6549,7 @@
       </c>
       <c r="H61" s="20">
         <f t="shared" si="19"/>
-        <v>24120.574148074706</v>
+        <v>24130.428710068707</v>
       </c>
       <c r="I61" s="20">
         <f t="shared" si="12"/>
@@ -6549,7 +6557,7 @@
       </c>
       <c r="J61" s="20">
         <f t="shared" si="13"/>
-        <v>7939.8756094985729</v>
+        <v>7943.1194790656127</v>
       </c>
       <c r="K61" s="20">
         <f t="shared" si="14"/>
@@ -6565,7 +6573,7 @@
       </c>
       <c r="N61" s="20">
         <f>SUM(J61:$J$87)</f>
-        <v>43236.606686259765</v>
+        <v>43264.469768128816</v>
       </c>
       <c r="O61" s="22">
         <f>IF(I61&lt;=0,0,(IF(A61&lt;$B$4,SUMPRODUCT(L61:$L$86,K61:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A61,$B$5)+1)-$M$87)-IF(A61&lt;=$B$5,$E$13*(N61-INDEX($N$16:$N$87,$B$5+1)),0))/I61)</f>
@@ -6613,7 +6621,7 @@
       </c>
       <c r="H62" s="20">
         <f t="shared" si="19"/>
-        <v>21275.294551224841</v>
+        <v>21284.903183483471</v>
       </c>
       <c r="I62" s="20">
         <f t="shared" si="12"/>
@@ -6621,7 +6629,7 @@
       </c>
       <c r="J62" s="20">
         <f t="shared" si="13"/>
-        <v>6832.4706294165044</v>
+        <v>6835.5564009219424</v>
       </c>
       <c r="K62" s="20">
         <f t="shared" si="14"/>
@@ -6637,7 +6645,7 @@
       </c>
       <c r="N62" s="20">
         <f>SUM(J62:$J$87)</f>
-        <v>35296.731076761193</v>
+        <v>35321.350289063201</v>
       </c>
       <c r="O62" s="22">
         <f>IF(I62&lt;=0,0,(IF(A62&lt;$B$4,SUMPRODUCT(L62:$L$86,K62:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A62,$B$5)+1)-$M$87)-IF(A62&lt;=$B$5,$E$13*(N62-INDEX($N$16:$N$87,$B$5+1)),0))/I62)</f>
@@ -6685,7 +6693,7 @@
       </c>
       <c r="H63" s="20">
         <f t="shared" si="19"/>
-        <v>18559.627877874111</v>
+        <v>18568.917481172331</v>
       </c>
       <c r="I63" s="20">
         <f t="shared" si="12"/>
@@ -6693,7 +6701,7 @@
       </c>
       <c r="J63" s="20">
         <f t="shared" si="13"/>
-        <v>5814.9715051478452</v>
+        <v>5817.8820580333195</v>
       </c>
       <c r="K63" s="20">
         <f t="shared" si="14"/>
@@ -6709,7 +6717,7 @@
       </c>
       <c r="N63" s="20">
         <f>SUM(J63:$J$87)</f>
-        <v>28464.260447344688</v>
+        <v>28485.793888141281</v>
       </c>
       <c r="O63" s="22">
         <f>IF(I63&lt;=0,0,(IF(A63&lt;$B$4,SUMPRODUCT(L63:$L$86,K63:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A63,$B$5)+1)-$M$87)-IF(A63&lt;=$B$5,$E$13*(N63-INDEX($N$16:$N$87,$B$5+1)),0))/I63)</f>
@@ -6757,7 +6765,7 @@
       </c>
       <c r="H64" s="20">
         <f t="shared" si="19"/>
-        <v>15991.471660066438</v>
+        <v>16000.375905961821</v>
       </c>
       <c r="I64" s="20">
         <f t="shared" si="12"/>
@@ -6765,7 +6773,7 @@
       </c>
       <c r="J64" s="20">
         <f t="shared" si="13"/>
-        <v>4888.1316487150389</v>
+        <v>4890.8534198624593</v>
       </c>
       <c r="K64" s="20">
         <f t="shared" si="14"/>
@@ -6781,7 +6789,7 @@
       </c>
       <c r="N64" s="20">
         <f>SUM(J64:$J$87)</f>
-        <v>22649.288942196843</v>
+        <v>22667.911830107962</v>
       </c>
       <c r="O64" s="22">
         <f>IF(I64&lt;=0,0,(IF(A64&lt;$B$4,SUMPRODUCT(L64:$L$86,K64:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A64,$B$5)+1)-$M$87)-IF(A64&lt;=$B$5,$E$13*(N64-INDEX($N$16:$N$87,$B$5+1)),0))/I64)</f>
@@ -6829,7 +6837,7 @@
       </c>
       <c r="H65" s="20">
         <f t="shared" si="19"/>
-        <v>13591.247894568613</v>
+        <v>13599.698161199945</v>
       </c>
       <c r="I65" s="20">
         <f t="shared" si="12"/>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="J65" s="20">
         <f t="shared" si="13"/>
-        <v>4053.1243635302922</v>
+        <v>4055.644366242881</v>
       </c>
       <c r="K65" s="20">
         <f t="shared" si="14"/>
@@ -6853,7 +6861,7 @@
       </c>
       <c r="N65" s="20">
         <f>SUM(J65:$J$87)</f>
-        <v>17761.1572934818</v>
+        <v>17777.0584102455</v>
       </c>
       <c r="O65" s="22">
         <f>IF(I65&lt;=0,0,(IF(A65&lt;$B$4,SUMPRODUCT(L65:$L$86,K65:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A65,$B$5)+1)-$M$87)-IF(A65&lt;=$B$5,$E$13*(N65-INDEX($N$16:$N$87,$B$5+1)),0))/I65)</f>
@@ -6901,7 +6909,7 @@
       </c>
       <c r="H66" s="20">
         <f t="shared" si="19"/>
-        <v>11380.084993883993</v>
+        <v>11388.007884736648</v>
       </c>
       <c r="I66" s="20">
         <f t="shared" si="12"/>
@@ -6909,7 +6917,7 @@
       </c>
       <c r="J66" s="20">
         <f t="shared" si="13"/>
-        <v>3310.9470551939821</v>
+        <v>3313.2521585522891</v>
       </c>
       <c r="K66" s="20">
         <f t="shared" si="14"/>
@@ -6925,7 +6933,7 @@
       </c>
       <c r="N66" s="20">
         <f>SUM(J66:$J$87)</f>
-        <v>13708.032929951503</v>
+        <v>13721.414044002624</v>
       </c>
       <c r="O66" s="22">
         <f>IF(I66&lt;=0,0,(IF(A66&lt;$B$4,SUMPRODUCT(L66:$L$86,K66:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A66,$B$5)+1)-$M$87)-IF(A66&lt;=$B$5,$E$13*(N66-INDEX($N$16:$N$87,$B$5+1)),0))/I66)</f>
@@ -6973,7 +6981,7 @@
       </c>
       <c r="H67" s="20">
         <f t="shared" si="19"/>
-        <v>9375.0337460902974</v>
+        <v>9382.3555477063892</v>
       </c>
       <c r="I67" s="20">
         <f t="shared" si="12"/>
@@ -6981,7 +6989,7 @@
       </c>
       <c r="J67" s="20">
         <f t="shared" si="13"/>
-        <v>2661.0663590584531</v>
+        <v>2663.1446235741842</v>
       </c>
       <c r="K67" s="20">
         <f t="shared" si="14"/>
@@ -6997,7 +7005,7 @@
       </c>
       <c r="N67" s="20">
         <f>SUM(J67:$J$87)</f>
-        <v>10397.085874757522</v>
+        <v>10408.161885450334</v>
       </c>
       <c r="O67" s="22">
         <f>IF(I67&lt;=0,0,(IF(A67&lt;$B$4,SUMPRODUCT(L67:$L$86,K67:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A67,$B$5)+1)-$M$87)-IF(A67&lt;=$B$5,$E$13*(N67-INDEX($N$16:$N$87,$B$5+1)),0))/I67)</f>
@@ -7045,7 +7053,7 @@
       </c>
       <c r="H68" s="20">
         <f t="shared" si="19"/>
-        <v>7585.7092043962448</v>
+        <v>7592.3601157403746</v>
       </c>
       <c r="I68" s="20">
         <f t="shared" si="12"/>
@@ -7053,7 +7061,7 @@
       </c>
       <c r="J68" s="20">
         <f t="shared" si="13"/>
-        <v>2100.6572136300952</v>
+        <v>2102.4990038326728</v>
       </c>
       <c r="K68" s="20">
         <f t="shared" si="14"/>
@@ -7069,7 +7077,7 @@
       </c>
       <c r="N68" s="20">
         <f>SUM(J68:$J$87)</f>
-        <v>7736.0195156990712</v>
+        <v>7745.0172618761471</v>
       </c>
       <c r="O68" s="22">
         <f>IF(I68&lt;=0,0,(IF(A68&lt;$B$4,SUMPRODUCT(L68:$L$86,K68:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A68,$B$5)+1)-$M$87)-IF(A68&lt;=$B$5,$E$13*(N68-INDEX($N$16:$N$87,$B$5+1)),0))/I68)</f>
@@ -7117,7 +7125,7 @@
       </c>
       <c r="H69" s="20">
         <f t="shared" si="19"/>
-        <v>6014.5255214906001</v>
+        <v>6020.4438912789165</v>
       </c>
       <c r="I69" s="20">
         <f t="shared" si="12"/>
@@ -7125,7 +7133,7 @@
       </c>
       <c r="J69" s="20">
         <f t="shared" si="13"/>
-        <v>1624.9369198596942</v>
+        <v>1626.5358785040719</v>
       </c>
       <c r="K69" s="20">
         <f t="shared" si="14"/>
@@ -7141,7 +7149,7 @@
       </c>
       <c r="N69" s="20">
         <f>SUM(J69:$J$87)</f>
-        <v>5635.3623020689765</v>
+        <v>5642.5182580434739</v>
       </c>
       <c r="O69" s="22">
         <f>IF(I69&lt;=0,0,(IF(A69&lt;$B$4,SUMPRODUCT(L69:$L$86,K69:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A69,$B$5)+1)-$M$87)-IF(A69&lt;=$B$5,$E$13*(N69-INDEX($N$16:$N$87,$B$5+1)),0))/I69)</f>
@@ -7189,7 +7197,7 @@
       </c>
       <c r="H70" s="20">
         <f t="shared" si="19"/>
-        <v>4661.3091732299572</v>
+        <v>4666.4497133892928</v>
       </c>
       <c r="I70" s="20">
         <f t="shared" si="12"/>
@@ -7197,7 +7205,7 @@
       </c>
       <c r="J70" s="20">
         <f t="shared" si="13"/>
-        <v>1228.6245200480394</v>
+        <v>1229.9794599268021</v>
       </c>
       <c r="K70" s="20">
         <f t="shared" si="14"/>
@@ -7213,7 +7221,7 @@
       </c>
       <c r="N70" s="20">
         <f>SUM(J70:$J$87)</f>
-        <v>4010.4253822092828</v>
+        <v>4015.9823795394022</v>
       </c>
       <c r="O70" s="22">
         <f>IF(I70&lt;=0,0,(IF(A70&lt;$B$4,SUMPRODUCT(L70:$L$86,K70:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A70,$B$5)+1)-$M$87)-IF(A70&lt;=$B$5,$E$13*(N70-INDEX($N$16:$N$87,$B$5+1)),0))/I70)</f>
@@ -7261,7 +7269,7 @@
       </c>
       <c r="H71" s="20">
         <f t="shared" si="19"/>
-        <v>3522.6264470294886</v>
+        <v>3526.9695059966057</v>
       </c>
       <c r="I71" s="20">
         <f t="shared" si="12"/>
@@ -7269,7 +7277,7 @@
       </c>
       <c r="J71" s="20">
         <f t="shared" si="13"/>
-        <v>905.84521548746386</v>
+        <v>906.96203535045572</v>
       </c>
       <c r="K71" s="20">
         <f t="shared" si="14"/>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="N71" s="20">
         <f>SUM(J71:$J$87)</f>
-        <v>2781.8008621612435</v>
+        <v>2786.0029196126002</v>
       </c>
       <c r="O71" s="22">
         <f>IF(I71&lt;=0,0,(IF(A71&lt;$B$4,SUMPRODUCT(L71:$L$86,K71:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A71,$B$5)+1)-$M$87)-IF(A71&lt;=$B$5,$E$13*(N71-INDEX($N$16:$N$87,$B$5+1)),0))/I71)</f>
@@ -7333,7 +7341,7 @@
       </c>
       <c r="H72" s="20">
         <f t="shared" si="19"/>
-        <v>2589.5831459584606</v>
+        <v>2593.1408634687841</v>
       </c>
       <c r="I72" s="20">
         <f t="shared" si="12"/>
@@ -7341,7 +7349,7 @@
       </c>
       <c r="J72" s="20">
         <f t="shared" si="13"/>
-        <v>649.67087543763409</v>
+        <v>650.56343046259985</v>
       </c>
       <c r="K72" s="20">
         <f t="shared" si="14"/>
@@ -7357,7 +7365,7 @@
       </c>
       <c r="N72" s="20">
         <f>SUM(J72:$J$87)</f>
-        <v>1875.9556466737795</v>
+        <v>1879.0408842621448</v>
       </c>
       <c r="O72" s="22">
         <f>IF(I72&lt;=0,0,(IF(A72&lt;$B$4,SUMPRODUCT(L72:$L$86,K72:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A72,$B$5)+1)-$M$87)-IF(A72&lt;=$B$5,$E$13*(N72-INDEX($N$16:$N$87,$B$5+1)),0))/I72)</f>
@@ -7405,7 +7413,7 @@
       </c>
       <c r="H73" s="20">
         <f t="shared" si="19"/>
-        <v>1846.525154454624</v>
+        <v>1849.3416525733874</v>
       </c>
       <c r="I73" s="20">
         <f t="shared" si="12"/>
@@ -7413,7 +7421,7 @@
       </c>
       <c r="J73" s="20">
         <f t="shared" si="13"/>
-        <v>451.95469356107623</v>
+        <v>452.64405841544072</v>
       </c>
       <c r="K73" s="20">
         <f t="shared" si="14"/>
@@ -7429,7 +7437,7 @@
       </c>
       <c r="N73" s="20">
         <f>SUM(J73:$J$87)</f>
-        <v>1226.2847712361454</v>
+        <v>1228.4774537995449</v>
       </c>
       <c r="O73" s="22">
         <f>IF(I73&lt;=0,0,(IF(A73&lt;$B$4,SUMPRODUCT(L73:$L$86,K73:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A73,$B$5)+1)-$M$87)-IF(A73&lt;=$B$5,$E$13*(N73-INDEX($N$16:$N$87,$B$5+1)),0))/I73)</f>
@@ -7477,7 +7485,7 @@
       </c>
       <c r="H74" s="20">
         <f t="shared" si="19"/>
-        <v>1272.4031047782119</v>
+        <v>1274.5498212235077</v>
       </c>
       <c r="I74" s="20">
         <f t="shared" si="12"/>
@@ -7485,7 +7493,7 @@
       </c>
       <c r="J74" s="20">
         <f t="shared" si="13"/>
-        <v>303.83690773352214</v>
+        <v>304.34952176603275</v>
       </c>
       <c r="K74" s="20">
         <f t="shared" si="14"/>
@@ -7501,7 +7509,7 @@
       </c>
       <c r="N74" s="20">
         <f>SUM(J74:$J$87)</f>
-        <v>774.33007767506888</v>
+        <v>775.83339538410428</v>
       </c>
       <c r="O74" s="22">
         <f>IF(I74&lt;=0,0,(IF(A74&lt;$B$4,SUMPRODUCT(L74:$L$86,K74:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A74,$B$5)+1)-$M$87)-IF(A74&lt;=$B$5,$E$13*(N74-INDEX($N$16:$N$87,$B$5+1)),0))/I74)</f>
@@ -7549,7 +7557,7 @@
       </c>
       <c r="H75" s="20">
         <f t="shared" si="19"/>
-        <v>843.61379630252588</v>
+        <v>845.18287697126698</v>
       </c>
       <c r="I75" s="20">
         <f t="shared" si="12"/>
@@ -7557,7 +7565,7 @@
       </c>
       <c r="J75" s="20">
         <f t="shared" si="13"/>
-        <v>196.5330596633566</v>
+        <v>196.89860160451249</v>
       </c>
       <c r="K75" s="20">
         <f t="shared" si="14"/>
@@ -7573,7 +7581,7 @@
       </c>
       <c r="N75" s="20">
         <f>SUM(J75:$J$87)</f>
-        <v>470.4931699415468</v>
+        <v>471.48387361807136</v>
       </c>
       <c r="O75" s="22">
         <f>IF(I75&lt;=0,0,(IF(A75&lt;$B$4,SUMPRODUCT(L75:$L$86,K75:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A75,$B$5)+1)-$M$87)-IF(A75&lt;=$B$5,$E$13*(N75-INDEX($N$16:$N$87,$B$5+1)),0))/I75)</f>
@@ -7621,7 +7629,7 @@
       </c>
       <c r="H76" s="20">
         <f t="shared" si="19"/>
-        <v>535.6776897268395</v>
+        <v>536.77303953449939</v>
       </c>
       <c r="I76" s="20">
         <f t="shared" si="12"/>
@@ -7629,7 +7637,7 @@
       </c>
       <c r="J76" s="20">
         <f t="shared" si="13"/>
-        <v>121.75074726493705</v>
+        <v>121.9997022991986</v>
       </c>
       <c r="K76" s="20">
         <f t="shared" si="14"/>
@@ -7645,7 +7653,7 @@
       </c>
       <c r="N76" s="20">
         <f>SUM(J76:$J$87)</f>
-        <v>273.96011027819014</v>
+        <v>274.58527201355884</v>
       </c>
       <c r="O76" s="22">
         <f>IF(I76&lt;=0,0,(IF(A76&lt;$B$4,SUMPRODUCT(L76:$L$86,K76:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A76,$B$5)+1)-$M$87)-IF(A76&lt;=$B$5,$E$13*(N76-INDEX($N$16:$N$87,$B$5+1)),0))/I76)</f>
@@ -7693,7 +7701,7 @@
       </c>
       <c r="H77" s="20">
         <f t="shared" si="19"/>
-        <v>324.32300400875147</v>
+        <v>325.05053394422004</v>
       </c>
       <c r="I77" s="20">
         <f t="shared" si="12"/>
@@ -7701,7 +7709,7 @@
       </c>
       <c r="J77" s="20">
         <f t="shared" si="13"/>
-        <v>71.915410713210548</v>
+        <v>72.076733263472704</v>
       </c>
       <c r="K77" s="20">
         <f t="shared" si="14"/>
@@ -7717,7 +7725,7 @@
       </c>
       <c r="N77" s="20">
         <f>SUM(J77:$J$87)</f>
-        <v>152.20936301325315</v>
+        <v>152.58556971436019</v>
       </c>
       <c r="O77" s="22">
         <f>IF(I77&lt;=0,0,(IF(A77&lt;$B$4,SUMPRODUCT(L77:$L$86,K77:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A77,$B$5)+1)-$M$87)-IF(A77&lt;=$B$5,$E$13*(N77-INDEX($N$16:$N$87,$B$5+1)),0))/I77)</f>
@@ -7765,7 +7773,7 @@
       </c>
       <c r="H78" s="20">
         <f t="shared" si="19"/>
-        <v>186.37685929322805</v>
+        <v>186.83480988635745</v>
       </c>
       <c r="I78" s="20">
         <f t="shared" si="12"/>
@@ -7773,7 +7781,7 @@
       </c>
       <c r="J78" s="20">
         <f t="shared" si="13"/>
-        <v>40.31923976373205</v>
+        <v>40.418309035713278</v>
       </c>
       <c r="K78" s="20">
         <f t="shared" si="14"/>
@@ -7789,7 +7797,7 @@
       </c>
       <c r="N78" s="20">
         <f>SUM(J78:$J$87)</f>
-        <v>80.293952300042605</v>
+        <v>80.508836450887543</v>
       </c>
       <c r="O78" s="22">
         <f>IF(I78&lt;=0,0,(IF(A78&lt;$B$4,SUMPRODUCT(L78:$L$86,K78:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A78,$B$5)+1)-$M$87)-IF(A78&lt;=$B$5,$E$13*(N78-INDEX($N$16:$N$87,$B$5+1)),0))/I78)</f>
@@ -7837,7 +7845,7 @@
       </c>
       <c r="H79" s="20">
         <f t="shared" si="19"/>
-        <v>101.12374946863729</v>
+        <v>101.39562966227804</v>
       </c>
       <c r="I79" s="20">
         <f t="shared" si="12"/>
@@ -7845,7 +7853,7 @@
       </c>
       <c r="J79" s="20">
         <f t="shared" si="13"/>
-        <v>21.34271398124498</v>
+        <v>21.400095765845833</v>
       </c>
       <c r="K79" s="20">
         <f t="shared" si="14"/>
@@ -7861,7 +7869,7 @@
       </c>
       <c r="N79" s="20">
         <f>SUM(J79:$J$87)</f>
-        <v>39.974712536310548</v>
+        <v>40.090527415174236</v>
       </c>
       <c r="O79" s="22">
         <f>IF(I79&lt;=0,0,(IF(A79&lt;$B$4,SUMPRODUCT(L79:$L$86,K79:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A79,$B$5)+1)-$M$87)-IF(A79&lt;=$B$5,$E$13*(N79-INDEX($N$16:$N$87,$B$5+1)),0))/I79)</f>
@@ -7909,7 +7917,7 @@
       </c>
       <c r="H80" s="20">
         <f t="shared" si="19"/>
-        <v>51.730706237108087</v>
+        <v>51.882756527482393</v>
       </c>
       <c r="I80" s="20">
         <f t="shared" ref="I80:I87" si="22">G80*현가율^A80</f>
@@ -7917,7 +7925,7 @@
       </c>
       <c r="J80" s="20">
         <f t="shared" ref="J80:J87" si="23">H80*현가율^A80</f>
-        <v>10.651751412457104</v>
+        <v>10.683059740007003</v>
       </c>
       <c r="K80" s="20">
         <f t="shared" ref="K80:K87" si="24">G80*F80*현가율^(A80+0.5)</f>
@@ -7933,7 +7941,7 @@
       </c>
       <c r="N80" s="20">
         <f>SUM(J80:$J$87)</f>
-        <v>18.631998555065572</v>
+        <v>18.69043164932841</v>
       </c>
       <c r="O80" s="22">
         <f>IF(I80&lt;=0,0,(IF(A80&lt;$B$4,SUMPRODUCT(L80:$L$86,K80:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A80,$B$5)+1)-$M$87)-IF(A80&lt;=$B$5,$E$13*(N80-INDEX($N$16:$N$87,$B$5+1)),0))/I80)</f>
@@ -7980,8 +7988,8 @@
         <v>131.98243715991799</v>
       </c>
       <c r="H81" s="20">
-        <f t="shared" ref="H81:H87" si="29">H80*MAX(0,1-F80-E80+F80*E80/2)</f>
-        <v>24.904131162070119</v>
+        <f t="shared" ref="H81:H87" si="29">H80*MAX(0,1-MIN(1,C80+(1-(1-D80)*(1-E80))-C80*(1-(1-D80)*(1-E80))/2))</f>
+        <v>24.984220117836781</v>
       </c>
       <c r="I81" s="20">
         <f t="shared" si="22"/>
@@ -7989,7 +7997,7 @@
       </c>
       <c r="J81" s="20">
         <f t="shared" si="23"/>
-        <v>5.002880674630811</v>
+        <v>5.0189693904526518</v>
       </c>
       <c r="K81" s="20">
         <f t="shared" si="24"/>
@@ -8005,7 +8013,7 @@
       </c>
       <c r="N81" s="20">
         <f>SUM(J81:$J$87)</f>
-        <v>7.9802471426084676</v>
+        <v>8.0073719093214066</v>
       </c>
       <c r="O81" s="22">
         <f>IF(I81&lt;=0,0,(IF(A81&lt;$B$4,SUMPRODUCT(L81:$L$86,K81:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A81,$B$5)+1)-$M$87)-IF(A81&lt;=$B$5,$E$13*(N81-INDEX($N$16:$N$87,$B$5+1)),0))/I81)</f>
@@ -8053,7 +8061,7 @@
       </c>
       <c r="H82" s="20">
         <f t="shared" si="29"/>
-        <v>10.464751659753198</v>
+        <v>10.501774376493222</v>
       </c>
       <c r="I82" s="20">
         <f t="shared" si="22"/>
@@ -8061,7 +8069,7 @@
       </c>
       <c r="J82" s="20">
         <f t="shared" si="23"/>
-        <v>2.0509440392442566</v>
+        <v>2.0581999706493574</v>
       </c>
       <c r="K82" s="20">
         <f t="shared" si="24"/>
@@ -8077,7 +8085,7 @@
       </c>
       <c r="N82" s="20">
         <f>SUM(J82:$J$87)</f>
-        <v>2.9773664679776557</v>
+        <v>2.9884025188687566</v>
       </c>
       <c r="O82" s="22">
         <f>IF(I82&lt;=0,0,(IF(A82&lt;$B$4,SUMPRODUCT(L82:$L$86,K82:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A82,$B$5)+1)-$M$87)-IF(A82&lt;=$B$5,$E$13*(N82-INDEX($N$16:$N$87,$B$5+1)),0))/I82)</f>
@@ -8125,7 +8133,7 @@
       </c>
       <c r="H83" s="20">
         <f t="shared" si="29"/>
-        <v>3.6743276683555304</v>
+        <v>3.688754528113102</v>
       </c>
       <c r="I83" s="20">
         <f t="shared" si="22"/>
@@ -8133,7 +8141,7 @@
       </c>
       <c r="J83" s="20">
         <f t="shared" si="23"/>
-        <v>0.70255269141556842</v>
+        <v>0.70531119040264789</v>
       </c>
       <c r="K83" s="20">
         <f t="shared" si="24"/>
@@ -8149,7 +8157,7 @@
       </c>
       <c r="N83" s="20">
         <f>SUM(J83:$J$87)</f>
-        <v>0.92642242873339908</v>
+        <v>0.93020254821939918</v>
       </c>
       <c r="O83" s="22">
         <f>IF(I83&lt;=0,0,(IF(A83&lt;$B$4,SUMPRODUCT(L83:$L$86,K83:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A83,$B$5)+1)-$M$87)-IF(A83&lt;=$B$5,$E$13*(N83-INDEX($N$16:$N$87,$B$5+1)),0))/I83)</f>
@@ -8197,7 +8205,7 @@
       </c>
       <c r="H84" s="20">
         <f t="shared" si="29"/>
-        <v>1.0036258611309146</v>
+        <v>1.0080671835263939</v>
       </c>
       <c r="I84" s="20">
         <f t="shared" si="22"/>
@@ -8205,7 +8213,7 @@
       </c>
       <c r="J84" s="20">
         <f t="shared" si="23"/>
-        <v>0.18721860155349082</v>
+        <v>0.18804709571663733</v>
       </c>
       <c r="K84" s="20">
         <f t="shared" si="24"/>
@@ -8221,7 +8229,7 @@
       </c>
       <c r="N84" s="20">
         <f>SUM(J84:$J$87)</f>
-        <v>0.22386973731783072</v>
+        <v>0.22489135781675124</v>
       </c>
       <c r="O84" s="22">
         <f>IF(I84&lt;=0,0,(IF(A84&lt;$B$4,SUMPRODUCT(L84:$L$86,K84:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A84,$B$5)+1)-$M$87)-IF(A84&lt;=$B$5,$E$13*(N84-INDEX($N$16:$N$87,$B$5+1)),0))/I84)</f>
@@ -8269,7 +8277,7 @@
       </c>
       <c r="H85" s="20">
         <f t="shared" si="29"/>
-        <v>0.18582498140659595</v>
+        <v>0.18678228800061483</v>
       </c>
       <c r="I85" s="20">
         <f t="shared" si="22"/>
@@ -8277,7 +8285,7 @@
       </c>
       <c r="J85" s="20">
         <f t="shared" si="23"/>
-        <v>3.3818737128861333E-2</v>
+        <v>3.3992959667778273E-2</v>
       </c>
       <c r="K85" s="20">
         <f t="shared" si="24"/>
@@ -8293,7 +8301,7 @@
       </c>
       <c r="N85" s="20">
         <f>SUM(J85:$J$87)</f>
-        <v>3.6651135764339905E-2</v>
+        <v>3.6844262100113906E-2</v>
       </c>
       <c r="O85" s="22">
         <f>IF(I85&lt;=0,0,(IF(A85&lt;$B$4,SUMPRODUCT(L85:$L$86,K85:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A85,$B$5)+1)-$M$87)-IF(A85&lt;=$B$5,$E$13*(N85-INDEX($N$16:$N$87,$B$5+1)),0))/I85)</f>
@@ -8341,7 +8349,7 @@
       </c>
       <c r="H86" s="20">
         <f t="shared" si="29"/>
-        <v>1.5952360441863277E-2</v>
+        <v>1.6058828570115508E-2</v>
       </c>
       <c r="I86" s="20">
         <f t="shared" si="22"/>
@@ -8349,7 +8357,7 @@
       </c>
       <c r="J86" s="20">
         <f t="shared" si="23"/>
-        <v>2.8323986354785737E-3</v>
+        <v>2.8513024323356334E-3</v>
       </c>
       <c r="K86" s="20">
         <f t="shared" si="24"/>
@@ -8365,7 +8373,7 @@
       </c>
       <c r="N86" s="20">
         <f>SUM(J86:$J$87)</f>
-        <v>2.8323986354785737E-3</v>
+        <v>2.8513024323356334E-3</v>
       </c>
       <c r="O86" s="22">
         <f>IF(I86&lt;=0,0,(IF(A86&lt;$B$4,SUMPRODUCT(L86:$L$86,K86:$K$86),0)+베타후*(INDEX($M$16:$M$87,MAX(A86,$B$5)+1)-$M$87)-IF(A86&lt;=$B$5,$E$13*(N86-INDEX($N$16:$N$87,$B$5+1)),0))/I86)</f>
@@ -8463,7 +8471,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -8481,40 +8489,40 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="12">
         <v>50000000</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="15">
-        <f>SUMPRODUCT($L$16:$L$76,$K$16:$K$76)</f>
-        <v>21792.989151600847</v>
+        <f>SUMPRODUCT($L$16:$L$75,$K$16:$K$75)</f>
+        <v>21787.536743751647</v>
       </c>
       <c r="F2" s="16">
-        <v>21792.98915160085</v>
+        <v>21787.536743751651</v>
       </c>
       <c r="G2" s="17">
         <f>E2-F2</f>
@@ -8523,20 +8531,20 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="12">
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="15">
-        <f>납입주기*(($N$16-INDEX($N$16:$N$77,B5+1))-(납입주기-1)/(2*납입주기)*($J$16-INDEX($J$16:$J$77,B5+1)))</f>
-        <v>18044821.636461876</v>
+        <f>납입주기*(($N$16-INDEX($N$16:$N$76,B5+1))-(납입주기-1)/(2*납입주기)*($J$16-INDEX($J$16:$J$76,B5+1)))</f>
+        <v>18044892.918851402</v>
       </c>
       <c r="F3" s="16">
-        <v>18044821.636461891</v>
+        <v>18044892.91885139</v>
       </c>
       <c r="G3" s="17">
         <f>E3-F3</f>
@@ -8545,21 +8553,21 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <f>MIN(보험기간,B3+1-가입나이)</f>
-        <v>61</v>
+        <f>MIN(보험기간,IF(B3&gt;=110,B3+1,B3)-가입나이)</f>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="15">
         <f>E2/E3</f>
-        <v>1.2077143011247791E-3</v>
+        <v>1.2074073723646387E-3</v>
       </c>
       <c r="F4" s="16">
-        <v>1.207714301124778E-3</v>
+        <v>1.20740737236464E-3</v>
       </c>
       <c r="G4" s="17">
         <f>E4-F4</f>
@@ -8568,21 +8576,21 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5">
         <f>MIN(납입기간,B4)</f>
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="15">
-        <f>E2/($N$16-INDEX($N$16:$N$77,MIN(B4,20)+1))</f>
-        <v>1.428634073011247E-2</v>
+        <f>E2/($N$16-INDEX($N$16:$N$76,MIN(B4,20)+1))</f>
+        <v>1.4282713995202779E-2</v>
       </c>
       <c r="F5" s="16">
-        <v>1.428634073011247E-2</v>
+        <v>1.4282713995202791E-2</v>
       </c>
       <c r="G5" s="17">
         <f>E5-F5</f>
@@ -8591,13 +8599,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="15">
         <f>알파P*MIN(B4,20)/20</f>
@@ -8608,31 +8616,31 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <f>MAX(0,1-B6/12)</f>
         <v>0.75</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="15">
         <f>(알파S+E6*E5)*$J$16/E3</f>
-        <v>1.3458897638000923E-4</v>
+        <v>1.3456834631495518E-4</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="15">
         <f>베타S/납입주기</f>
@@ -8643,37 +8651,37 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" s="15">
-        <f>베타후*(INDEX($M$16:$M$77,B5+1)-$M$77)/E3</f>
-        <v>4.3579504022804224E-5</v>
+        <f>베타후*(INDEX($M$16:$M$76,B5+1)-$M$76)/E3</f>
+        <v>4.3571773833028045E-5</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="15">
         <f>(E4+E7+E8+E9)/(1-베타G-감마)</f>
-        <v>1.6246051414275189E-3</v>
+        <v>1.6242446156049699E-3</v>
       </c>
       <c r="F10" s="16">
-        <v>1.624605141427518E-3</v>
+        <v>1.624244615604971E-3</v>
       </c>
       <c r="G10" s="17">
         <f>E10-F10</f>
@@ -8682,10 +8690,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" s="6">
-        <f>ROUND(E10*100000,0)</f>
+        <f>ROUND(ROUND(E10,6)*100000,0)</f>
         <v>162</v>
       </c>
       <c r="F11" s="7">
@@ -8698,7 +8706,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="6">
         <f>E11*B2/100000</f>
@@ -8714,74 +8722,74 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="15">
-        <f>(E2+베타후*(INDEX($M$16:$M$77,B5+1)-$M$77))/($N$16-INDEX($N$16:$N$77,B5+1))</f>
-        <v>1.4801853084929543E-2</v>
+        <f>(E2+베타후*(INDEX($M$16:$M$76,B5+1)-$M$76))/($N$16-INDEX($N$16:$N$76,B5+1))</f>
+        <v>1.4798135052059517E-2</v>
       </c>
       <c r="F13" s="16">
-        <v>1.4801853084929539E-2</v>
+        <v>1.4798135052059531E-2</v>
       </c>
       <c r="G13" s="17">
         <f>E13-F13</f>
-        <v>0</v>
+        <v>-1.3877787807814457E-17</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="34" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.45">
@@ -8831,15 +8839,15 @@
         <v>0.75</v>
       </c>
       <c r="M16" s="20">
-        <f>SUM(I16:$I$77)</f>
-        <v>2314987.0564684272</v>
+        <f>SUM(I16:$I$76)</f>
+        <v>2314905.7251933799</v>
       </c>
       <c r="N16" s="20">
-        <f>SUM(J16:$J$77)</f>
-        <v>2300458.0184516208</v>
+        <f>SUM(J16:$J$76)</f>
+        <v>2300476.2188908095</v>
       </c>
       <c r="O16" s="22">
-        <f>IF(I16&lt;=0,0,(IF(A16&lt;$B$4,SUMPRODUCT(L16:$L$76,K16:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A16,$B$5)+1)-$M$77)-IF(A16&lt;=$B$5,$E$13*(N16-INDEX($N$16:$N$77,$B$5+1)),0))/I16)</f>
+        <f>IF(I16&lt;=0,0,(IF(A16&lt;$B$4,SUMPRODUCT(L16:$L$75,K16:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A16,$B$5)+1)-$M$76)-IF(A16&lt;=$B$5,$E$13*(N16-INDEX($N$16:$N$76,$B$5+1)),0))/I16)</f>
         <v>0</v>
       </c>
       <c r="P16" s="6">
@@ -8883,8 +8891,8 @@
         <v>99657.110509999999</v>
       </c>
       <c r="H17" s="20">
-        <f t="shared" ref="H17:H48" si="9">H16*MAX(0,1-F16-E16+F16*E16/2)</f>
-        <v>99642.435712377526</v>
+        <f t="shared" ref="H17:H48" si="9">H16*MAX(0,1-MIN(1,C16+(1-(1-D16)*(1-E16))-C16*(1-(1-D16)*(1-E16))/2))</f>
+        <v>99642.454593755028</v>
       </c>
       <c r="I17" s="20">
         <f t="shared" si="2"/>
@@ -8892,7 +8900,7 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="3"/>
-        <v>97212.132402319548</v>
+        <v>97212.150823175645</v>
       </c>
       <c r="K17" s="20">
         <f t="shared" si="4"/>
@@ -8903,23 +8911,23 @@
         <v>1</v>
       </c>
       <c r="M17" s="20">
-        <f>SUM(I17:$I$77)</f>
-        <v>2214987.0564684276</v>
+        <f>SUM(I17:$I$76)</f>
+        <v>2214905.7251933804</v>
       </c>
       <c r="N17" s="20">
-        <f>SUM(J17:$J$77)</f>
-        <v>2200458.0184516208</v>
+        <f>SUM(J17:$J$76)</f>
+        <v>2200476.2188908095</v>
       </c>
       <c r="O17" s="22">
-        <f>IF(I17&lt;=0,0,(IF(A17&lt;$B$4,SUMPRODUCT(L17:$L$76,K17:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A17,$B$5)+1)-$M$77)-IF(A17&lt;=$B$5,$E$13*(N17-INDEX($N$16:$N$77,$B$5+1)),0))/I17)</f>
-        <v>1.3265941915148682E-2</v>
+        <f>IF(I17&lt;=0,0,(IF(A17&lt;$B$4,SUMPRODUCT(L17:$L$75,K17:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A17,$B$5)+1)-$M$76)-IF(A17&lt;=$B$5,$E$13*(N17-INDEX($N$16:$N$76,$B$5+1)),0))/I17)</f>
+        <v>1.3262117819033244E-2</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="6"/>
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="Q17" s="7">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="R17" s="6">
         <f t="shared" si="7"/>
@@ -8956,7 +8964,7 @@
       </c>
       <c r="H18" s="20">
         <f t="shared" si="9"/>
-        <v>99263.850194460858</v>
+        <v>99263.890398135787</v>
       </c>
       <c r="I18" s="20">
         <f t="shared" si="2"/>
@@ -8964,7 +8972,7 @@
       </c>
       <c r="J18" s="20">
         <f t="shared" si="3"/>
-        <v>94480.761636607611</v>
+        <v>94480.799903044186</v>
       </c>
       <c r="K18" s="20">
         <f t="shared" si="4"/>
@@ -8975,23 +8983,23 @@
         <v>1</v>
       </c>
       <c r="M18" s="20">
-        <f>SUM(I18:$I$77)</f>
-        <v>2117760.607190378</v>
+        <f>SUM(I18:$I$76)</f>
+        <v>2117679.2759153307</v>
       </c>
       <c r="N18" s="20">
-        <f>SUM(J18:$J$77)</f>
-        <v>2103245.8860493009</v>
+        <f>SUM(J18:$J$76)</f>
+        <v>2103264.0680676331</v>
       </c>
       <c r="O18" s="22">
-        <f>IF(I18&lt;=0,0,(IF(A18&lt;$B$4,SUMPRODUCT(L18:$L$76,K18:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A18,$B$5)+1)-$M$77)-IF(A18&lt;=$B$5,$E$13*(N18-INDEX($N$16:$N$77,$B$5+1)),0))/I18)</f>
-        <v>2.6126809926903142E-2</v>
+        <f>IF(I18&lt;=0,0,(IF(A18&lt;$B$4,SUMPRODUCT(L18:$L$75,K18:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A18,$B$5)+1)-$M$76)-IF(A18&lt;=$B$5,$E$13*(N18-INDEX($N$16:$N$76,$B$5+1)),0))/I18)</f>
+        <v>2.6119054444049876E-2</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="6"/>
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="Q18" s="7">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="R18" s="6">
         <f t="shared" si="7"/>
@@ -9028,7 +9036,7 @@
       </c>
       <c r="H19" s="20">
         <f t="shared" si="9"/>
-        <v>98862.706361801102</v>
+        <v>98862.770340922172</v>
       </c>
       <c r="I19" s="20">
         <f t="shared" si="2"/>
@@ -9036,7 +9044,7 @@
       </c>
       <c r="J19" s="20">
         <f t="shared" si="3"/>
-        <v>91803.850889500623</v>
+        <v>91803.910300474759</v>
       </c>
       <c r="K19" s="20">
         <f t="shared" si="4"/>
@@ -9047,23 +9055,23 @@
         <v>1</v>
       </c>
       <c r="M19" s="20">
-        <f>SUM(I19:$I$77)</f>
-        <v>2023250.8764376612</v>
+        <f>SUM(I19:$I$76)</f>
+        <v>2023169.5451626142</v>
       </c>
       <c r="N19" s="20">
-        <f>SUM(J19:$J$77)</f>
-        <v>2008765.1244126938</v>
+        <f>SUM(J19:$J$76)</f>
+        <v>2008783.2681645888</v>
       </c>
       <c r="O19" s="22">
-        <f>IF(I19&lt;=0,0,(IF(A19&lt;$B$4,SUMPRODUCT(L19:$L$76,K19:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A19,$B$5)+1)-$M$77)-IF(A19&lt;=$B$5,$E$13*(N19-INDEX($N$16:$N$77,$B$5+1)),0))/I19)</f>
-        <v>3.9242058966029135E-2</v>
+        <f>IF(I19&lt;=0,0,(IF(A19&lt;$B$4,SUMPRODUCT(L19:$L$75,K19:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A19,$B$5)+1)-$M$76)-IF(A19&lt;=$B$5,$E$13*(N19-INDEX($N$16:$N$76,$B$5+1)),0))/I19)</f>
+        <v>3.9230260254896288E-2</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="6"/>
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="Q19" s="7">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="R19" s="6">
         <f t="shared" si="7"/>
@@ -9100,7 +9108,7 @@
       </c>
       <c r="H20" s="20">
         <f t="shared" si="9"/>
-        <v>98438.892417949377</v>
+        <v>98438.982981699257</v>
       </c>
       <c r="I20" s="20">
         <f t="shared" si="2"/>
@@ -9108,7 +9116,7 @@
       </c>
       <c r="J20" s="20">
         <f t="shared" si="3"/>
-        <v>89180.778059414952</v>
+        <v>89180.860105702552</v>
       </c>
       <c r="K20" s="20">
         <f t="shared" si="4"/>
@@ -9119,23 +9127,23 @@
         <v>1</v>
       </c>
       <c r="M20" s="20">
-        <f>SUM(I20:$I$77)</f>
-        <v>1931403.1407341156</v>
+        <f>SUM(I20:$I$76)</f>
+        <v>1931321.8094590686</v>
       </c>
       <c r="N20" s="20">
-        <f>SUM(J20:$J$77)</f>
-        <v>1916961.2735231931</v>
+        <f>SUM(J20:$J$76)</f>
+        <v>1916979.3578641138</v>
       </c>
       <c r="O20" s="22">
-        <f>IF(I20&lt;=0,0,(IF(A20&lt;$B$4,SUMPRODUCT(L20:$L$76,K20:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A20,$B$5)+1)-$M$77)-IF(A20&lt;=$B$5,$E$13*(N20-INDEX($N$16:$N$77,$B$5+1)),0))/I20)</f>
-        <v>5.2644357784148436E-2</v>
+        <f>IF(I20&lt;=0,0,(IF(A20&lt;$B$4,SUMPRODUCT(L20:$L$75,K20:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A20,$B$5)+1)-$M$76)-IF(A20&lt;=$B$5,$E$13*(N20-INDEX($N$16:$N$76,$B$5+1)),0))/I20)</f>
+        <v>5.2628399303665079E-2</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="6"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="Q20" s="7">
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="7"/>
@@ -9172,7 +9180,7 @@
       </c>
       <c r="H21" s="20">
         <f t="shared" si="9"/>
-        <v>97991.040606488357</v>
+        <v>97991.160940633941</v>
       </c>
       <c r="I21" s="20">
         <f t="shared" si="2"/>
@@ -9180,7 +9188,7 @@
       </c>
       <c r="J21" s="20">
         <f t="shared" si="3"/>
-        <v>86609.801387363041</v>
+        <v>86609.907745213568</v>
       </c>
       <c r="K21" s="20">
         <f t="shared" si="4"/>
@@ -9191,23 +9199,23 @@
         <v>1</v>
       </c>
       <c r="M21" s="20">
-        <f>SUM(I21:$I$77)</f>
-        <v>1842163.0989372344</v>
+        <f>SUM(I21:$I$76)</f>
+        <v>1842081.7676621873</v>
       </c>
       <c r="N21" s="20">
-        <f>SUM(J21:$J$77)</f>
-        <v>1827780.495463778</v>
+        <f>SUM(J21:$J$76)</f>
+        <v>1827798.4977584113</v>
       </c>
       <c r="O21" s="22">
-        <f>IF(I21&lt;=0,0,(IF(A21&lt;$B$4,SUMPRODUCT(L21:$L$76,K21:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A21,$B$5)+1)-$M$77)-IF(A21&lt;=$B$5,$E$13*(N21-INDEX($N$16:$N$77,$B$5+1)),0))/I21)</f>
-        <v>6.6365345459647784E-2</v>
+        <f>IF(I21&lt;=0,0,(IF(A21&lt;$B$4,SUMPRODUCT(L21:$L$75,K21:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A21,$B$5)+1)-$M$76)-IF(A21&lt;=$B$5,$E$13*(N21-INDEX($N$16:$N$76,$B$5+1)),0))/I21)</f>
+        <v>6.6345105547331626E-2</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="6"/>
-        <v>6637</v>
+        <v>6635</v>
       </c>
       <c r="Q21" s="7">
-        <v>6637</v>
+        <v>6635</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="7"/>
@@ -9244,7 +9252,7 @@
       </c>
       <c r="H22" s="20">
         <f t="shared" si="9"/>
-        <v>97517.045875529191</v>
+        <v>97517.200282228834</v>
       </c>
       <c r="I22" s="20">
         <f t="shared" si="2"/>
@@ -9252,7 +9260,7 @@
       </c>
       <c r="J22" s="20">
         <f t="shared" si="3"/>
-        <v>84088.643036195586</v>
+        <v>84088.776180608766</v>
       </c>
       <c r="K22" s="20">
         <f t="shared" si="4"/>
@@ -9263,23 +9271,23 @@
         <v>1</v>
       </c>
       <c r="M22" s="20">
-        <f>SUM(I22:$I$77)</f>
-        <v>1755478.0199655662</v>
+        <f>SUM(I22:$I$76)</f>
+        <v>1755396.6886905192</v>
       </c>
       <c r="N22" s="20">
-        <f>SUM(J22:$J$77)</f>
-        <v>1741170.6940764152</v>
+        <f>SUM(J22:$J$76)</f>
+        <v>1741188.5900131976</v>
       </c>
       <c r="O22" s="22">
-        <f>IF(I22&lt;=0,0,(IF(A22&lt;$B$4,SUMPRODUCT(L22:$L$76,K22:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A22,$B$5)+1)-$M$77)-IF(A22&lt;=$B$5,$E$13*(N22-INDEX($N$16:$N$77,$B$5+1)),0))/I22)</f>
-        <v>8.0424452417298786E-2</v>
+        <f>IF(I22&lt;=0,0,(IF(A22&lt;$B$4,SUMPRODUCT(L22:$L$75,K22:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A22,$B$5)+1)-$M$76)-IF(A22&lt;=$B$5,$E$13*(N22-INDEX($N$16:$N$76,$B$5+1)),0))/I22)</f>
+        <v>8.0399803846712095E-2</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="6"/>
-        <v>8042</v>
+        <v>8040</v>
       </c>
       <c r="Q22" s="7">
-        <v>8042</v>
+        <v>8040</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="7"/>
@@ -9316,7 +9324,7 @@
       </c>
       <c r="H23" s="20">
         <f t="shared" si="9"/>
-        <v>97014.672213468832</v>
+        <v>97014.86615102661</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="2"/>
@@ -9324,7 +9332,7 @@
       </c>
       <c r="J23" s="20">
         <f t="shared" si="3"/>
-        <v>81615.071026204721</v>
+        <v>81615.234179129868</v>
       </c>
       <c r="K23" s="20">
         <f t="shared" si="4"/>
@@ -9335,23 +9343,23 @@
         <v>1</v>
       </c>
       <c r="M23" s="20">
-        <f>SUM(I23:$I$77)</f>
-        <v>1671296.9685415179</v>
+        <f>SUM(I23:$I$76)</f>
+        <v>1671215.6372664708</v>
       </c>
       <c r="N23" s="20">
-        <f>SUM(J23:$J$77)</f>
-        <v>1657082.0510402196</v>
+        <f>SUM(J23:$J$76)</f>
+        <v>1657099.8138325887</v>
       </c>
       <c r="O23" s="22">
-        <f>IF(I23&lt;=0,0,(IF(A23&lt;$B$4,SUMPRODUCT(L23:$L$76,K23:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A23,$B$5)+1)-$M$77)-IF(A23&lt;=$B$5,$E$13*(N23-INDEX($N$16:$N$77,$B$5+1)),0))/I23)</f>
-        <v>9.4818579226636238E-2</v>
+        <f>IF(I23&lt;=0,0,(IF(A23&lt;$B$4,SUMPRODUCT(L23:$L$75,K23:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A23,$B$5)+1)-$M$76)-IF(A23&lt;=$B$5,$E$13*(N23-INDEX($N$16:$N$76,$B$5+1)),0))/I23)</f>
+        <v>9.4789388794992782E-2</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="6"/>
-        <v>9482</v>
+        <v>9479</v>
       </c>
       <c r="Q23" s="7">
-        <v>9482</v>
+        <v>9479</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="7"/>
@@ -9388,7 +9396,7 @@
       </c>
       <c r="H24" s="20">
         <f t="shared" si="9"/>
-        <v>96480.11229661289</v>
+        <v>96480.352753141153</v>
       </c>
       <c r="I24" s="20">
         <f t="shared" si="2"/>
@@ -9396,7 +9404,7 @@
       </c>
       <c r="J24" s="20">
         <f t="shared" si="3"/>
-        <v>79185.721319107062</v>
+        <v>79185.918672978063</v>
       </c>
       <c r="K24" s="20">
         <f t="shared" si="4"/>
@@ -9407,23 +9415,23 @@
         <v>1</v>
       </c>
       <c r="M24" s="20">
-        <f>SUM(I24:$I$77)</f>
-        <v>1589570.9883634495</v>
+        <f>SUM(I24:$I$76)</f>
+        <v>1589489.6570884024</v>
       </c>
       <c r="N24" s="20">
-        <f>SUM(J24:$J$77)</f>
-        <v>1575466.9800140148</v>
+        <f>SUM(J24:$J$76)</f>
+        <v>1575484.5796534591</v>
       </c>
       <c r="O24" s="22">
-        <f>IF(I24&lt;=0,0,(IF(A24&lt;$B$4,SUMPRODUCT(L24:$L$76,K24:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A24,$B$5)+1)-$M$77)-IF(A24&lt;=$B$5,$E$13*(N24-INDEX($N$16:$N$77,$B$5+1)),0))/I24)</f>
-        <v>0.1095302653828968</v>
+        <f>IF(I24&lt;=0,0,(IF(A24&lt;$B$4,SUMPRODUCT(L24:$L$75,K24:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A24,$B$5)+1)-$M$76)-IF(A24&lt;=$B$5,$E$13*(N24-INDEX($N$16:$N$76,$B$5+1)),0))/I24)</f>
+        <v>0.10949639295153256</v>
       </c>
       <c r="P24" s="6">
         <f t="shared" si="6"/>
-        <v>10953</v>
+        <v>10950</v>
       </c>
       <c r="Q24" s="7">
-        <v>10953</v>
+        <v>10950</v>
       </c>
       <c r="R24" s="6">
         <f t="shared" si="7"/>
@@ -9460,7 +9468,7 @@
       </c>
       <c r="H25" s="20">
         <f t="shared" si="9"/>
-        <v>95910.064154332809</v>
+        <v>95910.359061995317</v>
       </c>
       <c r="I25" s="20">
         <f t="shared" si="2"/>
@@ -9468,7 +9476,7 @@
       </c>
       <c r="J25" s="20">
         <f t="shared" si="3"/>
-        <v>76797.908547446161</v>
+        <v>76798.144688375629</v>
       </c>
       <c r="K25" s="20">
         <f t="shared" si="4"/>
@@ -9479,23 +9487,23 @@
         <v>1</v>
       </c>
       <c r="M25" s="20">
-        <f>SUM(I25:$I$77)</f>
-        <v>1510254.2789503508</v>
+        <f>SUM(I25:$I$76)</f>
+        <v>1510172.9476753038</v>
       </c>
       <c r="N25" s="20">
-        <f>SUM(J25:$J$77)</f>
-        <v>1496281.2586949077</v>
+        <f>SUM(J25:$J$76)</f>
+        <v>1496298.6609804807</v>
       </c>
       <c r="O25" s="22">
-        <f>IF(I25&lt;=0,0,(IF(A25&lt;$B$4,SUMPRODUCT(L25:$L$76,K25:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A25,$B$5)+1)-$M$77)-IF(A25&lt;=$B$5,$E$13*(N25-INDEX($N$16:$N$77,$B$5+1)),0))/I25)</f>
-        <v>0.12454258134132806</v>
+        <f>IF(I25&lt;=0,0,(IF(A25&lt;$B$4,SUMPRODUCT(L25:$L$75,K25:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A25,$B$5)+1)-$M$76)-IF(A25&lt;=$B$5,$E$13*(N25-INDEX($N$16:$N$76,$B$5+1)),0))/I25)</f>
+        <v>0.12450387917761936</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="6"/>
-        <v>12454</v>
+        <v>12450</v>
       </c>
       <c r="Q25" s="7">
-        <v>12454</v>
+        <v>12450</v>
       </c>
       <c r="R25" s="6">
         <f t="shared" si="7"/>
@@ -9532,7 +9540,7 @@
       </c>
       <c r="H26" s="20">
         <f t="shared" si="9"/>
-        <v>95300.776980448791</v>
+        <v>95301.135780503479</v>
       </c>
       <c r="I26" s="20">
         <f t="shared" si="2"/>
@@ -9540,7 +9548,7 @@
       </c>
       <c r="J26" s="20">
         <f t="shared" si="3"/>
-        <v>74448.814660346572</v>
+        <v>74449.094954375832</v>
       </c>
       <c r="K26" s="20">
         <f t="shared" si="4"/>
@@ -9551,23 +9559,23 @@
         <v>1</v>
       </c>
       <c r="M26" s="20">
-        <f>SUM(I26:$I$77)</f>
-        <v>1433303.9445062699</v>
+        <f>SUM(I26:$I$76)</f>
+        <v>1433222.6132312228</v>
       </c>
       <c r="N26" s="20">
-        <f>SUM(J26:$J$77)</f>
-        <v>1419483.3501474615</v>
+        <f>SUM(J26:$J$76)</f>
+        <v>1419500.516292105</v>
       </c>
       <c r="O26" s="22">
-        <f>IF(I26&lt;=0,0,(IF(A26&lt;$B$4,SUMPRODUCT(L26:$L$76,K26:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A26,$B$5)+1)-$M$77)-IF(A26&lt;=$B$5,$E$13*(N26-INDEX($N$16:$N$77,$B$5+1)),0))/I26)</f>
-        <v>0.13984775777980327</v>
+        <f>IF(I26&lt;=0,0,(IF(A26&lt;$B$4,SUMPRODUCT(L26:$L$75,K26:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A26,$B$5)+1)-$M$76)-IF(A26&lt;=$B$5,$E$13*(N26-INDEX($N$16:$N$76,$B$5+1)),0))/I26)</f>
+        <v>0.13980406962234546</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="6"/>
-        <v>13985</v>
+        <v>13980</v>
       </c>
       <c r="Q26" s="7">
-        <v>13985</v>
+        <v>13980</v>
       </c>
       <c r="R26" s="6">
         <f t="shared" si="7"/>
@@ -9604,7 +9612,7 @@
       </c>
       <c r="H27" s="20">
         <f t="shared" si="9"/>
-        <v>94663.948633455686</v>
+        <v>94664.354383544051</v>
       </c>
       <c r="I27" s="20">
         <f t="shared" si="2"/>
@@ -9612,7 +9620,7 @@
       </c>
       <c r="J27" s="20">
         <f t="shared" si="3"/>
-        <v>72147.63451073358</v>
+        <v>72147.943751046303</v>
       </c>
       <c r="K27" s="20">
         <f t="shared" si="4"/>
@@ -9623,23 +9631,23 @@
         <v>1</v>
       </c>
       <c r="M27" s="20">
-        <f>SUM(I27:$I$77)</f>
-        <v>1358679.896852097</v>
+        <f>SUM(I27:$I$76)</f>
+        <v>1358598.56557705</v>
       </c>
       <c r="N27" s="20">
-        <f>SUM(J27:$J$77)</f>
-        <v>1345034.5354871152</v>
+        <f>SUM(J27:$J$76)</f>
+        <v>1345051.4213377293</v>
       </c>
       <c r="O27" s="22">
-        <f>IF(I27&lt;=0,0,(IF(A27&lt;$B$4,SUMPRODUCT(L27:$L$76,K27:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A27,$B$5)+1)-$M$77)-IF(A27&lt;=$B$5,$E$13*(N27-INDEX($N$16:$N$77,$B$5+1)),0))/I27)</f>
-        <v>0.15544110116762586</v>
+        <f>IF(I27&lt;=0,0,(IF(A27&lt;$B$4,SUMPRODUCT(L27:$L$75,K27:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A27,$B$5)+1)-$M$76)-IF(A27&lt;=$B$5,$E$13*(N27-INDEX($N$16:$N$76,$B$5+1)),0))/I27)</f>
+        <v>0.1553922620438464</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="6"/>
-        <v>15544</v>
+        <v>15539</v>
       </c>
       <c r="Q27" s="7">
-        <v>15544</v>
+        <v>15539</v>
       </c>
       <c r="R27" s="6">
         <f t="shared" si="7"/>
@@ -9676,7 +9684,7 @@
       </c>
       <c r="H28" s="20">
         <f t="shared" si="9"/>
-        <v>93983.090137495034</v>
+        <v>93983.549659921133</v>
       </c>
       <c r="I28" s="20">
         <f t="shared" si="2"/>
@@ -9684,7 +9692,7 @@
       </c>
       <c r="J28" s="20">
         <f t="shared" si="3"/>
-        <v>69881.679766478133</v>
+        <v>69882.02144708237</v>
       </c>
       <c r="K28" s="20">
         <f t="shared" si="4"/>
@@ -9695,23 +9703,23 @@
         <v>1</v>
       </c>
       <c r="M28" s="20">
-        <f>SUM(I28:$I$77)</f>
-        <v>1286343.5774875029</v>
+        <f>SUM(I28:$I$76)</f>
+        <v>1286262.2462124559</v>
       </c>
       <c r="N28" s="20">
-        <f>SUM(J28:$J$77)</f>
-        <v>1272886.900976382</v>
+        <f>SUM(J28:$J$76)</f>
+        <v>1272903.4775866829</v>
       </c>
       <c r="O28" s="22">
-        <f>IF(I28&lt;=0,0,(IF(A28&lt;$B$4,SUMPRODUCT(L28:$L$76,K28:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A28,$B$5)+1)-$M$77)-IF(A28&lt;=$B$5,$E$13*(N28-INDEX($N$16:$N$77,$B$5+1)),0))/I28)</f>
-        <v>0.17132267388411129</v>
+        <f>IF(I28&lt;=0,0,(IF(A28&lt;$B$4,SUMPRODUCT(L28:$L$75,K28:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A28,$B$5)+1)-$M$76)-IF(A28&lt;=$B$5,$E$13*(N28-INDEX($N$16:$N$76,$B$5+1)),0))/I28)</f>
+        <v>0.17126850313648409</v>
       </c>
       <c r="P28" s="6">
         <f t="shared" si="6"/>
-        <v>17132</v>
+        <v>17127</v>
       </c>
       <c r="Q28" s="7">
-        <v>17132</v>
+        <v>17127</v>
       </c>
       <c r="R28" s="6">
         <f t="shared" si="7"/>
@@ -9748,7 +9756,7 @@
       </c>
       <c r="H29" s="20">
         <f t="shared" si="9"/>
-        <v>93251.411770440231</v>
+        <v>93251.932774164146</v>
       </c>
       <c r="I29" s="20">
         <f t="shared" si="2"/>
@@ -9756,7 +9764,7 @@
       </c>
       <c r="J29" s="20">
         <f t="shared" si="3"/>
-        <v>67646.474156774813</v>
+        <v>67646.852103491939</v>
       </c>
       <c r="K29" s="20">
         <f t="shared" si="4"/>
@@ -9767,23 +9775,23 @@
         <v>1</v>
       </c>
       <c r="M29" s="20">
-        <f>SUM(I29:$I$77)</f>
-        <v>1216259.3767300891</v>
+        <f>SUM(I29:$I$76)</f>
+        <v>1216178.045455042</v>
       </c>
       <c r="N29" s="20">
-        <f>SUM(J29:$J$77)</f>
-        <v>1203005.2212099039</v>
+        <f>SUM(J29:$J$76)</f>
+        <v>1203021.4561396004</v>
       </c>
       <c r="O29" s="22">
-        <f>IF(I29&lt;=0,0,(IF(A29&lt;$B$4,SUMPRODUCT(L29:$L$76,K29:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A29,$B$5)+1)-$M$77)-IF(A29&lt;=$B$5,$E$13*(N29-INDEX($N$16:$N$77,$B$5+1)),0))/I29)</f>
-        <v>0.18748899692053511</v>
+        <f>IF(I29&lt;=0,0,(IF(A29&lt;$B$4,SUMPRODUCT(L29:$L$75,K29:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A29,$B$5)+1)-$M$76)-IF(A29&lt;=$B$5,$E$13*(N29-INDEX($N$16:$N$76,$B$5+1)),0))/I29)</f>
+        <v>0.18742929908274253</v>
       </c>
       <c r="P29" s="6">
         <f t="shared" si="6"/>
-        <v>18749</v>
+        <v>18743</v>
       </c>
       <c r="Q29" s="7">
-        <v>18749</v>
+        <v>18743</v>
       </c>
       <c r="R29" s="6">
         <f t="shared" si="7"/>
@@ -9820,7 +9828,7 @@
       </c>
       <c r="H30" s="20">
         <f t="shared" si="9"/>
-        <v>92464.478455144606</v>
+        <v>92465.069567153332</v>
       </c>
       <c r="I30" s="20">
         <f t="shared" si="2"/>
@@ -9828,7 +9836,7 @@
       </c>
       <c r="J30" s="20">
         <f t="shared" si="3"/>
-        <v>65439.626044466793</v>
+        <v>65440.04439051111</v>
       </c>
       <c r="K30" s="20">
         <f t="shared" si="4"/>
@@ -9839,23 +9847,23 @@
         <v>1</v>
       </c>
       <c r="M30" s="20">
-        <f>SUM(I30:$I$77)</f>
-        <v>1148396.2874066154</v>
+        <f>SUM(I30:$I$76)</f>
+        <v>1148314.9561315684</v>
       </c>
       <c r="N30" s="20">
-        <f>SUM(J30:$J$77)</f>
-        <v>1135358.7470531291</v>
+        <f>SUM(J30:$J$76)</f>
+        <v>1135374.6040361086</v>
       </c>
       <c r="O30" s="22">
-        <f>IF(I30&lt;=0,0,(IF(A30&lt;$B$4,SUMPRODUCT(L30:$L$76,K30:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A30,$B$5)+1)-$M$77)-IF(A30&lt;=$B$5,$E$13*(N30-INDEX($N$16:$N$77,$B$5+1)),0))/I30)</f>
-        <v>0.20393853719801319</v>
+        <f>IF(I30&lt;=0,0,(IF(A30&lt;$B$4,SUMPRODUCT(L30:$L$75,K30:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A30,$B$5)+1)-$M$76)-IF(A30&lt;=$B$5,$E$13*(N30-INDEX($N$16:$N$76,$B$5+1)),0))/I30)</f>
+        <v>0.2038731014181524</v>
       </c>
       <c r="P30" s="6">
         <f t="shared" si="6"/>
-        <v>20394</v>
+        <v>20387</v>
       </c>
       <c r="Q30" s="7">
-        <v>20394</v>
+        <v>20387</v>
       </c>
       <c r="R30" s="6">
         <f t="shared" si="7"/>
@@ -9892,7 +9900,7 @@
       </c>
       <c r="H31" s="20">
         <f t="shared" si="9"/>
-        <v>91616.563888028206</v>
+        <v>91617.234165977541</v>
       </c>
       <c r="I31" s="20">
         <f t="shared" si="2"/>
@@ -9900,7 +9908,7 @@
       </c>
       <c r="J31" s="20">
         <f t="shared" si="3"/>
-        <v>63258.081800621942</v>
+        <v>63258.544604459472</v>
       </c>
       <c r="K31" s="20">
         <f t="shared" si="4"/>
@@ -9911,23 +9919,23 @@
         <v>1</v>
       </c>
       <c r="M31" s="20">
-        <f>SUM(I31:$I$77)</f>
-        <v>1082725.8145311344</v>
+        <f>SUM(I31:$I$76)</f>
+        <v>1082644.4832560874</v>
       </c>
       <c r="N31" s="20">
-        <f>SUM(J31:$J$77)</f>
-        <v>1069919.1210086623</v>
+        <f>SUM(J31:$J$76)</f>
+        <v>1069934.5596455976</v>
       </c>
       <c r="O31" s="22">
-        <f>IF(I31&lt;=0,0,(IF(A31&lt;$B$4,SUMPRODUCT(L31:$L$76,K31:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A31,$B$5)+1)-$M$77)-IF(A31&lt;=$B$5,$E$13*(N31-INDEX($N$16:$N$77,$B$5+1)),0))/I31)</f>
-        <v>0.22067851296348714</v>
+        <f>IF(I31&lt;=0,0,(IF(A31&lt;$B$4,SUMPRODUCT(L31:$L$75,K31:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A31,$B$5)+1)-$M$76)-IF(A31&lt;=$B$5,$E$13*(N31-INDEX($N$16:$N$76,$B$5+1)),0))/I31)</f>
+        <v>0.22060710986224899</v>
       </c>
       <c r="P31" s="6">
         <f t="shared" si="6"/>
-        <v>22068</v>
+        <v>22061</v>
       </c>
       <c r="Q31" s="7">
-        <v>22068</v>
+        <v>22061</v>
       </c>
       <c r="R31" s="6">
         <f t="shared" si="7"/>
@@ -9964,7 +9972,7 @@
       </c>
       <c r="H32" s="20">
         <f t="shared" si="9"/>
-        <v>90704.317064834278</v>
+        <v>90705.075886087056</v>
       </c>
       <c r="I32" s="20">
         <f t="shared" si="2"/>
@@ -9972,7 +9980,7 @@
       </c>
       <c r="J32" s="20">
         <f t="shared" si="3"/>
-        <v>61100.689551093412</v>
+        <v>61101.200712009348</v>
       </c>
       <c r="K32" s="20">
         <f t="shared" si="4"/>
@@ -9983,23 +9991,23 @@
         <v>1</v>
       </c>
       <c r="M32" s="20">
-        <f>SUM(I32:$I$77)</f>
-        <v>1019222.7668037523</v>
+        <f>SUM(I32:$I$76)</f>
+        <v>1019141.4355287052</v>
       </c>
       <c r="N32" s="20">
-        <f>SUM(J32:$J$77)</f>
-        <v>1006661.0392080402</v>
+        <f>SUM(J32:$J$76)</f>
+        <v>1006676.0150411386</v>
       </c>
       <c r="O32" s="22">
-        <f>IF(I32&lt;=0,0,(IF(A32&lt;$B$4,SUMPRODUCT(L32:$L$76,K32:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A32,$B$5)+1)-$M$77)-IF(A32&lt;=$B$5,$E$13*(N32-INDEX($N$16:$N$77,$B$5+1)),0))/I32)</f>
-        <v>0.23771786341279061</v>
+        <f>IF(I32&lt;=0,0,(IF(A32&lt;$B$4,SUMPRODUCT(L32:$L$75,K32:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A32,$B$5)+1)-$M$76)-IF(A32&lt;=$B$5,$E$13*(N32-INDEX($N$16:$N$76,$B$5+1)),0))/I32)</f>
+        <v>0.23764024435588524</v>
       </c>
       <c r="P32" s="6">
         <f t="shared" si="6"/>
-        <v>23772</v>
+        <v>23764</v>
       </c>
       <c r="Q32" s="7">
-        <v>23772</v>
+        <v>23764</v>
       </c>
       <c r="R32" s="6">
         <f t="shared" si="7"/>
@@ -10036,7 +10044,7 @@
       </c>
       <c r="H33" s="20">
         <f t="shared" si="9"/>
-        <v>89720.823481680229</v>
+        <v>89721.680877245992</v>
       </c>
       <c r="I33" s="20">
         <f t="shared" si="2"/>
@@ -10044,7 +10052,7 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="3"/>
-        <v>58964.081708821628</v>
+        <v>58964.645184949404</v>
       </c>
       <c r="K33" s="20">
         <f t="shared" si="4"/>
@@ -10055,23 +10063,23 @@
         <v>1</v>
       </c>
       <c r="M33" s="20">
-        <f>SUM(I33:$I$77)</f>
-        <v>957863.33099709696</v>
+        <f>SUM(I33:$I$76)</f>
+        <v>957781.99972204992</v>
       </c>
       <c r="N33" s="20">
-        <f>SUM(J33:$J$77)</f>
-        <v>945560.34965694672</v>
+        <f>SUM(J33:$J$76)</f>
+        <v>945574.81432912918</v>
       </c>
       <c r="O33" s="22">
-        <f>IF(I33&lt;=0,0,(IF(A33&lt;$B$4,SUMPRODUCT(L33:$L$76,K33:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A33,$B$5)+1)-$M$77)-IF(A33&lt;=$B$5,$E$13*(N33-INDEX($N$16:$N$77,$B$5+1)),0))/I33)</f>
-        <v>0.25506807000591358</v>
+        <f>IF(I33&lt;=0,0,(IF(A33&lt;$B$4,SUMPRODUCT(L33:$L$75,K33:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A33,$B$5)+1)-$M$76)-IF(A33&lt;=$B$5,$E$13*(N33-INDEX($N$16:$N$76,$B$5+1)),0))/I33)</f>
+        <v>0.25498396131616718</v>
       </c>
       <c r="P33" s="6">
         <f t="shared" si="6"/>
-        <v>25507</v>
+        <v>25498</v>
       </c>
       <c r="Q33" s="7">
-        <v>25507</v>
+        <v>25498</v>
       </c>
       <c r="R33" s="6">
         <f t="shared" si="7"/>
@@ -10108,7 +10116,7 @@
       </c>
       <c r="H34" s="20">
         <f t="shared" si="9"/>
-        <v>88657.370864054858</v>
+        <v>88658.337393518261</v>
       </c>
       <c r="I34" s="20">
         <f t="shared" si="2"/>
@@ -10116,7 +10124,7 @@
       </c>
       <c r="J34" s="20">
         <f t="shared" si="3"/>
-        <v>56844.08380983922</v>
+        <v>56844.703515581532</v>
       </c>
       <c r="K34" s="20">
         <f t="shared" si="4"/>
@@ -10127,23 +10135,23 @@
         <v>1</v>
       </c>
       <c r="M34" s="20">
-        <f>SUM(I34:$I$77)</f>
-        <v>898627.21997878316</v>
+        <f>SUM(I34:$I$76)</f>
+        <v>898545.88870373613</v>
       </c>
       <c r="N34" s="20">
-        <f>SUM(J34:$J$77)</f>
-        <v>886596.26794812514</v>
+        <f>SUM(J34:$J$76)</f>
+        <v>886610.16914417979</v>
       </c>
       <c r="O34" s="22">
-        <f>IF(I34&lt;=0,0,(IF(A34&lt;$B$4,SUMPRODUCT(L34:$L$76,K34:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A34,$B$5)+1)-$M$77)-IF(A34&lt;=$B$5,$E$13*(N34-INDEX($N$16:$N$77,$B$5+1)),0))/I34)</f>
-        <v>0.27273711747632995</v>
+        <f>IF(I34&lt;=0,0,(IF(A34&lt;$B$4,SUMPRODUCT(L34:$L$75,K34:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A34,$B$5)+1)-$M$76)-IF(A34&lt;=$B$5,$E$13*(N34-INDEX($N$16:$N$76,$B$5+1)),0))/I34)</f>
+        <v>0.27264621456605725</v>
       </c>
       <c r="P34" s="6">
         <f t="shared" si="6"/>
-        <v>27274</v>
+        <v>27265</v>
       </c>
       <c r="Q34" s="7">
-        <v>27274</v>
+        <v>27265</v>
       </c>
       <c r="R34" s="6">
         <f t="shared" si="7"/>
@@ -10180,7 +10188,7 @@
       </c>
       <c r="H35" s="20">
         <f t="shared" si="9"/>
-        <v>87504.538206749407</v>
+        <v>87505.625174992616</v>
       </c>
       <c r="I35" s="20">
         <f t="shared" si="2"/>
@@ -10188,7 +10196,7 @@
       </c>
       <c r="J35" s="20">
         <f t="shared" si="3"/>
-        <v>54736.513961756013</v>
+        <v>54737.193890519018</v>
       </c>
       <c r="K35" s="20">
         <f t="shared" si="4"/>
@@ -10199,23 +10207,23 @@
         <v>1</v>
       </c>
       <c r="M35" s="20">
-        <f>SUM(I35:$I$77)</f>
-        <v>841498.53547409608</v>
+        <f>SUM(I35:$I$76)</f>
+        <v>841417.20419904904</v>
       </c>
       <c r="N35" s="20">
-        <f>SUM(J35:$J$77)</f>
-        <v>829752.18413828581</v>
+        <f>SUM(J35:$J$76)</f>
+        <v>829765.46562859823</v>
       </c>
       <c r="O35" s="22">
-        <f>IF(I35&lt;=0,0,(IF(A35&lt;$B$4,SUMPRODUCT(L35:$L$76,K35:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A35,$B$5)+1)-$M$77)-IF(A35&lt;=$B$5,$E$13*(N35-INDEX($N$16:$N$77,$B$5+1)),0))/I35)</f>
-        <v>0.29074032598120292</v>
+        <f>IF(I35&lt;=0,0,(IF(A35&lt;$B$4,SUMPRODUCT(L35:$L$75,K35:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A35,$B$5)+1)-$M$76)-IF(A35&lt;=$B$5,$E$13*(N35-INDEX($N$16:$N$76,$B$5+1)),0))/I35)</f>
+        <v>0.29064228738045428</v>
       </c>
       <c r="P35" s="6">
         <f t="shared" si="6"/>
-        <v>29074</v>
+        <v>29064</v>
       </c>
       <c r="Q35" s="7">
-        <v>29074</v>
+        <v>29064</v>
       </c>
       <c r="R35" s="6">
         <f t="shared" si="7"/>
@@ -10252,7 +10260,7 @@
       </c>
       <c r="H36" s="20">
         <f t="shared" si="9"/>
-        <v>86254.820107085747</v>
+        <v>86256.040387089888</v>
       </c>
       <c r="I36" s="20">
         <f t="shared" si="2"/>
@@ -10260,7 +10268,7 @@
       </c>
       <c r="J36" s="20">
         <f t="shared" si="3"/>
-        <v>52638.810392870037</v>
+        <v>52639.55509429871</v>
       </c>
       <c r="K36" s="20">
         <f t="shared" si="4"/>
@@ -10271,23 +10279,23 @@
         <v>1</v>
       </c>
       <c r="M36" s="20">
-        <f>SUM(I36:$I$77)</f>
-        <v>786465.70837202214</v>
+        <f>SUM(I36:$I$76)</f>
+        <v>786384.37709697511</v>
       </c>
       <c r="N36" s="20">
-        <f>SUM(J36:$J$77)</f>
-        <v>775015.67017652991</v>
+        <f>SUM(J36:$J$76)</f>
+        <v>775028.27173807926</v>
       </c>
       <c r="O36" s="22">
-        <f>IF(I36&lt;=0,0,(IF(A36&lt;$B$4,SUMPRODUCT(L36:$L$76,K36:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A36,$B$5)+1)-$M$77)-IF(A36&lt;=$B$5,$E$13*(N36-INDEX($N$16:$N$77,$B$5+1)),0))/I36)</f>
-        <v>0.30910294160956214</v>
+        <f>IF(I36&lt;=0,0,(IF(A36&lt;$B$4,SUMPRODUCT(L36:$L$75,K36:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A36,$B$5)+1)-$M$76)-IF(A36&lt;=$B$5,$E$13*(N36-INDEX($N$16:$N$76,$B$5+1)),0))/I36)</f>
+        <v>0.30899738516164493</v>
       </c>
       <c r="P36" s="6">
         <f t="shared" si="6"/>
-        <v>30910</v>
+        <v>30900</v>
       </c>
       <c r="Q36" s="7">
-        <v>30910</v>
+        <v>30900</v>
       </c>
       <c r="R36" s="6">
         <f t="shared" si="7"/>
@@ -10324,7 +10332,7 @@
       </c>
       <c r="H37" s="20">
         <f t="shared" si="9"/>
-        <v>84896.75528911654</v>
+        <v>84898.154839736613</v>
       </c>
       <c r="I37" s="20">
         <f t="shared" si="2"/>
@@ -10332,7 +10340,7 @@
       </c>
       <c r="J37" s="20">
         <f t="shared" si="3"/>
-        <v>50546.363800921528</v>
+        <v>50547.197074166885</v>
       </c>
       <c r="K37" s="20">
         <f t="shared" si="4"/>
@@ -10343,23 +10351,23 @@
         <v>1</v>
       </c>
       <c r="M37" s="20">
-        <f>SUM(I37:$I$77)</f>
-        <v>733519.70691928186</v>
+        <f>SUM(I37:$I$76)</f>
+        <v>733438.37564423482</v>
       </c>
       <c r="N37" s="20">
-        <f>SUM(J37:$J$77)</f>
-        <v>722376.85978365992</v>
+        <f>SUM(J37:$J$76)</f>
+        <v>722388.71664378059</v>
       </c>
       <c r="O37" s="22">
-        <f>IF(I37&lt;=0,0,(IF(A37&lt;$B$4,SUMPRODUCT(L37:$L$76,K37:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A37,$B$5)+1)-$M$77)-IF(A37&lt;=$B$5,$E$13*(N37-INDEX($N$16:$N$77,$B$5+1)),0))/I37)</f>
-        <v>0.31150940846180486</v>
+        <f>IF(I37&lt;=0,0,(IF(A37&lt;$B$4,SUMPRODUCT(L37:$L$75,K37:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A37,$B$5)+1)-$M$76)-IF(A37&lt;=$B$5,$E$13*(N37-INDEX($N$16:$N$76,$B$5+1)),0))/I37)</f>
+        <v>0.31139953960927291</v>
       </c>
       <c r="P37" s="6">
         <f t="shared" si="6"/>
-        <v>31151</v>
+        <v>31140</v>
       </c>
       <c r="Q37" s="7">
-        <v>31151</v>
+        <v>31140</v>
       </c>
       <c r="R37" s="6">
         <f t="shared" si="7"/>
@@ -10396,7 +10404,7 @@
       </c>
       <c r="H38" s="20">
         <f t="shared" si="9"/>
-        <v>83435.127346083551</v>
+        <v>83436.721217583734</v>
       </c>
       <c r="I38" s="20">
         <f t="shared" si="2"/>
@@ -10404,7 +10412,7 @@
       </c>
       <c r="J38" s="20">
         <f t="shared" si="3"/>
-        <v>48464.517628117566</v>
+        <v>48465.443451758932</v>
       </c>
       <c r="K38" s="20">
         <f t="shared" si="4"/>
@@ -10415,23 +10423,23 @@
         <v>1</v>
       </c>
       <c r="M38" s="20">
-        <f>SUM(I38:$I$77)</f>
-        <v>682651.86115612474</v>
+        <f>SUM(I38:$I$76)</f>
+        <v>682570.5298810777</v>
       </c>
       <c r="N38" s="20">
-        <f>SUM(J38:$J$77)</f>
-        <v>671830.49598273833</v>
+        <f>SUM(J38:$J$76)</f>
+        <v>671841.51956961374</v>
       </c>
       <c r="O38" s="22">
-        <f>IF(I38&lt;=0,0,(IF(A38&lt;$B$4,SUMPRODUCT(L38:$L$76,K38:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A38,$B$5)+1)-$M$77)-IF(A38&lt;=$B$5,$E$13*(N38-INDEX($N$16:$N$77,$B$5+1)),0))/I38)</f>
-        <v>0.3136623581027993</v>
+        <f>IF(I38&lt;=0,0,(IF(A38&lt;$B$4,SUMPRODUCT(L38:$L$75,K38:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A38,$B$5)+1)-$M$76)-IF(A38&lt;=$B$5,$E$13*(N38-INDEX($N$16:$N$76,$B$5+1)),0))/I38)</f>
+        <v>0.31354783107678375</v>
       </c>
       <c r="P38" s="6">
         <f t="shared" si="6"/>
-        <v>31366</v>
+        <v>31355</v>
       </c>
       <c r="Q38" s="7">
-        <v>31366</v>
+        <v>31355</v>
       </c>
       <c r="R38" s="6">
         <f t="shared" si="7"/>
@@ -10468,7 +10476,7 @@
       </c>
       <c r="H39" s="20">
         <f t="shared" si="9"/>
-        <v>81867.528481342291</v>
+        <v>81869.331364767611</v>
       </c>
       <c r="I39" s="20">
         <f t="shared" si="2"/>
@@ -10476,7 +10484,7 @@
       </c>
       <c r="J39" s="20">
         <f t="shared" si="3"/>
-        <v>46394.102275549987</v>
+        <v>46395.123964607621</v>
       </c>
       <c r="K39" s="20">
         <f t="shared" si="4"/>
@@ -10487,23 +10495,23 @@
         <v>1</v>
       </c>
       <c r="M39" s="20">
-        <f>SUM(I39:$I$77)</f>
-        <v>633852.97028112283</v>
+        <f>SUM(I39:$I$76)</f>
+        <v>633771.6390060758</v>
       </c>
       <c r="N39" s="20">
-        <f>SUM(J39:$J$77)</f>
-        <v>623365.97835462063</v>
+        <f>SUM(J39:$J$76)</f>
+        <v>623376.07611785468</v>
       </c>
       <c r="O39" s="22">
-        <f>IF(I39&lt;=0,0,(IF(A39&lt;$B$4,SUMPRODUCT(L39:$L$76,K39:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A39,$B$5)+1)-$M$77)-IF(A39&lt;=$B$5,$E$13*(N39-INDEX($N$16:$N$77,$B$5+1)),0))/I39)</f>
-        <v>0.31553588508383312</v>
+        <f>IF(I39&lt;=0,0,(IF(A39&lt;$B$4,SUMPRODUCT(L39:$L$75,K39:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A39,$B$5)+1)-$M$76)-IF(A39&lt;=$B$5,$E$13*(N39-INDEX($N$16:$N$76,$B$5+1)),0))/I39)</f>
+        <v>0.3154163127833654</v>
       </c>
       <c r="P39" s="6">
         <f t="shared" si="6"/>
-        <v>31554</v>
+        <v>31542</v>
       </c>
       <c r="Q39" s="7">
-        <v>31554</v>
+        <v>31542</v>
       </c>
       <c r="R39" s="6">
         <f t="shared" si="7"/>
@@ -10540,7 +10548,7 @@
       </c>
       <c r="H40" s="20">
         <f t="shared" si="9"/>
-        <v>80193.108498271409</v>
+        <v>80195.137144922948</v>
       </c>
       <c r="I40" s="20">
         <f t="shared" si="2"/>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="J40" s="20">
         <f t="shared" si="3"/>
-        <v>44336.793264218999</v>
+        <v>44337.914852954986</v>
       </c>
       <c r="K40" s="20">
         <f t="shared" si="4"/>
@@ -10559,23 +10567,23 @@
         <v>1</v>
       </c>
       <c r="M40" s="20">
-        <f>SUM(I40:$I$77)</f>
-        <v>587113.11646121508</v>
+        <f>SUM(I40:$I$76)</f>
+        <v>587031.78518616804</v>
       </c>
       <c r="N40" s="20">
-        <f>SUM(J40:$J$77)</f>
-        <v>576971.87607907073</v>
+        <f>SUM(J40:$J$76)</f>
+        <v>576980.95215324708</v>
       </c>
       <c r="O40" s="22">
-        <f>IF(I40&lt;=0,0,(IF(A40&lt;$B$4,SUMPRODUCT(L40:$L$76,K40:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A40,$B$5)+1)-$M$77)-IF(A40&lt;=$B$5,$E$13*(N40-INDEX($N$16:$N$77,$B$5+1)),0))/I40)</f>
-        <v>0.31710101943440466</v>
+        <f>IF(I40&lt;=0,0,(IF(A40&lt;$B$4,SUMPRODUCT(L40:$L$75,K40:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A40,$B$5)+1)-$M$76)-IF(A40&lt;=$B$5,$E$13*(N40-INDEX($N$16:$N$76,$B$5+1)),0))/I40)</f>
+        <v>0.31697596979013354</v>
       </c>
       <c r="P40" s="6">
         <f t="shared" si="6"/>
-        <v>31710</v>
+        <v>31698</v>
       </c>
       <c r="Q40" s="7">
-        <v>31710</v>
+        <v>31698</v>
       </c>
       <c r="R40" s="6">
         <f t="shared" si="7"/>
@@ -10612,7 +10620,7 @@
       </c>
       <c r="H41" s="20">
         <f t="shared" si="9"/>
-        <v>78411.615307435437</v>
+        <v>78413.891092198639</v>
       </c>
       <c r="I41" s="20">
         <f t="shared" si="2"/>
@@ -10620,7 +10628,7 @@
       </c>
       <c r="J41" s="20">
         <f t="shared" si="3"/>
-        <v>42294.487400347796</v>
+        <v>42295.714937232675</v>
       </c>
       <c r="K41" s="20">
         <f t="shared" si="4"/>
@@ -10631,23 +10639,23 @@
         <v>1</v>
       </c>
       <c r="M41" s="20">
-        <f>SUM(I41:$I$77)</f>
-        <v>542420.53154946107</v>
+        <f>SUM(I41:$I$76)</f>
+        <v>542339.20027441403</v>
       </c>
       <c r="N41" s="20">
-        <f>SUM(J41:$J$77)</f>
-        <v>532635.08281485178</v>
+        <f>SUM(J41:$J$76)</f>
+        <v>532643.03730029194</v>
       </c>
       <c r="O41" s="22">
-        <f>IF(I41&lt;=0,0,(IF(A41&lt;$B$4,SUMPRODUCT(L41:$L$76,K41:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A41,$B$5)+1)-$M$77)-IF(A41&lt;=$B$5,$E$13*(N41-INDEX($N$16:$N$77,$B$5+1)),0))/I41)</f>
-        <v>0.31832623923222281</v>
+        <f>IF(I41&lt;=0,0,(IF(A41&lt;$B$4,SUMPRODUCT(L41:$L$75,K41:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A41,$B$5)+1)-$M$76)-IF(A41&lt;=$B$5,$E$13*(N41-INDEX($N$16:$N$76,$B$5+1)),0))/I41)</f>
+        <v>0.31819522941824102</v>
       </c>
       <c r="P41" s="6">
         <f t="shared" si="6"/>
-        <v>31833</v>
+        <v>31820</v>
       </c>
       <c r="Q41" s="7">
-        <v>31833</v>
+        <v>31820</v>
       </c>
       <c r="R41" s="6">
         <f t="shared" si="7"/>
@@ -10684,7 +10692,7 @@
       </c>
       <c r="H42" s="20">
         <f t="shared" si="9"/>
-        <v>76521.534330309252</v>
+        <v>76524.084065295217</v>
       </c>
       <c r="I42" s="20">
         <f t="shared" si="2"/>
@@ -10692,7 +10700,7 @@
       </c>
       <c r="J42" s="20">
         <f t="shared" si="3"/>
-        <v>40268.28830047691</v>
+        <v>40269.630059556926</v>
       </c>
       <c r="K42" s="20">
         <f t="shared" si="4"/>
@@ -10703,23 +10711,23 @@
         <v>1</v>
       </c>
       <c r="M42" s="20">
-        <f>SUM(I42:$I$77)</f>
-        <v>499761.19424552855</v>
+        <f>SUM(I42:$I$76)</f>
+        <v>499679.86297048151</v>
       </c>
       <c r="N42" s="20">
-        <f>SUM(J42:$J$77)</f>
-        <v>490340.595414504</v>
+        <f>SUM(J42:$J$76)</f>
+        <v>490347.32236305898</v>
       </c>
       <c r="O42" s="22">
-        <f>IF(I42&lt;=0,0,(IF(A42&lt;$B$4,SUMPRODUCT(L42:$L$76,K42:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A42,$B$5)+1)-$M$77)-IF(A42&lt;=$B$5,$E$13*(N42-INDEX($N$16:$N$77,$B$5+1)),0))/I42)</f>
-        <v>0.3191873910688669</v>
+        <f>IF(I42&lt;=0,0,(IF(A42&lt;$B$4,SUMPRODUCT(L42:$L$75,K42:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A42,$B$5)+1)-$M$76)-IF(A42&lt;=$B$5,$E$13*(N42-INDEX($N$16:$N$76,$B$5+1)),0))/I42)</f>
+        <v>0.31904987676246382</v>
       </c>
       <c r="P42" s="6">
         <f t="shared" si="6"/>
-        <v>31919</v>
+        <v>31905</v>
       </c>
       <c r="Q42" s="7">
-        <v>31919</v>
+        <v>31905</v>
       </c>
       <c r="R42" s="6">
         <f t="shared" si="7"/>
@@ -10756,7 +10764,7 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="9"/>
-        <v>74516.313655742357</v>
+        <v>74519.171068280775</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="2"/>
@@ -10764,7 +10772,7 @@
       </c>
       <c r="J43" s="20">
         <f t="shared" si="3"/>
-        <v>38256.655177973415</v>
+        <v>38258.122172794014</v>
       </c>
       <c r="K43" s="20">
         <f t="shared" si="4"/>
@@ -10775,23 +10783,23 @@
         <v>1</v>
       </c>
       <c r="M43" s="20">
-        <f>SUM(I43:$I$77)</f>
-        <v>459119.66398619488</v>
+        <f>SUM(I43:$I$76)</f>
+        <v>459038.33271114784</v>
       </c>
       <c r="N43" s="20">
-        <f>SUM(J43:$J$77)</f>
-        <v>450072.30711402703</v>
+        <f>SUM(J43:$J$76)</f>
+        <v>450077.692303502</v>
       </c>
       <c r="O43" s="22">
-        <f>IF(I43&lt;=0,0,(IF(A43&lt;$B$4,SUMPRODUCT(L43:$L$76,K43:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A43,$B$5)+1)-$M$77)-IF(A43&lt;=$B$5,$E$13*(N43-INDEX($N$16:$N$77,$B$5+1)),0))/I43)</f>
-        <v>0.31967149377525272</v>
+        <f>IF(I43&lt;=0,0,(IF(A43&lt;$B$4,SUMPRODUCT(L43:$L$75,K43:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A43,$B$5)+1)-$M$76)-IF(A43&lt;=$B$5,$E$13*(N43-INDEX($N$16:$N$76,$B$5+1)),0))/I43)</f>
+        <v>0.31952684847646823</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="6"/>
-        <v>31967</v>
+        <v>31953</v>
       </c>
       <c r="Q43" s="7">
-        <v>31967</v>
+        <v>31953</v>
       </c>
       <c r="R43" s="6">
         <f t="shared" si="7"/>
@@ -10828,7 +10836,7 @@
       </c>
       <c r="H44" s="20">
         <f t="shared" si="9"/>
-        <v>72383.801745158213</v>
+        <v>72387.00443097479</v>
       </c>
       <c r="I44" s="20">
         <f t="shared" si="2"/>
@@ -10836,7 +10844,7 @@
       </c>
       <c r="J44" s="20">
         <f t="shared" si="3"/>
-        <v>36255.438187978216</v>
+        <v>36257.042342151646</v>
       </c>
       <c r="K44" s="20">
         <f t="shared" si="4"/>
@@ -10847,23 +10855,23 @@
         <v>1</v>
       </c>
       <c r="M44" s="20">
-        <f>SUM(I44:$I$77)</f>
-        <v>420481.75531071506</v>
+        <f>SUM(I44:$I$76)</f>
+        <v>420400.42403566802</v>
       </c>
       <c r="N44" s="20">
-        <f>SUM(J44:$J$77)</f>
-        <v>411815.65193605365</v>
+        <f>SUM(J44:$J$76)</f>
+        <v>411819.57013070799</v>
       </c>
       <c r="O44" s="22">
-        <f>IF(I44&lt;=0,0,(IF(A44&lt;$B$4,SUMPRODUCT(L44:$L$76,K44:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A44,$B$5)+1)-$M$77)-IF(A44&lt;=$B$5,$E$13*(N44-INDEX($N$16:$N$77,$B$5+1)),0))/I44)</f>
-        <v>0.31977775244915946</v>
+        <f>IF(I44&lt;=0,0,(IF(A44&lt;$B$4,SUMPRODUCT(L44:$L$75,K44:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A44,$B$5)+1)-$M$76)-IF(A44&lt;=$B$5,$E$13*(N44-INDEX($N$16:$N$76,$B$5+1)),0))/I44)</f>
+        <v>0.31962523762767581</v>
       </c>
       <c r="P44" s="6">
         <f t="shared" si="6"/>
-        <v>31978</v>
+        <v>31963</v>
       </c>
       <c r="Q44" s="7">
-        <v>31978</v>
+        <v>31963</v>
       </c>
       <c r="R44" s="6">
         <f t="shared" si="7"/>
@@ -10900,7 +10908,7 @@
       </c>
       <c r="H45" s="20">
         <f t="shared" si="9"/>
-        <v>70111.400350264055</v>
+        <v>70114.988799704923</v>
       </c>
       <c r="I45" s="20">
         <f t="shared" si="2"/>
@@ -10908,7 +10916,7 @@
       </c>
       <c r="J45" s="20">
         <f t="shared" si="3"/>
-        <v>34260.724696402525</v>
+        <v>34262.478232600151</v>
       </c>
       <c r="K45" s="20">
         <f t="shared" si="4"/>
@@ -10919,23 +10927,23 @@
         <v>1</v>
       </c>
       <c r="M45" s="20">
-        <f>SUM(I45:$I$77)</f>
-        <v>383837.50139227766</v>
+        <f>SUM(I45:$I$76)</f>
+        <v>383756.17011723062</v>
       </c>
       <c r="N45" s="20">
-        <f>SUM(J45:$J$77)</f>
-        <v>375560.21374807548</v>
+        <f>SUM(J45:$J$76)</f>
+        <v>375562.52778855647</v>
       </c>
       <c r="O45" s="22">
-        <f>IF(I45&lt;=0,0,(IF(A45&lt;$B$4,SUMPRODUCT(L45:$L$76,K45:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A45,$B$5)+1)-$M$77)-IF(A45&lt;=$B$5,$E$13*(N45-INDEX($N$16:$N$77,$B$5+1)),0))/I45)</f>
-        <v>0.31950767979870071</v>
+        <f>IF(I45&lt;=0,0,(IF(A45&lt;$B$4,SUMPRODUCT(L45:$L$75,K45:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A45,$B$5)+1)-$M$76)-IF(A45&lt;=$B$5,$E$13*(N45-INDEX($N$16:$N$76,$B$5+1)),0))/I45)</f>
+        <v>0.31934641729667107</v>
       </c>
       <c r="P45" s="6">
         <f t="shared" si="6"/>
-        <v>31951</v>
+        <v>31935</v>
       </c>
       <c r="Q45" s="7">
-        <v>31951</v>
+        <v>31935</v>
       </c>
       <c r="R45" s="6">
         <f t="shared" si="7"/>
@@ -10972,7 +10980,7 @@
       </c>
       <c r="H46" s="20">
         <f t="shared" si="9"/>
-        <v>67694.055738688898</v>
+        <v>67698.068647821274</v>
       </c>
       <c r="I46" s="20">
         <f t="shared" si="2"/>
@@ -10980,7 +10988,7 @@
       </c>
       <c r="J46" s="20">
         <f t="shared" si="3"/>
-        <v>32272.645903652869</v>
+        <v>32274.559028728025</v>
       </c>
       <c r="K46" s="20">
         <f t="shared" si="4"/>
@@ -10991,23 +10999,23 @@
         <v>1</v>
       </c>
       <c r="M46" s="20">
-        <f>SUM(I46:$I$77)</f>
-        <v>349181.01414675405</v>
+        <f>SUM(I46:$I$76)</f>
+        <v>349099.68287170702</v>
       </c>
       <c r="N46" s="20">
-        <f>SUM(J46:$J$77)</f>
-        <v>341299.48905167292</v>
+        <f>SUM(J46:$J$76)</f>
+        <v>341300.04955595633</v>
       </c>
       <c r="O46" s="22">
-        <f>IF(I46&lt;=0,0,(IF(A46&lt;$B$4,SUMPRODUCT(L46:$L$76,K46:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A46,$B$5)+1)-$M$77)-IF(A46&lt;=$B$5,$E$13*(N46-INDEX($N$16:$N$77,$B$5+1)),0))/I46)</f>
-        <v>0.3188511438723402</v>
+        <f>IF(I46&lt;=0,0,(IF(A46&lt;$B$4,SUMPRODUCT(L46:$L$75,K46:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A46,$B$5)+1)-$M$76)-IF(A46&lt;=$B$5,$E$13*(N46-INDEX($N$16:$N$76,$B$5+1)),0))/I46)</f>
+        <v>0.31868009871360498</v>
       </c>
       <c r="P46" s="6">
         <f t="shared" si="6"/>
-        <v>31885</v>
+        <v>31868</v>
       </c>
       <c r="Q46" s="7">
-        <v>31885</v>
+        <v>31868</v>
       </c>
       <c r="R46" s="6">
         <f t="shared" si="7"/>
@@ -11044,7 +11052,7 @@
       </c>
       <c r="H47" s="20">
         <f t="shared" si="9"/>
-        <v>65132.228604667063</v>
+        <v>65136.774487252987</v>
       </c>
       <c r="I47" s="20">
         <f t="shared" si="2"/>
@@ -11052,7 +11060,7 @@
       </c>
       <c r="J47" s="20">
         <f t="shared" si="3"/>
-        <v>30293.964445668131</v>
+        <v>30296.078803005232</v>
       </c>
       <c r="K47" s="20">
         <f t="shared" si="4"/>
@@ -11063,23 +11071,23 @@
         <v>1</v>
       </c>
       <c r="M47" s="20">
-        <f>SUM(I47:$I$77)</f>
-        <v>316506.64975025284</v>
+        <f>SUM(I47:$I$76)</f>
+        <v>316425.3184752058</v>
       </c>
       <c r="N47" s="20">
-        <f>SUM(J47:$J$77)</f>
-        <v>309026.84314802004</v>
+        <f>SUM(J47:$J$76)</f>
+        <v>309025.49052722834</v>
       </c>
       <c r="O47" s="22">
-        <f>IF(I47&lt;=0,0,(IF(A47&lt;$B$4,SUMPRODUCT(L47:$L$76,K47:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A47,$B$5)+1)-$M$77)-IF(A47&lt;=$B$5,$E$13*(N47-INDEX($N$16:$N$77,$B$5+1)),0))/I47)</f>
-        <v>0.31777865130729654</v>
+        <f>IF(I47&lt;=0,0,(IF(A47&lt;$B$4,SUMPRODUCT(L47:$L$75,K47:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A47,$B$5)+1)-$M$76)-IF(A47&lt;=$B$5,$E$13*(N47-INDEX($N$16:$N$76,$B$5+1)),0))/I47)</f>
+        <v>0.31759662877116751</v>
       </c>
       <c r="P47" s="6">
         <f t="shared" si="6"/>
-        <v>31778</v>
+        <v>31760</v>
       </c>
       <c r="Q47" s="7">
-        <v>31778</v>
+        <v>31760</v>
       </c>
       <c r="R47" s="6">
         <f t="shared" si="7"/>
@@ -11107,7 +11115,7 @@
         <v>1.175E-3</v>
       </c>
       <c r="F48" s="19">
-        <f t="shared" ref="F48:F77" si="11">MIN(1,C48+D48-C48*D48/2)</f>
+        <f t="shared" ref="F48:F76" si="11">MIN(1,C48+D48-C48*D48/2)</f>
         <v>4.3123172360000003E-2</v>
       </c>
       <c r="G48" s="20">
@@ -11116,42 +11124,42 @@
       </c>
       <c r="H48" s="20">
         <f t="shared" si="9"/>
-        <v>62454.268463173365</v>
+        <v>62459.374879814619</v>
       </c>
       <c r="I48" s="20">
-        <f t="shared" ref="I48:I77" si="12">G48*현가율^A48</f>
+        <f t="shared" ref="I48:I76" si="12">G48*현가율^A48</f>
         <v>28755.964260434142</v>
       </c>
       <c r="J48" s="20">
-        <f t="shared" ref="J48:J77" si="13">H48*현가율^A48</f>
-        <v>28339.907815011549</v>
+        <f t="shared" ref="J48:J76" si="13">H48*현가율^A48</f>
+        <v>28342.224956504666</v>
       </c>
       <c r="K48" s="20">
-        <f t="shared" ref="K48:K77" si="14">G48*D48*현가율^(A48+0.5)</f>
+        <f t="shared" ref="K48:K76" si="14">G48*D48*현가율^(A48+0.5)</f>
         <v>631.91254657612706</v>
       </c>
       <c r="L48" s="21">
-        <f t="shared" ref="L48:L77" si="15">IF(A48=0,$B$7,1)</f>
+        <f t="shared" ref="L48:L76" si="15">IF(A48=0,$B$7,1)</f>
         <v>1</v>
       </c>
       <c r="M48" s="20">
-        <f>SUM(I48:$I$77)</f>
-        <v>285802.80415164778</v>
+        <f>SUM(I48:$I$76)</f>
+        <v>285721.47287660075</v>
       </c>
       <c r="N48" s="20">
-        <f>SUM(J48:$J$77)</f>
-        <v>278732.87870235182</v>
+        <f>SUM(J48:$J$76)</f>
+        <v>278729.41172422312</v>
       </c>
       <c r="O48" s="22">
-        <f>IF(I48&lt;=0,0,(IF(A48&lt;$B$4,SUMPRODUCT(L48:$L$76,K48:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A48,$B$5)+1)-$M$77)-IF(A48&lt;=$B$5,$E$13*(N48-INDEX($N$16:$N$77,$B$5+1)),0))/I48)</f>
-        <v>0.3162380436765313</v>
+        <f>IF(I48&lt;=0,0,(IF(A48&lt;$B$4,SUMPRODUCT(L48:$L$75,K48:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A48,$B$5)+1)-$M$76)-IF(A48&lt;=$B$5,$E$13*(N48-INDEX($N$16:$N$76,$B$5+1)),0))/I48)</f>
+        <v>0.31604369123562004</v>
       </c>
       <c r="P48" s="6">
         <f t="shared" ref="P48:P79" si="16">ROUND(O48*100000,0)</f>
-        <v>31624</v>
+        <v>31604</v>
       </c>
       <c r="Q48" s="7">
-        <v>31624</v>
+        <v>31604</v>
       </c>
       <c r="R48" s="6">
         <f t="shared" ref="R48:R79" si="17">P48-Q48</f>
@@ -11183,12 +11191,12 @@
         <v>4.6015356275000002E-2</v>
       </c>
       <c r="G49" s="20">
-        <f t="shared" ref="G49:G77" si="18">G48*MAX(0,1-F48)</f>
+        <f t="shared" ref="G49:G76" si="18">G48*MAX(0,1-F48)</f>
         <v>60638.390469594946</v>
       </c>
       <c r="H49" s="20">
-        <f t="shared" ref="H49:H77" si="19">H48*MAX(0,1-F48-E48+F48*E48/2)</f>
-        <v>59689.240784556838</v>
+        <f t="shared" ref="H49:H76" si="19">H48*MAX(0,1-MIN(1,C48+(1-(1-D48)*(1-E48))-C48*(1-(1-D48)*(1-E48))/2))</f>
+        <v>59694.928896422469</v>
       </c>
       <c r="I49" s="20">
         <f t="shared" si="12"/>
@@ -11196,7 +11204,7 @@
       </c>
       <c r="J49" s="20">
         <f t="shared" si="13"/>
-        <v>26424.604567472357</v>
+        <v>26427.122711526616</v>
       </c>
       <c r="K49" s="20">
         <f t="shared" si="14"/>
@@ -11207,23 +11215,23 @@
         <v>1</v>
       </c>
       <c r="M49" s="20">
-        <f>SUM(I49:$I$77)</f>
-        <v>257046.83989121357</v>
+        <f>SUM(I49:$I$76)</f>
+        <v>256965.50861616654</v>
       </c>
       <c r="N49" s="20">
-        <f>SUM(J49:$J$77)</f>
-        <v>250392.97088734031</v>
+        <f>SUM(J49:$J$76)</f>
+        <v>250387.18676771852</v>
       </c>
       <c r="O49" s="22">
-        <f>IF(I49&lt;=0,0,(IF(A49&lt;$B$4,SUMPRODUCT(L49:$L$76,K49:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A49,$B$5)+1)-$M$77)-IF(A49&lt;=$B$5,$E$13*(N49-INDEX($N$16:$N$77,$B$5+1)),0))/I49)</f>
-        <v>0.31414138457287311</v>
+        <f>IF(I49&lt;=0,0,(IF(A49&lt;$B$4,SUMPRODUCT(L49:$L$75,K49:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A49,$B$5)+1)-$M$76)-IF(A49&lt;=$B$5,$E$13*(N49-INDEX($N$16:$N$76,$B$5+1)),0))/I49)</f>
+        <v>0.31393319554981419</v>
       </c>
       <c r="P49" s="6">
         <f t="shared" si="16"/>
-        <v>31414</v>
+        <v>31393</v>
       </c>
       <c r="Q49" s="7">
-        <v>31414</v>
+        <v>31393</v>
       </c>
       <c r="R49" s="6">
         <f t="shared" si="17"/>
@@ -11260,7 +11268,7 @@
       </c>
       <c r="H50" s="20">
         <f t="shared" si="19"/>
-        <v>56870.482298730079</v>
+        <v>56876.764475438387</v>
       </c>
       <c r="I50" s="20">
         <f t="shared" si="12"/>
@@ -11268,7 +11276,7 @@
       </c>
       <c r="J50" s="20">
         <f t="shared" si="13"/>
-        <v>24562.665166269078</v>
+        <v>24565.378471955337</v>
       </c>
       <c r="K50" s="20">
         <f t="shared" si="14"/>
@@ -11279,23 +11287,23 @@
         <v>1</v>
       </c>
       <c r="M50" s="20">
-        <f>SUM(I50:$I$77)</f>
-        <v>230202.04393291753</v>
+        <f>SUM(I50:$I$76)</f>
+        <v>230120.71265787049</v>
       </c>
       <c r="N50" s="20">
-        <f>SUM(J50:$J$77)</f>
-        <v>223968.36631986796</v>
+        <f>SUM(J50:$J$76)</f>
+        <v>223960.06405619188</v>
       </c>
       <c r="O50" s="22">
-        <f>IF(I50&lt;=0,0,(IF(A50&lt;$B$4,SUMPRODUCT(L50:$L$76,K50:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A50,$B$5)+1)-$M$77)-IF(A50&lt;=$B$5,$E$13*(N50-INDEX($N$16:$N$77,$B$5+1)),0))/I50)</f>
-        <v>0.31137118636498901</v>
+        <f>IF(I50&lt;=0,0,(IF(A50&lt;$B$4,SUMPRODUCT(L50:$L$75,K50:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A50,$B$5)+1)-$M$76)-IF(A50&lt;=$B$5,$E$13*(N50-INDEX($N$16:$N$76,$B$5+1)),0))/I50)</f>
+        <v>0.31114749958969451</v>
       </c>
       <c r="P50" s="6">
         <f t="shared" si="16"/>
-        <v>31137</v>
+        <v>31115</v>
       </c>
       <c r="Q50" s="7">
-        <v>31137</v>
+        <v>31115</v>
       </c>
       <c r="R50" s="6">
         <f t="shared" si="17"/>
@@ -11332,7 +11340,7 @@
       </c>
       <c r="H51" s="20">
         <f t="shared" si="19"/>
-        <v>54026.845845416625</v>
+        <v>54033.723560711835</v>
       </c>
       <c r="I51" s="20">
         <f t="shared" si="12"/>
@@ -11340,7 +11348,7 @@
       </c>
       <c r="J51" s="20">
         <f t="shared" si="13"/>
-        <v>22765.34964722965</v>
+        <v>22768.247717457878</v>
       </c>
       <c r="K51" s="20">
         <f t="shared" si="14"/>
@@ -11351,23 +11359,23 @@
         <v>1</v>
       </c>
       <c r="M51" s="20">
-        <f>SUM(I51:$I$77)</f>
-        <v>205217.14333960495</v>
+        <f>SUM(I51:$I$76)</f>
+        <v>205135.81206455792</v>
       </c>
       <c r="N51" s="20">
-        <f>SUM(J51:$J$77)</f>
-        <v>199405.70115359884</v>
+        <f>SUM(J51:$J$76)</f>
+        <v>199394.68558423655</v>
       </c>
       <c r="O51" s="22">
-        <f>IF(I51&lt;=0,0,(IF(A51&lt;$B$4,SUMPRODUCT(L51:$L$76,K51:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A51,$B$5)+1)-$M$77)-IF(A51&lt;=$B$5,$E$13*(N51-INDEX($N$16:$N$77,$B$5+1)),0))/I51)</f>
-        <v>0.30780175322079895</v>
+        <f>IF(I51&lt;=0,0,(IF(A51&lt;$B$4,SUMPRODUCT(L51:$L$75,K51:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A51,$B$5)+1)-$M$76)-IF(A51&lt;=$B$5,$E$13*(N51-INDEX($N$16:$N$76,$B$5+1)),0))/I51)</f>
+        <v>0.30756072676480822</v>
       </c>
       <c r="P51" s="6">
         <f t="shared" si="16"/>
-        <v>30780</v>
+        <v>30756</v>
       </c>
       <c r="Q51" s="7">
-        <v>30780</v>
+        <v>30756</v>
       </c>
       <c r="R51" s="6">
         <f t="shared" si="17"/>
@@ -11404,7 +11412,7 @@
       </c>
       <c r="H52" s="20">
         <f t="shared" si="19"/>
-        <v>51170.458866533794</v>
+        <v>51177.922691144784</v>
       </c>
       <c r="I52" s="20">
         <f t="shared" si="12"/>
@@ -11412,7 +11420,7 @@
       </c>
       <c r="J52" s="20">
         <f t="shared" si="13"/>
-        <v>21035.854458471556</v>
+        <v>21038.922789920955</v>
       </c>
       <c r="K52" s="20">
         <f t="shared" si="14"/>
@@ -11423,23 +11431,23 @@
         <v>1</v>
       </c>
       <c r="M52" s="20">
-        <f>SUM(I52:$I$77)</f>
-        <v>182029.68110936807</v>
+        <f>SUM(I52:$I$76)</f>
+        <v>181948.34983432104</v>
       </c>
       <c r="N52" s="20">
-        <f>SUM(J52:$J$77)</f>
-        <v>176640.35150636919</v>
+        <f>SUM(J52:$J$76)</f>
+        <v>176626.43786677864</v>
       </c>
       <c r="O52" s="22">
-        <f>IF(I52&lt;=0,0,(IF(A52&lt;$B$4,SUMPRODUCT(L52:$L$76,K52:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A52,$B$5)+1)-$M$77)-IF(A52&lt;=$B$5,$E$13*(N52-INDEX($N$16:$N$77,$B$5+1)),0))/I52)</f>
-        <v>0.30334934413777737</v>
+        <f>IF(I52&lt;=0,0,(IF(A52&lt;$B$4,SUMPRODUCT(L52:$L$75,K52:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A52,$B$5)+1)-$M$76)-IF(A52&lt;=$B$5,$E$13*(N52-INDEX($N$16:$N$76,$B$5+1)),0))/I52)</f>
+        <v>0.30308886222544751</v>
       </c>
       <c r="P52" s="6">
         <f t="shared" si="16"/>
-        <v>30335</v>
+        <v>30309</v>
       </c>
       <c r="Q52" s="7">
-        <v>30335</v>
+        <v>30309</v>
       </c>
       <c r="R52" s="6">
         <f t="shared" si="17"/>
@@ -11476,7 +11484,7 @@
       </c>
       <c r="H53" s="20">
         <f t="shared" si="19"/>
-        <v>48292.480571559463</v>
+        <v>48300.506219126815</v>
       </c>
       <c r="I53" s="20">
         <f t="shared" si="12"/>
@@ -11484,7 +11492,7 @@
       </c>
       <c r="J53" s="20">
         <f t="shared" si="13"/>
-        <v>19368.522581083587</v>
+        <v>19371.741403854674</v>
       </c>
       <c r="K53" s="20">
         <f t="shared" si="14"/>
@@ -11495,23 +11503,23 @@
         <v>1</v>
       </c>
       <c r="M53" s="20">
-        <f>SUM(I53:$I$77)</f>
-        <v>160574.09597954855</v>
+        <f>SUM(I53:$I$76)</f>
+        <v>160492.76470450152</v>
       </c>
       <c r="N53" s="20">
-        <f>SUM(J53:$J$77)</f>
-        <v>155604.49704789766</v>
+        <f>SUM(J53:$J$76)</f>
+        <v>155587.51507685767</v>
       </c>
       <c r="O53" s="22">
-        <f>IF(I53&lt;=0,0,(IF(A53&lt;$B$4,SUMPRODUCT(L53:$L$76,K53:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A53,$B$5)+1)-$M$77)-IF(A53&lt;=$B$5,$E$13*(N53-INDEX($N$16:$N$77,$B$5+1)),0))/I53)</f>
-        <v>0.29799779280749328</v>
+        <f>IF(I53&lt;=0,0,(IF(A53&lt;$B$4,SUMPRODUCT(L53:$L$75,K53:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A53,$B$5)+1)-$M$76)-IF(A53&lt;=$B$5,$E$13*(N53-INDEX($N$16:$N$76,$B$5+1)),0))/I53)</f>
+        <v>0.29771529293981291</v>
       </c>
       <c r="P53" s="6">
         <f t="shared" si="16"/>
-        <v>29800</v>
+        <v>29772</v>
       </c>
       <c r="Q53" s="7">
-        <v>29800</v>
+        <v>29772</v>
       </c>
       <c r="R53" s="6">
         <f t="shared" si="17"/>
@@ -11548,7 +11556,7 @@
       </c>
       <c r="H54" s="20">
         <f t="shared" si="19"/>
-        <v>45371.721691841965</v>
+        <v>45380.270996650659</v>
       </c>
       <c r="I54" s="20">
         <f t="shared" si="12"/>
@@ -11556,7 +11564,7 @@
       </c>
       <c r="J54" s="20">
         <f t="shared" si="13"/>
-        <v>17753.270674962736</v>
+        <v>17756.615889045253</v>
       </c>
       <c r="K54" s="20">
         <f t="shared" si="14"/>
@@ -11567,23 +11575,23 @@
         <v>1</v>
       </c>
       <c r="M54" s="20">
-        <f>SUM(I54:$I$77)</f>
-        <v>140790.75274947006</v>
+        <f>SUM(I54:$I$76)</f>
+        <v>140709.42147442303</v>
       </c>
       <c r="N54" s="20">
-        <f>SUM(J54:$J$77)</f>
-        <v>136235.97446681405</v>
+        <f>SUM(J54:$J$76)</f>
+        <v>136215.77367300299</v>
       </c>
       <c r="O54" s="22">
-        <f>IF(I54&lt;=0,0,(IF(A54&lt;$B$4,SUMPRODUCT(L54:$L$76,K54:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A54,$B$5)+1)-$M$77)-IF(A54&lt;=$B$5,$E$13*(N54-INDEX($N$16:$N$77,$B$5+1)),0))/I54)</f>
-        <v>0.29177698236217259</v>
+        <f>IF(I54&lt;=0,0,(IF(A54&lt;$B$4,SUMPRODUCT(L54:$L$75,K54:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A54,$B$5)+1)-$M$76)-IF(A54&lt;=$B$5,$E$13*(N54-INDEX($N$16:$N$76,$B$5+1)),0))/I54)</f>
+        <v>0.29146923650536111</v>
       </c>
       <c r="P54" s="6">
         <f t="shared" si="16"/>
-        <v>29178</v>
+        <v>29147</v>
       </c>
       <c r="Q54" s="7">
-        <v>29178</v>
+        <v>29147</v>
       </c>
       <c r="R54" s="6">
         <f t="shared" si="17"/>
@@ -11620,7 +11628,7 @@
       </c>
       <c r="H55" s="20">
         <f t="shared" si="19"/>
-        <v>42391.945145259604</v>
+        <v>42400.965021732503</v>
       </c>
       <c r="I55" s="20">
         <f t="shared" si="12"/>
@@ -11628,7 +11636,7 @@
       </c>
       <c r="J55" s="20">
         <f t="shared" si="13"/>
-        <v>16182.760034467521</v>
+        <v>16186.203294643512</v>
       </c>
       <c r="K55" s="20">
         <f t="shared" si="14"/>
@@ -11639,23 +11647,23 @@
         <v>1</v>
       </c>
       <c r="M55" s="20">
-        <f>SUM(I55:$I$77)</f>
-        <v>122630.33979484586</v>
+        <f>SUM(I55:$I$76)</f>
+        <v>122549.00851979882</v>
       </c>
       <c r="N55" s="20">
-        <f>SUM(J55:$J$77)</f>
-        <v>118482.70379185132</v>
+        <f>SUM(J55:$J$76)</f>
+        <v>118459.15778395781</v>
       </c>
       <c r="O55" s="22">
-        <f>IF(I55&lt;=0,0,(IF(A55&lt;$B$4,SUMPRODUCT(L55:$L$76,K55:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A55,$B$5)+1)-$M$77)-IF(A55&lt;=$B$5,$E$13*(N55-INDEX($N$16:$N$77,$B$5+1)),0))/I55)</f>
-        <v>0.28464649104387268</v>
+        <f>IF(I55&lt;=0,0,(IF(A55&lt;$B$4,SUMPRODUCT(L55:$L$75,K55:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A55,$B$5)+1)-$M$76)-IF(A55&lt;=$B$5,$E$13*(N55-INDEX($N$16:$N$76,$B$5+1)),0))/I55)</f>
+        <v>0.28430939507005087</v>
       </c>
       <c r="P55" s="6">
         <f t="shared" si="16"/>
-        <v>28465</v>
+        <v>28431</v>
       </c>
       <c r="Q55" s="7">
-        <v>28465</v>
+        <v>28431</v>
       </c>
       <c r="R55" s="6">
         <f t="shared" si="17"/>
@@ -11692,7 +11700,7 @@
       </c>
       <c r="H56" s="20">
         <f t="shared" si="19"/>
-        <v>39353.841126284431</v>
+        <v>39363.264775186391</v>
       </c>
       <c r="I56" s="20">
         <f t="shared" si="12"/>
@@ -11700,7 +11708,7 @@
       </c>
       <c r="J56" s="20">
         <f t="shared" si="13"/>
-        <v>14656.575595566481</v>
+        <v>14660.085251004548</v>
       </c>
       <c r="K56" s="20">
         <f t="shared" si="14"/>
@@ -11711,23 +11719,23 @@
         <v>1</v>
       </c>
       <c r="M56" s="20">
-        <f>SUM(I56:$I$77)</f>
-        <v>106051.10931217464</v>
+        <f>SUM(I56:$I$76)</f>
+        <v>105969.7780371276</v>
       </c>
       <c r="N56" s="20">
-        <f>SUM(J56:$J$77)</f>
-        <v>102299.94375738381</v>
+        <f>SUM(J56:$J$76)</f>
+        <v>102272.95448931429</v>
       </c>
       <c r="O56" s="22">
-        <f>IF(I56&lt;=0,0,(IF(A56&lt;$B$4,SUMPRODUCT(L56:$L$76,K56:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A56,$B$5)+1)-$M$77)-IF(A56&lt;=$B$5,$E$13*(N56-INDEX($N$16:$N$77,$B$5+1)),0))/I56)</f>
-        <v>0.27649939287656528</v>
+        <f>IF(I56&lt;=0,0,(IF(A56&lt;$B$4,SUMPRODUCT(L56:$L$75,K56:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A56,$B$5)+1)-$M$76)-IF(A56&lt;=$B$5,$E$13*(N56-INDEX($N$16:$N$76,$B$5+1)),0))/I56)</f>
+        <v>0.27612778192025256</v>
       </c>
       <c r="P56" s="6">
         <f t="shared" si="16"/>
-        <v>27650</v>
+        <v>27613</v>
       </c>
       <c r="Q56" s="7">
-        <v>27650</v>
+        <v>27613</v>
       </c>
       <c r="R56" s="6">
         <f t="shared" si="17"/>
@@ -11764,7 +11772,7 @@
       </c>
       <c r="H57" s="20">
         <f t="shared" si="19"/>
-        <v>36273.993303760573</v>
+        <v>36283.743676059945</v>
       </c>
       <c r="I57" s="20">
         <f t="shared" si="12"/>
@@ -11772,7 +11780,7 @@
       </c>
       <c r="J57" s="20">
         <f t="shared" si="13"/>
-        <v>13180.044829394725</v>
+        <v>13183.587597430569</v>
       </c>
       <c r="K57" s="20">
         <f t="shared" si="14"/>
@@ -11783,23 +11791,23 @@
         <v>1</v>
       </c>
       <c r="M57" s="20">
-        <f>SUM(I57:$I$77)</f>
-        <v>91011.746909549984</v>
+        <f>SUM(I57:$I$76)</f>
+        <v>90930.415634502948</v>
       </c>
       <c r="N57" s="20">
-        <f>SUM(J57:$J$77)</f>
-        <v>87643.368161817314</v>
+        <f>SUM(J57:$J$76)</f>
+        <v>87612.869238309766</v>
       </c>
       <c r="O57" s="22">
-        <f>IF(I57&lt;=0,0,(IF(A57&lt;$B$4,SUMPRODUCT(L57:$L$76,K57:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A57,$B$5)+1)-$M$77)-IF(A57&lt;=$B$5,$E$13*(N57-INDEX($N$16:$N$77,$B$5+1)),0))/I57)</f>
-        <v>0.2672785886292155</v>
+        <f>IF(I57&lt;=0,0,(IF(A57&lt;$B$4,SUMPRODUCT(L57:$L$75,K57:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A57,$B$5)+1)-$M$76)-IF(A57&lt;=$B$5,$E$13*(N57-INDEX($N$16:$N$76,$B$5+1)),0))/I57)</f>
+        <v>0.2668660226903467</v>
       </c>
       <c r="P57" s="6">
         <f t="shared" si="16"/>
-        <v>26728</v>
+        <v>26687</v>
       </c>
       <c r="Q57" s="7">
-        <v>26728</v>
+        <v>26687</v>
       </c>
       <c r="R57" s="6">
         <f t="shared" si="17"/>
@@ -11836,7 +11844,7 @@
       </c>
       <c r="H58" s="20">
         <f t="shared" si="19"/>
-        <v>33180.323772403499</v>
+        <v>33190.289423591792</v>
       </c>
       <c r="I58" s="20">
         <f t="shared" si="12"/>
@@ -11844,7 +11852,7 @@
       </c>
       <c r="J58" s="20">
         <f t="shared" si="13"/>
-        <v>11761.921405878766</v>
+        <v>11765.454078038299</v>
       </c>
       <c r="K58" s="20">
         <f t="shared" si="14"/>
@@ -11855,23 +11863,23 @@
         <v>1</v>
       </c>
       <c r="M58" s="20">
-        <f>SUM(I58:$I$77)</f>
-        <v>77465.326038996922</v>
+        <f>SUM(I58:$I$76)</f>
+        <v>77383.994763949886</v>
       </c>
       <c r="N58" s="20">
-        <f>SUM(J58:$J$77)</f>
-        <v>74463.323332422602</v>
+        <f>SUM(J58:$J$76)</f>
+        <v>74429.281640879199</v>
       </c>
       <c r="O58" s="22">
-        <f>IF(I58&lt;=0,0,(IF(A58&lt;$B$4,SUMPRODUCT(L58:$L$76,K58:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A58,$B$5)+1)-$M$77)-IF(A58&lt;=$B$5,$E$13*(N58-INDEX($N$16:$N$77,$B$5+1)),0))/I58)</f>
-        <v>0.25708532715950572</v>
+        <f>IF(I58&lt;=0,0,(IF(A58&lt;$B$4,SUMPRODUCT(L58:$L$75,K58:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A58,$B$5)+1)-$M$76)-IF(A58&lt;=$B$5,$E$13*(N58-INDEX($N$16:$N$76,$B$5+1)),0))/I58)</f>
+        <v>0.25662379253078682</v>
       </c>
       <c r="P58" s="6">
         <f t="shared" si="16"/>
-        <v>25709</v>
+        <v>25662</v>
       </c>
       <c r="Q58" s="7">
-        <v>25709</v>
+        <v>25662</v>
       </c>
       <c r="R58" s="6">
         <f t="shared" si="17"/>
@@ -11908,7 +11916,7 @@
       </c>
       <c r="H59" s="20">
         <f t="shared" si="19"/>
-        <v>30102.780640637789</v>
+        <v>30112.833348394222</v>
       </c>
       <c r="I59" s="20">
         <f t="shared" si="12"/>
@@ -11916,7 +11924,7 @@
       </c>
       <c r="J59" s="20">
         <f t="shared" si="13"/>
-        <v>10410.711272587201</v>
+        <v>10414.187889555224</v>
       </c>
       <c r="K59" s="20">
         <f t="shared" si="14"/>
@@ -11927,23 +11935,23 @@
         <v>1</v>
       </c>
       <c r="M59" s="20">
-        <f>SUM(I59:$I$77)</f>
-        <v>65356.176482254821</v>
+        <f>SUM(I59:$I$76)</f>
+        <v>65274.845207207785</v>
       </c>
       <c r="N59" s="20">
-        <f>SUM(J59:$J$77)</f>
-        <v>62701.401926543855</v>
+        <f>SUM(J59:$J$76)</f>
+        <v>62663.827562840852</v>
       </c>
       <c r="O59" s="22">
-        <f>IF(I59&lt;=0,0,(IF(A59&lt;$B$4,SUMPRODUCT(L59:$L$76,K59:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A59,$B$5)+1)-$M$77)-IF(A59&lt;=$B$5,$E$13*(N59-INDEX($N$16:$N$77,$B$5+1)),0))/I59)</f>
-        <v>0.24620114407714069</v>
+        <f>IF(I59&lt;=0,0,(IF(A59&lt;$B$4,SUMPRODUCT(L59:$L$75,K59:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A59,$B$5)+1)-$M$76)-IF(A59&lt;=$B$5,$E$13*(N59-INDEX($N$16:$N$76,$B$5+1)),0))/I59)</f>
+        <v>0.24568060311289669</v>
       </c>
       <c r="P59" s="6">
         <f t="shared" si="16"/>
-        <v>24620</v>
+        <v>24568</v>
       </c>
       <c r="Q59" s="7">
-        <v>24620</v>
+        <v>24568</v>
       </c>
       <c r="R59" s="6">
         <f t="shared" si="17"/>
@@ -11980,7 +11988,7 @@
       </c>
       <c r="H60" s="20">
         <f t="shared" si="19"/>
-        <v>27072.543057345621</v>
+        <v>27082.55348176237</v>
       </c>
       <c r="I60" s="20">
         <f t="shared" si="12"/>
@@ -11988,7 +11996,7 @@
       </c>
       <c r="J60" s="20">
         <f t="shared" si="13"/>
-        <v>9134.3779199968903</v>
+        <v>9137.7554748711573</v>
       </c>
       <c r="K60" s="20">
         <f t="shared" si="14"/>
@@ -11999,23 +12007,23 @@
         <v>1</v>
       </c>
       <c r="M60" s="20">
-        <f>SUM(I60:$I$77)</f>
-        <v>54619.669216416973</v>
+        <f>SUM(I60:$I$76)</f>
+        <v>54538.337941369937</v>
       </c>
       <c r="N60" s="20">
-        <f>SUM(J60:$J$77)</f>
-        <v>52290.69065395667</v>
+        <f>SUM(J60:$J$76)</f>
+        <v>52249.639673285623</v>
       </c>
       <c r="O60" s="22">
-        <f>IF(I60&lt;=0,0,(IF(A60&lt;$B$4,SUMPRODUCT(L60:$L$76,K60:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A60,$B$5)+1)-$M$77)-IF(A60&lt;=$B$5,$E$13*(N60-INDEX($N$16:$N$77,$B$5+1)),0))/I60)</f>
-        <v>0.23497296120310543</v>
+        <f>IF(I60&lt;=0,0,(IF(A60&lt;$B$4,SUMPRODUCT(L60:$L$75,K60:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A60,$B$5)+1)-$M$76)-IF(A60&lt;=$B$5,$E$13*(N60-INDEX($N$16:$N$76,$B$5+1)),0))/I60)</f>
+        <v>0.23438074793769489</v>
       </c>
       <c r="P60" s="6">
         <f t="shared" si="16"/>
-        <v>23497</v>
+        <v>23438</v>
       </c>
       <c r="Q60" s="7">
-        <v>23497</v>
+        <v>23438</v>
       </c>
       <c r="R60" s="6">
         <f t="shared" si="17"/>
@@ -12052,7 +12060,7 @@
       </c>
       <c r="H61" s="20">
         <f t="shared" si="19"/>
-        <v>24120.574148074727</v>
+        <v>24130.428710068707</v>
       </c>
       <c r="I61" s="20">
         <f t="shared" si="12"/>
@@ -12060,7 +12068,7 @@
       </c>
       <c r="J61" s="20">
         <f t="shared" si="13"/>
-        <v>7939.8756094985802</v>
+        <v>7943.1194790656127</v>
       </c>
       <c r="K61" s="20">
         <f t="shared" si="14"/>
@@ -12071,23 +12079,23 @@
         <v>1</v>
       </c>
       <c r="M61" s="20">
-        <f>SUM(I61:$I$77)</f>
-        <v>45182.542135351687</v>
+        <f>SUM(I61:$I$76)</f>
+        <v>45101.210860304651</v>
       </c>
       <c r="N61" s="20">
-        <f>SUM(J61:$J$77)</f>
-        <v>43156.31273395977</v>
+        <f>SUM(J61:$J$76)</f>
+        <v>43111.884198414467</v>
       </c>
       <c r="O61" s="22">
-        <f>IF(I61&lt;=0,0,(IF(A61&lt;$B$4,SUMPRODUCT(L61:$L$76,K61:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A61,$B$5)+1)-$M$77)-IF(A61&lt;=$B$5,$E$13*(N61-INDEX($N$16:$N$77,$B$5+1)),0))/I61)</f>
-        <v>0.22368844274558103</v>
+        <f>IF(I61&lt;=0,0,(IF(A61&lt;$B$4,SUMPRODUCT(L61:$L$75,K61:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A61,$B$5)+1)-$M$76)-IF(A61&lt;=$B$5,$E$13*(N61-INDEX($N$16:$N$76,$B$5+1)),0))/I61)</f>
+        <v>0.22300843856262384</v>
       </c>
       <c r="P61" s="6">
         <f t="shared" si="16"/>
-        <v>22369</v>
+        <v>22301</v>
       </c>
       <c r="Q61" s="7">
-        <v>22369</v>
+        <v>22301</v>
       </c>
       <c r="R61" s="6">
         <f t="shared" si="17"/>
@@ -12124,7 +12132,7 @@
       </c>
       <c r="H62" s="20">
         <f t="shared" si="19"/>
-        <v>21275.294551224859</v>
+        <v>21284.903183483471</v>
       </c>
       <c r="I62" s="20">
         <f t="shared" si="12"/>
@@ -12132,7 +12140,7 @@
       </c>
       <c r="J62" s="20">
         <f t="shared" si="13"/>
-        <v>6832.4706294165107</v>
+        <v>6835.5564009219424</v>
       </c>
       <c r="K62" s="20">
         <f t="shared" si="14"/>
@@ -12143,23 +12151,23 @@
         <v>1</v>
       </c>
       <c r="M62" s="20">
-        <f>SUM(I62:$I$77)</f>
-        <v>36963.781155870645</v>
+        <f>SUM(I62:$I$76)</f>
+        <v>36882.449880823609</v>
       </c>
       <c r="N62" s="20">
-        <f>SUM(J62:$J$77)</f>
-        <v>35216.437124461183</v>
+        <f>SUM(J62:$J$76)</f>
+        <v>35168.764719348852</v>
       </c>
       <c r="O62" s="22">
-        <f>IF(I62&lt;=0,0,(IF(A62&lt;$B$4,SUMPRODUCT(L62:$L$76,K62:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A62,$B$5)+1)-$M$77)-IF(A62&lt;=$B$5,$E$13*(N62-INDEX($N$16:$N$77,$B$5+1)),0))/I62)</f>
-        <v>0.21251481147603943</v>
+        <f>IF(I62&lt;=0,0,(IF(A62&lt;$B$4,SUMPRODUCT(L62:$L$75,K62:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A62,$B$5)+1)-$M$76)-IF(A62&lt;=$B$5,$E$13*(N62-INDEX($N$16:$N$76,$B$5+1)),0))/I62)</f>
+        <v>0.21172625978665788</v>
       </c>
       <c r="P62" s="6">
         <f t="shared" si="16"/>
-        <v>21251</v>
+        <v>21173</v>
       </c>
       <c r="Q62" s="7">
-        <v>21251</v>
+        <v>21173</v>
       </c>
       <c r="R62" s="6">
         <f t="shared" si="17"/>
@@ -12196,7 +12204,7 @@
       </c>
       <c r="H63" s="20">
         <f t="shared" si="19"/>
-        <v>18559.627877874129</v>
+        <v>18568.917481172331</v>
       </c>
       <c r="I63" s="20">
         <f t="shared" si="12"/>
@@ -12204,7 +12212,7 @@
       </c>
       <c r="J63" s="20">
         <f t="shared" si="13"/>
-        <v>5814.9715051478506</v>
+        <v>5817.8820580333195</v>
       </c>
       <c r="K63" s="20">
         <f t="shared" si="14"/>
@@ -12215,23 +12223,23 @@
         <v>1</v>
       </c>
       <c r="M63" s="20">
-        <f>SUM(I63:$I$77)</f>
-        <v>29876.367711667062</v>
+        <f>SUM(I63:$I$76)</f>
+        <v>29795.036436620023</v>
       </c>
       <c r="N63" s="20">
-        <f>SUM(J63:$J$77)</f>
-        <v>28383.966495044668</v>
+        <f>SUM(J63:$J$76)</f>
+        <v>28333.208318426921</v>
       </c>
       <c r="O63" s="22">
-        <f>IF(I63&lt;=0,0,(IF(A63&lt;$B$4,SUMPRODUCT(L63:$L$76,K63:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A63,$B$5)+1)-$M$77)-IF(A63&lt;=$B$5,$E$13*(N63-INDEX($N$16:$N$77,$B$5+1)),0))/I63)</f>
-        <v>0.20151940349658934</v>
+        <f>IF(I63&lt;=0,0,(IF(A63&lt;$B$4,SUMPRODUCT(L63:$L$75,K63:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A63,$B$5)+1)-$M$76)-IF(A63&lt;=$B$5,$E$13*(N63-INDEX($N$16:$N$76,$B$5+1)),0))/I63)</f>
+        <v>0.20059508020176875</v>
       </c>
       <c r="P63" s="6">
         <f t="shared" si="16"/>
-        <v>20152</v>
+        <v>20060</v>
       </c>
       <c r="Q63" s="7">
-        <v>20152</v>
+        <v>20060</v>
       </c>
       <c r="R63" s="6">
         <f t="shared" si="17"/>
@@ -12268,7 +12276,7 @@
       </c>
       <c r="H64" s="20">
         <f t="shared" si="19"/>
-        <v>15991.471660066454</v>
+        <v>16000.375905961821</v>
       </c>
       <c r="I64" s="20">
         <f t="shared" si="12"/>
@@ -12276,7 +12284,7 @@
       </c>
       <c r="J64" s="20">
         <f t="shared" si="13"/>
-        <v>4888.1316487150434</v>
+        <v>4890.8534198624593</v>
       </c>
       <c r="K64" s="20">
         <f t="shared" si="14"/>
@@ -12287,23 +12295,23 @@
         <v>1</v>
       </c>
       <c r="M64" s="20">
-        <f>SUM(I64:$I$77)</f>
-        <v>23830.007227095546</v>
+        <f>SUM(I64:$I$76)</f>
+        <v>23748.675952048507</v>
       </c>
       <c r="N64" s="20">
-        <f>SUM(J64:$J$77)</f>
-        <v>22568.994989896815</v>
+        <f>SUM(J64:$J$76)</f>
+        <v>22515.326260393602</v>
       </c>
       <c r="O64" s="22">
-        <f>IF(I64&lt;=0,0,(IF(A64&lt;$B$4,SUMPRODUCT(L64:$L$76,K64:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A64,$B$5)+1)-$M$77)-IF(A64&lt;=$B$5,$E$13*(N64-INDEX($N$16:$N$77,$B$5+1)),0))/I64)</f>
-        <v>0.19073598853166615</v>
+        <f>IF(I64&lt;=0,0,(IF(A64&lt;$B$4,SUMPRODUCT(L64:$L$75,K64:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A64,$B$5)+1)-$M$76)-IF(A64&lt;=$B$5,$E$13*(N64-INDEX($N$16:$N$76,$B$5+1)),0))/I64)</f>
+        <v>0.18963940854734981</v>
       </c>
       <c r="P64" s="6">
         <f t="shared" si="16"/>
-        <v>19074</v>
+        <v>18964</v>
       </c>
       <c r="Q64" s="7">
-        <v>19074</v>
+        <v>18964</v>
       </c>
       <c r="R64" s="6">
         <f t="shared" si="17"/>
@@ -12340,7 +12348,7 @@
       </c>
       <c r="H65" s="20">
         <f t="shared" si="19"/>
-        <v>13591.247894568627</v>
+        <v>13599.698161199945</v>
       </c>
       <c r="I65" s="20">
         <f t="shared" si="12"/>
@@ -12348,7 +12356,7 @@
       </c>
       <c r="J65" s="20">
         <f t="shared" si="13"/>
-        <v>4053.1243635302963</v>
+        <v>4055.644366242881</v>
       </c>
       <c r="K65" s="20">
         <f t="shared" si="14"/>
@@ -12359,23 +12367,23 @@
         <v>1</v>
       </c>
       <c r="M65" s="20">
-        <f>SUM(I65:$I$77)</f>
-        <v>18733.441609716741</v>
+        <f>SUM(I65:$I$76)</f>
+        <v>18652.110334669702</v>
       </c>
       <c r="N65" s="20">
-        <f>SUM(J65:$J$77)</f>
-        <v>17680.863341181775</v>
+        <f>SUM(J65:$J$76)</f>
+        <v>17624.47284053114</v>
       </c>
       <c r="O65" s="22">
-        <f>IF(I65&lt;=0,0,(IF(A65&lt;$B$4,SUMPRODUCT(L65:$L$76,K65:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A65,$B$5)+1)-$M$77)-IF(A65&lt;=$B$5,$E$13*(N65-INDEX($N$16:$N$77,$B$5+1)),0))/I65)</f>
-        <v>0.18017814584242872</v>
+        <f>IF(I65&lt;=0,0,(IF(A65&lt;$B$4,SUMPRODUCT(L65:$L$75,K65:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A65,$B$5)+1)-$M$76)-IF(A65&lt;=$B$5,$E$13*(N65-INDEX($N$16:$N$76,$B$5+1)),0))/I65)</f>
+        <v>0.1788598070189156</v>
       </c>
       <c r="P65" s="6">
         <f t="shared" si="16"/>
-        <v>18018</v>
+        <v>17886</v>
       </c>
       <c r="Q65" s="7">
-        <v>18018</v>
+        <v>17886</v>
       </c>
       <c r="R65" s="6">
         <f t="shared" si="17"/>
@@ -12412,7 +12420,7 @@
       </c>
       <c r="H66" s="20">
         <f t="shared" si="19"/>
-        <v>11380.084993884004</v>
+        <v>11388.007884736648</v>
       </c>
       <c r="I66" s="20">
         <f t="shared" si="12"/>
@@ -12420,7 +12428,7 @@
       </c>
       <c r="J66" s="20">
         <f t="shared" si="13"/>
-        <v>3310.9470551939853</v>
+        <v>3313.2521585522891</v>
       </c>
       <c r="K66" s="20">
         <f t="shared" si="14"/>
@@ -12431,23 +12439,23 @@
         <v>1</v>
       </c>
       <c r="M66" s="20">
-        <f>SUM(I66:$I$77)</f>
-        <v>14494.17341470198</v>
+        <f>SUM(I66:$I$76)</f>
+        <v>14412.842139654942</v>
       </c>
       <c r="N66" s="20">
-        <f>SUM(J66:$J$77)</f>
-        <v>13627.738977651479</v>
+        <f>SUM(J66:$J$76)</f>
+        <v>13568.828474288262</v>
       </c>
       <c r="O66" s="22">
-        <f>IF(I66&lt;=0,0,(IF(A66&lt;$B$4,SUMPRODUCT(L66:$L$76,K66:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A66,$B$5)+1)-$M$77)-IF(A66&lt;=$B$5,$E$13*(N66-INDEX($N$16:$N$77,$B$5+1)),0))/I66)</f>
-        <v>0.16985751104349159</v>
+        <f>IF(I66&lt;=0,0,(IF(A66&lt;$B$4,SUMPRODUCT(L66:$L$75,K66:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A66,$B$5)+1)-$M$76)-IF(A66&lt;=$B$5,$E$13*(N66-INDEX($N$16:$N$76,$B$5+1)),0))/I66)</f>
+        <v>0.1682494568608667</v>
       </c>
       <c r="P66" s="6">
         <f t="shared" si="16"/>
-        <v>16986</v>
+        <v>16825</v>
       </c>
       <c r="Q66" s="7">
-        <v>16986</v>
+        <v>16825</v>
       </c>
       <c r="R66" s="6">
         <f t="shared" si="17"/>
@@ -12484,7 +12492,7 @@
       </c>
       <c r="H67" s="20">
         <f t="shared" si="19"/>
-        <v>9375.0337460903065</v>
+        <v>9382.3555477063892</v>
       </c>
       <c r="I67" s="20">
         <f t="shared" si="12"/>
@@ -12492,7 +12500,7 @@
       </c>
       <c r="J67" s="20">
         <f t="shared" si="13"/>
-        <v>2661.0663590584559</v>
+        <v>2663.1446235741842</v>
       </c>
       <c r="K67" s="20">
         <f t="shared" si="14"/>
@@ -12503,23 +12511,23 @@
         <v>1</v>
       </c>
       <c r="M67" s="20">
-        <f>SUM(I67:$I$77)</f>
-        <v>11018.673705078001</v>
+        <f>SUM(I67:$I$76)</f>
+        <v>10937.342430030963</v>
       </c>
       <c r="N67" s="20">
-        <f>SUM(J67:$J$77)</f>
-        <v>10316.791922457493</v>
+        <f>SUM(J67:$J$76)</f>
+        <v>10255.576315735972</v>
       </c>
       <c r="O67" s="22">
-        <f>IF(I67&lt;=0,0,(IF(A67&lt;$B$4,SUMPRODUCT(L67:$L$76,K67:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A67,$B$5)+1)-$M$77)-IF(A67&lt;=$B$5,$E$13*(N67-INDEX($N$16:$N$77,$B$5+1)),0))/I67)</f>
-        <v>0.15974220880811796</v>
+        <f>IF(I67&lt;=0,0,(IF(A67&lt;$B$4,SUMPRODUCT(L67:$L$75,K67:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A67,$B$5)+1)-$M$76)-IF(A67&lt;=$B$5,$E$13*(N67-INDEX($N$16:$N$76,$B$5+1)),0))/I67)</f>
+        <v>0.15774961913952812</v>
       </c>
       <c r="P67" s="6">
         <f t="shared" si="16"/>
-        <v>15974</v>
+        <v>15775</v>
       </c>
       <c r="Q67" s="7">
-        <v>15974</v>
+        <v>15775</v>
       </c>
       <c r="R67" s="6">
         <f t="shared" si="17"/>
@@ -12556,7 +12564,7 @@
       </c>
       <c r="H68" s="20">
         <f t="shared" si="19"/>
-        <v>7585.7092043962521</v>
+        <v>7592.3601157403746</v>
       </c>
       <c r="I68" s="20">
         <f t="shared" si="12"/>
@@ -12564,7 +12572,7 @@
       </c>
       <c r="J68" s="20">
         <f t="shared" si="13"/>
-        <v>2100.657213630097</v>
+        <v>2102.4990038326728</v>
       </c>
       <c r="K68" s="20">
         <f t="shared" si="14"/>
@@ -12575,23 +12583,23 @@
         <v>1</v>
       </c>
       <c r="M68" s="20">
-        <f>SUM(I68:$I$77)</f>
-        <v>8213.8855779130608</v>
+        <f>SUM(I68:$I$76)</f>
+        <v>8132.5543028660231</v>
       </c>
       <c r="N68" s="20">
-        <f>SUM(J68:$J$77)</f>
-        <v>7655.7255633990371</v>
+        <f>SUM(J68:$J$76)</f>
+        <v>7592.4316921617874</v>
       </c>
       <c r="O68" s="22">
-        <f>IF(I68&lt;=0,0,(IF(A68&lt;$B$4,SUMPRODUCT(L68:$L$76,K68:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A68,$B$5)+1)-$M$77)-IF(A68&lt;=$B$5,$E$13*(N68-INDEX($N$16:$N$77,$B$5+1)),0))/I68)</f>
-        <v>0.14978918808082373</v>
+        <f>IF(I68&lt;=0,0,(IF(A68&lt;$B$4,SUMPRODUCT(L68:$L$75,K68:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A68,$B$5)+1)-$M$76)-IF(A68&lt;=$B$5,$E$13*(N68-INDEX($N$16:$N$76,$B$5+1)),0))/I68)</f>
+        <v>0.14727666923651953</v>
       </c>
       <c r="P68" s="6">
         <f t="shared" si="16"/>
-        <v>14979</v>
+        <v>14728</v>
       </c>
       <c r="Q68" s="7">
-        <v>14979</v>
+        <v>14728</v>
       </c>
       <c r="R68" s="6">
         <f t="shared" si="17"/>
@@ -12628,7 +12636,7 @@
       </c>
       <c r="H69" s="20">
         <f t="shared" si="19"/>
-        <v>6014.5255214906056</v>
+        <v>6020.4438912789165</v>
       </c>
       <c r="I69" s="20">
         <f t="shared" si="12"/>
@@ -12636,7 +12644,7 @@
       </c>
       <c r="J69" s="20">
         <f t="shared" si="13"/>
-        <v>1624.9369198596955</v>
+        <v>1626.5358785040719</v>
       </c>
       <c r="K69" s="20">
         <f t="shared" si="14"/>
@@ -12647,23 +12655,23 @@
         <v>1</v>
       </c>
       <c r="M69" s="20">
-        <f>SUM(I69:$I$77)</f>
-        <v>5989.507497150852</v>
+        <f>SUM(I69:$I$76)</f>
+        <v>5908.1762221038134</v>
       </c>
       <c r="N69" s="20">
-        <f>SUM(J69:$J$77)</f>
-        <v>5555.0683497689397</v>
+        <f>SUM(J69:$J$76)</f>
+        <v>5489.9326883291142</v>
       </c>
       <c r="O69" s="22">
-        <f>IF(I69&lt;=0,0,(IF(A69&lt;$B$4,SUMPRODUCT(L69:$L$76,K69:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A69,$B$5)+1)-$M$77)-IF(A69&lt;=$B$5,$E$13*(N69-INDEX($N$16:$N$77,$B$5+1)),0))/I69)</f>
-        <v>0.13996564540147605</v>
+        <f>IF(I69&lt;=0,0,(IF(A69&lt;$B$4,SUMPRODUCT(L69:$L$75,K69:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A69,$B$5)+1)-$M$76)-IF(A69&lt;=$B$5,$E$13*(N69-INDEX($N$16:$N$76,$B$5+1)),0))/I69)</f>
+        <v>0.13673432661033635</v>
       </c>
       <c r="P69" s="6">
         <f t="shared" si="16"/>
-        <v>13997</v>
+        <v>13673</v>
       </c>
       <c r="Q69" s="7">
-        <v>13997</v>
+        <v>13673</v>
       </c>
       <c r="R69" s="6">
         <f t="shared" si="17"/>
@@ -12700,7 +12708,7 @@
       </c>
       <c r="H70" s="20">
         <f t="shared" si="19"/>
-        <v>4661.3091732299617</v>
+        <v>4666.4497133892928</v>
       </c>
       <c r="I70" s="20">
         <f t="shared" si="12"/>
@@ -12708,7 +12716,7 @@
       </c>
       <c r="J70" s="20">
         <f t="shared" si="13"/>
-        <v>1228.6245200480405</v>
+        <v>1229.9794599268021</v>
       </c>
       <c r="K70" s="20">
         <f t="shared" si="14"/>
@@ -12719,23 +12727,23 @@
         <v>1</v>
       </c>
       <c r="M70" s="20">
-        <f>SUM(I70:$I$77)</f>
-        <v>4259.9375580607266</v>
+        <f>SUM(I70:$I$76)</f>
+        <v>4178.606283013688</v>
       </c>
       <c r="N70" s="20">
-        <f>SUM(J70:$J$77)</f>
-        <v>3930.1314299092433</v>
+        <f>SUM(J70:$J$76)</f>
+        <v>3863.3968098250425</v>
       </c>
       <c r="O70" s="22">
-        <f>IF(I70&lt;=0,0,(IF(A70&lt;$B$4,SUMPRODUCT(L70:$L$76,K70:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A70,$B$5)+1)-$M$77)-IF(A70&lt;=$B$5,$E$13*(N70-INDEX($N$16:$N$77,$B$5+1)),0))/I70)</f>
-        <v>0.13018082077160409</v>
+        <f>IF(I70&lt;=0,0,(IF(A70&lt;$B$4,SUMPRODUCT(L70:$L$75,K70:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A70,$B$5)+1)-$M$76)-IF(A70&lt;=$B$5,$E$13*(N70-INDEX($N$16:$N$76,$B$5+1)),0))/I70)</f>
+        <v>0.12593160899045014</v>
       </c>
       <c r="P70" s="6">
         <f t="shared" si="16"/>
-        <v>13018</v>
+        <v>12593</v>
       </c>
       <c r="Q70" s="7">
-        <v>13018</v>
+        <v>12593</v>
       </c>
       <c r="R70" s="6">
         <f t="shared" si="17"/>
@@ -12772,7 +12780,7 @@
       </c>
       <c r="H71" s="20">
         <f t="shared" si="19"/>
-        <v>3522.6264470294918</v>
+        <v>3526.9695059966057</v>
       </c>
       <c r="I71" s="20">
         <f t="shared" si="12"/>
@@ -12780,7 +12788,7 @@
       </c>
       <c r="J71" s="20">
         <f t="shared" si="13"/>
-        <v>905.84521548746466</v>
+        <v>906.96203535045572</v>
       </c>
       <c r="K71" s="20">
         <f t="shared" si="14"/>
@@ -12791,23 +12799,23 @@
         <v>1</v>
       </c>
       <c r="M71" s="20">
-        <f>SUM(I71:$I$77)</f>
-        <v>2944.683780981497</v>
+        <f>SUM(I71:$I$76)</f>
+        <v>2863.3525059344588</v>
       </c>
       <c r="N71" s="20">
-        <f>SUM(J71:$J$77)</f>
-        <v>2701.506909861203</v>
+        <f>SUM(J71:$J$76)</f>
+        <v>2633.4173498982404</v>
       </c>
       <c r="O71" s="22">
-        <f>IF(I71&lt;=0,0,(IF(A71&lt;$B$4,SUMPRODUCT(L71:$L$76,K71:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A71,$B$5)+1)-$M$77)-IF(A71&lt;=$B$5,$E$13*(N71-INDEX($N$16:$N$77,$B$5+1)),0))/I71)</f>
-        <v>0.12023807833114679</v>
+        <f>IF(I71&lt;=0,0,(IF(A71&lt;$B$4,SUMPRODUCT(L71:$L$75,K71:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A71,$B$5)+1)-$M$76)-IF(A71&lt;=$B$5,$E$13*(N71-INDEX($N$16:$N$76,$B$5+1)),0))/I71)</f>
+        <v>0.11451078400235387</v>
       </c>
       <c r="P71" s="6">
         <f t="shared" si="16"/>
-        <v>12024</v>
+        <v>11451</v>
       </c>
       <c r="Q71" s="7">
-        <v>12024</v>
+        <v>11451</v>
       </c>
       <c r="R71" s="6">
         <f t="shared" si="17"/>
@@ -12844,7 +12852,7 @@
       </c>
       <c r="H72" s="20">
         <f t="shared" si="19"/>
-        <v>2589.5831459584629</v>
+        <v>2593.1408634687841</v>
       </c>
       <c r="I72" s="20">
         <f t="shared" si="12"/>
@@ -12852,7 +12860,7 @@
       </c>
       <c r="J72" s="20">
         <f t="shared" si="13"/>
-        <v>649.67087543763466</v>
+        <v>650.56343046259985</v>
       </c>
       <c r="K72" s="20">
         <f t="shared" si="14"/>
@@ -12863,23 +12871,23 @@
         <v>1</v>
       </c>
       <c r="M72" s="20">
-        <f>SUM(I72:$I$77)</f>
-        <v>1968.8666631714932</v>
+        <f>SUM(I72:$I$76)</f>
+        <v>1887.5353881244548</v>
       </c>
       <c r="N72" s="20">
-        <f>SUM(J72:$J$77)</f>
-        <v>1795.6616943737383</v>
+        <f>SUM(J72:$J$76)</f>
+        <v>1726.4553145477844</v>
       </c>
       <c r="O72" s="22">
-        <f>IF(I72&lt;=0,0,(IF(A72&lt;$B$4,SUMPRODUCT(L72:$L$76,K72:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A72,$B$5)+1)-$M$77)-IF(A72&lt;=$B$5,$E$13*(N72-INDEX($N$16:$N$77,$B$5+1)),0))/I72)</f>
-        <v>0.10976887630753981</v>
+        <f>IF(I72&lt;=0,0,(IF(A72&lt;$B$4,SUMPRODUCT(L72:$L$75,K72:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A72,$B$5)+1)-$M$76)-IF(A72&lt;=$B$5,$E$13*(N72-INDEX($N$16:$N$76,$B$5+1)),0))/I72)</f>
+        <v>0.10183729218236488</v>
       </c>
       <c r="P72" s="6">
         <f t="shared" si="16"/>
-        <v>10977</v>
+        <v>10184</v>
       </c>
       <c r="Q72" s="7">
-        <v>10977</v>
+        <v>10184</v>
       </c>
       <c r="R72" s="6">
         <f t="shared" si="17"/>
@@ -12916,7 +12924,7 @@
       </c>
       <c r="H73" s="20">
         <f t="shared" si="19"/>
-        <v>1846.5251544546256</v>
+        <v>1849.3416525733874</v>
       </c>
       <c r="I73" s="20">
         <f t="shared" si="12"/>
@@ -12924,7 +12932,7 @@
       </c>
       <c r="J73" s="20">
         <f t="shared" si="13"/>
-        <v>451.95469356107662</v>
+        <v>452.64405841544072</v>
       </c>
       <c r="K73" s="20">
         <f t="shared" si="14"/>
@@ -12935,23 +12943,23 @@
         <v>1</v>
       </c>
       <c r="M73" s="20">
-        <f>SUM(I73:$I$77)</f>
-        <v>1264.2417412680102</v>
+        <f>SUM(I73:$I$76)</f>
+        <v>1182.9104662209718</v>
       </c>
       <c r="N73" s="20">
-        <f>SUM(J73:$J$77)</f>
-        <v>1145.9908189361036</v>
+        <f>SUM(J73:$J$76)</f>
+        <v>1075.8918840851845</v>
       </c>
       <c r="O73" s="22">
-        <f>IF(I73&lt;=0,0,(IF(A73&lt;$B$4,SUMPRODUCT(L73:$L$76,K73:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A73,$B$5)+1)-$M$77)-IF(A73&lt;=$B$5,$E$13*(N73-INDEX($N$16:$N$77,$B$5+1)),0))/I73)</f>
-        <v>9.8168298026157938E-2</v>
+        <f>IF(I73&lt;=0,0,(IF(A73&lt;$B$4,SUMPRODUCT(L73:$L$75,K73:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A73,$B$5)+1)-$M$76)-IF(A73&lt;=$B$5,$E$13*(N73-INDEX($N$16:$N$76,$B$5+1)),0))/I73)</f>
+        <v>8.6849765400958248E-2</v>
       </c>
       <c r="P73" s="6">
         <f t="shared" si="16"/>
-        <v>9817</v>
+        <v>8685</v>
       </c>
       <c r="Q73" s="7">
-        <v>9817</v>
+        <v>8685</v>
       </c>
       <c r="R73" s="6">
         <f t="shared" si="17"/>
@@ -12988,7 +12996,7 @@
       </c>
       <c r="H74" s="20">
         <f t="shared" si="19"/>
-        <v>1272.4031047782132</v>
+        <v>1274.5498212235077</v>
       </c>
       <c r="I74" s="20">
         <f t="shared" si="12"/>
@@ -12996,7 +13004,7 @@
       </c>
       <c r="J74" s="20">
         <f t="shared" si="13"/>
-        <v>303.83690773352242</v>
+        <v>304.34952176603275</v>
       </c>
       <c r="K74" s="20">
         <f t="shared" si="14"/>
@@ -13007,23 +13015,23 @@
         <v>1</v>
       </c>
       <c r="M74" s="20">
-        <f>SUM(I74:$I$77)</f>
-        <v>770.46820808674306</v>
+        <f>SUM(I74:$I$76)</f>
+        <v>689.13693303970467</v>
       </c>
       <c r="N74" s="20">
-        <f>SUM(J74:$J$77)</f>
-        <v>694.03612537502693</v>
+        <f>SUM(J74:$J$76)</f>
+        <v>623.24782566974386</v>
       </c>
       <c r="O74" s="22">
-        <f>IF(I74&lt;=0,0,(IF(A74&lt;$B$4,SUMPRODUCT(L74:$L$76,K74:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A74,$B$5)+1)-$M$77)-IF(A74&lt;=$B$5,$E$13*(N74-INDEX($N$16:$N$77,$B$5+1)),0))/I74)</f>
-        <v>8.4410619874958973E-2</v>
+        <f>IF(I74&lt;=0,0,(IF(A74&lt;$B$4,SUMPRODUCT(L74:$L$75,K74:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A74,$B$5)+1)-$M$76)-IF(A74&lt;=$B$5,$E$13*(N74-INDEX($N$16:$N$76,$B$5+1)),0))/I74)</f>
+        <v>6.7705097698060115E-2</v>
       </c>
       <c r="P74" s="6">
         <f t="shared" si="16"/>
-        <v>8441</v>
+        <v>6771</v>
       </c>
       <c r="Q74" s="7">
-        <v>8441</v>
+        <v>6771</v>
       </c>
       <c r="R74" s="6">
         <f t="shared" si="17"/>
@@ -13060,7 +13068,7 @@
       </c>
       <c r="H75" s="20">
         <f t="shared" si="19"/>
-        <v>843.61379630252668</v>
+        <v>845.18287697126698</v>
       </c>
       <c r="I75" s="20">
         <f t="shared" si="12"/>
@@ -13068,7 +13076,7 @@
       </c>
       <c r="J75" s="20">
         <f t="shared" si="13"/>
-        <v>196.53305966335679</v>
+        <v>196.89860160451249</v>
       </c>
       <c r="K75" s="20">
         <f t="shared" si="14"/>
@@ -13079,23 +13087,23 @@
         <v>1</v>
       </c>
       <c r="M75" s="20">
-        <f>SUM(I75:$I$77)</f>
-        <v>435.9206383914526</v>
+        <f>SUM(I75:$I$76)</f>
+        <v>354.58936334441421</v>
       </c>
       <c r="N75" s="20">
-        <f>SUM(J75:$J$77)</f>
-        <v>390.19921764150456</v>
+        <f>SUM(J75:$J$76)</f>
+        <v>318.89830390371111</v>
       </c>
       <c r="O75" s="22">
-        <f>IF(I75&lt;=0,0,(IF(A75&lt;$B$4,SUMPRODUCT(L75:$L$76,K75:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A75,$B$5)+1)-$M$77)-IF(A75&lt;=$B$5,$E$13*(N75-INDEX($N$16:$N$77,$B$5+1)),0))/I75)</f>
-        <v>6.6590886875114483E-2</v>
+        <f>IF(I75&lt;=0,0,(IF(A75&lt;$B$4,SUMPRODUCT(L75:$L$75,K75:$K$75),0)+베타후*(INDEX($M$16:$M$76,MAX(A75,$B$5)+1)-$M$76)-IF(A75&lt;=$B$5,$E$13*(N75-INDEX($N$16:$N$76,$B$5+1)),0))/I75)</f>
+        <v>4.0978355424392189E-2</v>
       </c>
       <c r="P75" s="6">
         <f t="shared" si="16"/>
-        <v>6659</v>
+        <v>4098</v>
       </c>
       <c r="Q75" s="7">
-        <v>6659</v>
+        <v>4098</v>
       </c>
       <c r="R75" s="6">
         <f t="shared" si="17"/>
@@ -13132,7 +13140,7 @@
       </c>
       <c r="H76" s="20">
         <f t="shared" si="19"/>
-        <v>535.67768972683996</v>
+        <v>536.77303953449939</v>
       </c>
       <c r="I76" s="20">
         <f t="shared" si="12"/>
@@ -13140,7 +13148,7 @@
       </c>
       <c r="J76" s="20">
         <f t="shared" si="13"/>
-        <v>121.75074726493715</v>
+        <v>121.9997022991986</v>
       </c>
       <c r="K76" s="20">
         <f t="shared" si="14"/>
@@ -13151,97 +13159,25 @@
         <v>1</v>
       </c>
       <c r="M76" s="20">
-        <f>SUM(I76:$I$77)</f>
-        <v>217.71527061962757</v>
+        <f>SUM(I76:$I$76)</f>
+        <v>136.38399557258919</v>
       </c>
       <c r="N76" s="20">
-        <f>SUM(J76:$J$77)</f>
-        <v>193.66615797814777</v>
+        <f>SUM(J76:$J$76)</f>
+        <v>121.9997022991986</v>
       </c>
       <c r="O76" s="22">
-        <f>IF(I76&lt;=0,0,(IF(A76&lt;$B$4,SUMPRODUCT(L76:$L$76,K76:$K$76),0)+베타후*(INDEX($M$16:$M$77,MAX(A76,$B$5)+1)-$M$77)-IF(A76&lt;=$B$5,$E$13*(N76-INDEX($N$16:$N$77,$B$5+1)),0))/I76)</f>
-        <v>4.0978355424392189E-2</v>
+        <f>IF(I76&lt;=0,0,(IF(A76&lt;$B$4,SUMPRODUCT(L$75:$L76,K$75:$K76),0)+베타후*(INDEX($M$16:$M$76,MAX(A76,$B$5)+1)-$M$76)-IF(A76&lt;=$B$5,$E$13*(N76-INDEX($N$16:$N$76,$B$5+1)),0))/I76)</f>
+        <v>0</v>
       </c>
       <c r="P76" s="6">
         <f t="shared" si="16"/>
-        <v>4098</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="7">
-        <v>4098</v>
+        <v>0</v>
       </c>
       <c r="R76" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A77">
-        <v>61</v>
-      </c>
-      <c r="B77">
-        <f t="shared" si="10"/>
-        <v>101</v>
-      </c>
-      <c r="C77" s="19">
-        <f>INDEX(위험률!$B:$B,B77+2)</f>
-        <v>0.38674999999999998</v>
-      </c>
-      <c r="D77" s="19">
-        <f>INDEX(위험률!$D:$D,B77+2)</f>
-        <v>4.0474999999999997E-2</v>
-      </c>
-      <c r="E77" s="19">
-        <f>INDEX(위험률!$C:$C,B77+2)</f>
-        <v>7.5129999999999997E-3</v>
-      </c>
-      <c r="F77" s="19">
-        <f t="shared" si="11"/>
-        <v>0.41939814687499999</v>
-      </c>
-      <c r="G77" s="20">
-        <f t="shared" si="18"/>
-        <v>366.78652296526548</v>
-      </c>
-      <c r="H77" s="20">
-        <f t="shared" si="19"/>
-        <v>324.32300400875181</v>
-      </c>
-      <c r="I77" s="20">
-        <f t="shared" si="12"/>
-        <v>81.331275047038389</v>
-      </c>
-      <c r="J77" s="20">
-        <f t="shared" si="13"/>
-        <v>71.915410713210619</v>
-      </c>
-      <c r="K77" s="20">
-        <f t="shared" si="14"/>
-        <v>3.2514906209495007</v>
-      </c>
-      <c r="L77" s="21">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="M77" s="20">
-        <f>SUM(I77:$I$77)</f>
-        <v>81.331275047038389</v>
-      </c>
-      <c r="N77" s="20">
-        <f>SUM(J77:$J$77)</f>
-        <v>71.915410713210619</v>
-      </c>
-      <c r="O77" s="22">
-        <f>IF(I77&lt;=0,0,(IF(A77&lt;$B$4,SUMPRODUCT(L$76:$L77,K$76:$K77),0)+베타후*(INDEX($M$16:$M$77,MAX(A77,$B$5)+1)-$M$77)-IF(A77&lt;=$B$5,$E$13*(N77-INDEX($N$16:$N$77,$B$5+1)),0))/I77)</f>
-        <v>0</v>
-      </c>
-      <c r="P77" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="7">
-        <v>0</v>
-      </c>
-      <c r="R77" s="6">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
